--- a/Versão5/ARQ/Ontologia_Circulacao.xlsx
+++ b/Versão5/ARQ/Ontologia_Circulacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63AF6B4-51A6-429E-B78B-BBBC26B459D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD0AECA-52E4-4F4B-99B9-95063BD80462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="594">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1108,9 +1108,6 @@
     <t>Texto Bajar de escaleras</t>
   </si>
   <si>
-    <t>[ 3E ]</t>
-  </si>
-  <si>
     <t>[ OST_StairsRailing ]</t>
   </si>
   <si>
@@ -1849,6 +1846,15 @@
   </si>
   <si>
     <t>"Layout de circulação do projeto"</t>
+  </si>
+  <si>
+    <t>[ 3E.08.06.04 ]</t>
+  </si>
+  <si>
+    <t>[ 3E.08.04.10 ]</t>
+  </si>
+  <si>
+    <t>[ 3E.08.06.02 ]</t>
   </si>
 </sst>
 </file>
@@ -2361,15 +2367,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <font>
         <b val="0"/>
@@ -2991,7 +2989,7 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="66.28515625" customWidth="1"/>
+    <col min="2" max="2" width="69.5703125" customWidth="1"/>
     <col min="3" max="3" width="3.42578125" style="41" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3190,7 +3188,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46248.412230439812</v>
+        <v>46248.423007638892</v>
       </c>
       <c r="C18" s="40" t="s">
         <v>173</v>
@@ -3318,7 +3316,7 @@
         <v>38</v>
       </c>
       <c r="F1" s="33" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G1" s="52" t="s">
         <v>0</v>
@@ -3375,7 +3373,7 @@
         <v>167</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Z1" s="55" t="s">
         <v>169</v>
@@ -3389,19 +3387,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>9</v>
@@ -3435,10 +3433,10 @@
         <v>Elevador.Hidráulico</v>
       </c>
       <c r="P2" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="Q2" s="27" t="s">
         <v>451</v>
-      </c>
-      <c r="Q2" s="27" t="s">
-        <v>452</v>
       </c>
       <c r="R2" s="50" t="s">
         <v>9</v>
@@ -3463,13 +3461,13 @@
         <v>Key-CIRCU-2</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y2" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z2" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA2" s="27" t="str">
         <f t="shared" ref="AA2:AA33" si="7">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -3481,19 +3479,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F3" s="31" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>9</v>
@@ -3555,13 +3553,13 @@
         <v>Key-CIRCU-3</v>
       </c>
       <c r="X3" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y3" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z3" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA3" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3573,19 +3571,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>9</v>
@@ -3619,10 +3617,10 @@
         <v>Elevador.MR</v>
       </c>
       <c r="P4" s="27" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q4" s="27" t="s">
         <v>455</v>
-      </c>
-      <c r="Q4" s="27" t="s">
-        <v>456</v>
       </c>
       <c r="R4" s="50" t="s">
         <v>9</v>
@@ -3647,13 +3645,13 @@
         <v>Key-CIRCU-4</v>
       </c>
       <c r="X4" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y4" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z4" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA4" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3665,19 +3663,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>9</v>
@@ -3711,10 +3709,10 @@
         <v>Elevador.MRL</v>
       </c>
       <c r="P5" s="27" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q5" s="27" t="s">
         <v>458</v>
-      </c>
-      <c r="Q5" s="27" t="s">
-        <v>459</v>
       </c>
       <c r="R5" s="50" t="s">
         <v>9</v>
@@ -3739,13 +3737,13 @@
         <v>Key-CIRCU-5</v>
       </c>
       <c r="X5" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y5" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z5" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA5" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3757,13 +3755,13 @@
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E6" s="30" t="s">
         <v>201</v>
@@ -3831,13 +3829,13 @@
         <v>Key-CIRCU-6</v>
       </c>
       <c r="X6" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y6" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z6" s="50" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AA6" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3849,19 +3847,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>201</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>9</v>
@@ -3895,10 +3893,10 @@
         <v>Plataforma.de.Elevação</v>
       </c>
       <c r="P7" s="27" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q7" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="R7" s="50" t="s">
         <v>9</v>
@@ -3923,13 +3921,13 @@
         <v>Key-CIRCU-7</v>
       </c>
       <c r="X7" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y7" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z7" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA7" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3941,19 +3939,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>9</v>
@@ -3987,10 +3985,10 @@
         <v>Plataforma.Articulada</v>
       </c>
       <c r="P8" s="27" t="s">
+        <v>463</v>
+      </c>
+      <c r="Q8" s="27" t="s">
         <v>464</v>
-      </c>
-      <c r="Q8" s="27" t="s">
-        <v>465</v>
       </c>
       <c r="R8" s="50" t="s">
         <v>9</v>
@@ -4015,13 +4013,13 @@
         <v>Key-CIRCU-8</v>
       </c>
       <c r="X8" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y8" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z8" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA8" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4033,19 +4031,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>9</v>
@@ -4079,10 +4077,10 @@
         <v>Plataforma.Cesto</v>
       </c>
       <c r="P9" s="27" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q9" s="27" t="s">
         <v>467</v>
-      </c>
-      <c r="Q9" s="27" t="s">
-        <v>468</v>
       </c>
       <c r="R9" s="50" t="s">
         <v>9</v>
@@ -4107,13 +4105,13 @@
         <v>Key-CIRCU-9</v>
       </c>
       <c r="X9" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y9" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z9" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA9" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4125,19 +4123,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>201</v>
       </c>
       <c r="F10" s="49" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>9</v>
@@ -4171,10 +4169,10 @@
         <v>Acessório.Maquinária</v>
       </c>
       <c r="P10" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q10" s="27" t="s">
         <v>470</v>
-      </c>
-      <c r="Q10" s="27" t="s">
-        <v>471</v>
       </c>
       <c r="R10" s="50" t="s">
         <v>9</v>
@@ -4199,13 +4197,13 @@
         <v>Key-CIRCU-10</v>
       </c>
       <c r="X10" s="27" t="s">
+        <v>471</v>
+      </c>
+      <c r="Y10" s="26" t="s">
         <v>472</v>
       </c>
-      <c r="Y10" s="26" t="s">
+      <c r="Z10" s="50" t="s">
         <v>473</v>
-      </c>
-      <c r="Z10" s="50" t="s">
-        <v>474</v>
       </c>
       <c r="AA10" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4217,13 +4215,13 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>238</v>
@@ -4291,13 +4289,13 @@
         <v>Key-CIRCU-11</v>
       </c>
       <c r="X11" s="27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="Y11" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z11" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA11" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4309,13 +4307,13 @@
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>238</v>
@@ -4383,13 +4381,13 @@
         <v>Key-CIRCU-12</v>
       </c>
       <c r="X12" s="27" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y12" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z12" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA12" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4401,13 +4399,13 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>238</v>
@@ -4475,13 +4473,13 @@
         <v>Key-CIRCU-13</v>
       </c>
       <c r="X13" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y13" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z13" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA13" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4493,13 +4491,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>238</v>
@@ -4567,13 +4565,13 @@
         <v>Key-CIRCU-14</v>
       </c>
       <c r="X14" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Y14" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z14" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA14" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4585,13 +4583,13 @@
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>238</v>
@@ -4659,13 +4657,13 @@
         <v>Key-CIRCU-15</v>
       </c>
       <c r="X15" s="27" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="Y15" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z15" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA15" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4677,13 +4675,13 @@
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>238</v>
@@ -4751,13 +4749,13 @@
         <v>Key-CIRCU-16</v>
       </c>
       <c r="X16" s="27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="Y16" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z16" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA16" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4769,13 +4767,13 @@
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>238</v>
@@ -4843,13 +4841,13 @@
         <v>Key-CIRCU-17</v>
       </c>
       <c r="X17" s="27" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="Y17" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z17" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA17" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4861,13 +4859,13 @@
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>238</v>
@@ -4935,13 +4933,13 @@
         <v>Key-CIRCU-18</v>
       </c>
       <c r="X18" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="Y18" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z18" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA18" s="27" t="str">
         <f t="shared" si="7"/>
@@ -4953,13 +4951,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>238</v>
@@ -5027,13 +5025,13 @@
         <v>Key-CIRCU-19</v>
       </c>
       <c r="X19" s="27" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="Y19" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z19" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA19" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5045,13 +5043,13 @@
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>238</v>
@@ -5119,13 +5117,13 @@
         <v>Key-CIRCU-20</v>
       </c>
       <c r="X20" s="27" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="Y20" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z20" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA20" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5137,13 +5135,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>238</v>
@@ -5211,13 +5209,13 @@
         <v>Key-CIRCU-21</v>
       </c>
       <c r="X21" s="27" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Y21" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z21" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA21" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5229,13 +5227,13 @@
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>238</v>
@@ -5303,13 +5301,13 @@
         <v>Key-CIRCU-22</v>
       </c>
       <c r="X22" s="27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Y22" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z22" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA22" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5321,13 +5319,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>238</v>
@@ -5395,13 +5393,13 @@
         <v>Key-CIRCU-23</v>
       </c>
       <c r="X23" s="27" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Y23" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z23" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA23" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5413,13 +5411,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>238</v>
@@ -5487,13 +5485,13 @@
         <v>Key-CIRCU-24</v>
       </c>
       <c r="X24" s="27" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y24" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z24" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA24" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5505,19 +5503,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="G25" s="53" t="s">
         <v>9</v>
@@ -5579,13 +5577,13 @@
         <v>Key-CIRCU-25</v>
       </c>
       <c r="X25" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y25" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Z25" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA25" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5597,19 +5595,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>238</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G26" s="53" t="s">
         <v>9</v>
@@ -5671,13 +5669,13 @@
         <v>Key-CIRCU-26</v>
       </c>
       <c r="X26" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y26" s="26" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Z26" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA26" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5689,13 +5687,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>238</v>
@@ -5763,13 +5761,13 @@
         <v>Key-CIRCU-27</v>
       </c>
       <c r="X27" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y27" s="26" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Z27" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA27" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5781,13 +5779,13 @@
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>238</v>
@@ -5855,13 +5853,13 @@
         <v>Key-CIRCU-28</v>
       </c>
       <c r="X28" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y28" s="26" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Z28" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA28" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5873,13 +5871,13 @@
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>238</v>
@@ -5947,13 +5945,13 @@
         <v>Key-CIRCU-29</v>
       </c>
       <c r="X29" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y29" s="26" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Z29" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA29" s="27" t="str">
         <f t="shared" si="7"/>
@@ -5965,13 +5963,13 @@
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>238</v>
@@ -6039,13 +6037,13 @@
         <v>Key-CIRCU-30</v>
       </c>
       <c r="X30" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y30" s="26" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Z30" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA30" s="27" t="str">
         <f t="shared" si="7"/>
@@ -6057,13 +6055,13 @@
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>238</v>
@@ -6131,13 +6129,13 @@
         <v>Key-CIRCU-31</v>
       </c>
       <c r="X31" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y31" s="26" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Z31" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA31" s="27" t="str">
         <f t="shared" si="7"/>
@@ -6149,13 +6147,13 @@
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>238</v>
@@ -6223,13 +6221,13 @@
         <v>Key-CIRCU-32</v>
       </c>
       <c r="X32" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y32" s="26" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Z32" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA32" s="27" t="str">
         <f t="shared" si="7"/>
@@ -6241,13 +6239,13 @@
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>238</v>
@@ -6315,13 +6313,13 @@
         <v>Key-CIRCU-33</v>
       </c>
       <c r="X33" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y33" s="26" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Z33" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA33" s="27" t="str">
         <f t="shared" si="7"/>
@@ -6333,13 +6331,13 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>238</v>
@@ -6407,13 +6405,13 @@
         <v>Key-CIRCU-34</v>
       </c>
       <c r="X34" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y34" s="26" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Z34" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA34" s="27" t="str">
         <f t="shared" ref="AA34:AA65" si="16">_xlfn.TRANSLATE(P34,"pt","en")</f>
@@ -6425,13 +6423,13 @@
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>238</v>
@@ -6499,13 +6497,13 @@
         <v>Key-CIRCU-35</v>
       </c>
       <c r="X35" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y35" s="26" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Z35" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA35" s="27" t="str">
         <f t="shared" si="16"/>
@@ -6517,13 +6515,13 @@
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>238</v>
@@ -6591,13 +6589,13 @@
         <v>Key-CIRCU-36</v>
       </c>
       <c r="X36" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y36" s="26" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Z36" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA36" s="27" t="str">
         <f t="shared" si="16"/>
@@ -6609,13 +6607,13 @@
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>238</v>
@@ -6683,13 +6681,13 @@
         <v>Key-CIRCU-37</v>
       </c>
       <c r="X37" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y37" s="26" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Z37" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA37" s="27" t="str">
         <f t="shared" si="16"/>
@@ -6701,13 +6699,13 @@
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>238</v>
@@ -6775,13 +6773,13 @@
         <v>Key-CIRCU-38</v>
       </c>
       <c r="X38" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y38" s="26" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Z38" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA38" s="27" t="str">
         <f t="shared" si="16"/>
@@ -6793,13 +6791,13 @@
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>238</v>
@@ -6867,13 +6865,13 @@
         <v>Key-CIRCU-39</v>
       </c>
       <c r="X39" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y39" s="26" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Z39" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA39" s="27" t="str">
         <f t="shared" si="16"/>
@@ -6885,13 +6883,13 @@
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>238</v>
@@ -6959,13 +6957,13 @@
         <v>Key-CIRCU-40</v>
       </c>
       <c r="X40" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y40" s="26" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Z40" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA40" s="27" t="str">
         <f t="shared" si="16"/>
@@ -6977,13 +6975,13 @@
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>238</v>
@@ -7051,13 +7049,13 @@
         <v>Key-CIRCU-41</v>
       </c>
       <c r="X41" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="Y41" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z41" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA41" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7069,13 +7067,13 @@
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>238</v>
@@ -7143,13 +7141,13 @@
         <v>Key-CIRCU-42</v>
       </c>
       <c r="X42" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="Y42" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z42" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA42" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7161,13 +7159,13 @@
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>238</v>
@@ -7235,13 +7233,13 @@
         <v>Key-CIRCU-43</v>
       </c>
       <c r="X43" s="27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Y43" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z43" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA43" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7253,13 +7251,13 @@
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>238</v>
@@ -7327,13 +7325,13 @@
         <v>Key-CIRCU-44</v>
       </c>
       <c r="X44" s="27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="Y44" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z44" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA44" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7345,13 +7343,13 @@
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>238</v>
@@ -7419,13 +7417,13 @@
         <v>Key-CIRCU-45</v>
       </c>
       <c r="X45" s="27" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="Y45" s="27" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Z45" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA45" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7437,13 +7435,13 @@
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>238</v>
@@ -7511,13 +7509,13 @@
         <v>Key-CIRCU-46</v>
       </c>
       <c r="X46" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y46" s="26" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Z46" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA46" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7529,13 +7527,13 @@
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>238</v>
@@ -7603,13 +7601,13 @@
         <v>Key-CIRCU-47</v>
       </c>
       <c r="X47" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y47" s="26" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Z47" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA47" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7621,13 +7619,13 @@
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>238</v>
@@ -7695,13 +7693,13 @@
         <v>Key-CIRCU-48</v>
       </c>
       <c r="X48" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y48" s="26" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Z48" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA48" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7713,13 +7711,13 @@
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>238</v>
@@ -7787,13 +7785,13 @@
         <v>Key-CIRCU-49</v>
       </c>
       <c r="X49" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y49" s="26" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Z49" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA49" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7805,13 +7803,13 @@
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>238</v>
@@ -7879,13 +7877,13 @@
         <v>Key-CIRCU-50</v>
       </c>
       <c r="X50" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y50" s="26" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Z50" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA50" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7897,16 +7895,16 @@
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>290</v>
@@ -7971,13 +7969,13 @@
         <v>Key-CIRCU-51</v>
       </c>
       <c r="X51" s="27" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Y51" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z51" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA51" s="27" t="str">
         <f t="shared" si="16"/>
@@ -7989,16 +7987,16 @@
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>292</v>
@@ -8063,13 +8061,13 @@
         <v>Key-CIRCU-52</v>
       </c>
       <c r="X52" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Y52" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z52" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA52" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8081,19 +8079,19 @@
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F53" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G53" s="53" t="s">
         <v>9</v>
@@ -8155,13 +8153,13 @@
         <v>Key-CIRCU-53</v>
       </c>
       <c r="X53" s="27" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y53" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z53" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA53" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8173,19 +8171,19 @@
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G54" s="53" t="s">
         <v>9</v>
@@ -8247,13 +8245,13 @@
         <v>Key-CIRCU-54</v>
       </c>
       <c r="X54" s="27" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="Y54" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z54" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA54" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8265,19 +8263,19 @@
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F55" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="G55" s="53" t="s">
         <v>9</v>
@@ -8339,13 +8337,13 @@
         <v>Key-CIRCU-55</v>
       </c>
       <c r="X55" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Y55" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z55" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA55" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8357,19 +8355,19 @@
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F56" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G56" s="53" t="s">
         <v>9</v>
@@ -8431,13 +8429,13 @@
         <v>Key-CIRCU-56</v>
       </c>
       <c r="X56" s="27" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y56" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z56" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA56" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8449,19 +8447,19 @@
         <v>57</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E57" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F57" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G57" s="53" t="s">
         <v>9</v>
@@ -8523,13 +8521,13 @@
         <v>Key-CIRCU-57</v>
       </c>
       <c r="X57" s="27" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y57" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z57" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA57" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8541,19 +8539,19 @@
         <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F58" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G58" s="53" t="s">
         <v>9</v>
@@ -8615,13 +8613,13 @@
         <v>Key-CIRCU-58</v>
       </c>
       <c r="X58" s="27" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y58" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z58" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA58" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8633,19 +8631,19 @@
         <v>59</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="F59" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G59" s="53" t="s">
         <v>9</v>
@@ -8707,13 +8705,13 @@
         <v>Key-CIRCU-59</v>
       </c>
       <c r="X59" s="27" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y59" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z59" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA59" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8725,13 +8723,13 @@
         <v>60</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>194</v>
@@ -8799,13 +8797,13 @@
         <v>Key-CIRCU-60</v>
       </c>
       <c r="X60" s="27" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y60" s="27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Z60" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA60" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8817,13 +8815,13 @@
         <v>61</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>194</v>
@@ -8891,13 +8889,13 @@
         <v>Key-CIRCU-61</v>
       </c>
       <c r="X61" s="27" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Y61" s="27" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Z61" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA61" s="27" t="str">
         <f t="shared" si="16"/>
@@ -8909,19 +8907,19 @@
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G62" s="53" t="s">
         <v>9</v>
@@ -8983,13 +8981,13 @@
         <v>Key-CIRCU-62</v>
       </c>
       <c r="X62" s="27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Y62" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z62" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA62" s="27" t="str">
         <f t="shared" si="16"/>
@@ -9001,19 +8999,19 @@
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D63" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="G63" s="53" t="s">
         <v>9</v>
@@ -9075,13 +9073,13 @@
         <v>Key-CIRCU-63</v>
       </c>
       <c r="X63" s="27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Y63" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z63" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA63" s="27" t="str">
         <f t="shared" si="16"/>
@@ -9093,19 +9091,19 @@
         <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G64" s="53" t="s">
         <v>9</v>
@@ -9167,13 +9165,13 @@
         <v>Key-CIRCU-64</v>
       </c>
       <c r="X64" s="27" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Y64" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z64" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA64" s="27" t="str">
         <f t="shared" si="16"/>
@@ -9185,16 +9183,16 @@
         <v>65</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>44</v>
@@ -9259,13 +9257,13 @@
         <v>Key-CIRCU-65</v>
       </c>
       <c r="X65" s="27" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Y65" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z65" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA65" s="27" t="str">
         <f t="shared" si="16"/>
@@ -9277,19 +9275,19 @@
         <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G66" s="53" t="s">
         <v>9</v>
@@ -9351,13 +9349,13 @@
         <v>Key-CIRCU-66</v>
       </c>
       <c r="X66" s="27" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Y66" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z66" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA66" s="27" t="str">
         <f t="shared" ref="AA66:AA97" si="24">_xlfn.TRANSLATE(P66,"pt","en")</f>
@@ -9369,19 +9367,19 @@
         <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G67" s="53" t="s">
         <v>9</v>
@@ -9443,13 +9441,13 @@
         <v>Key-CIRCU-67</v>
       </c>
       <c r="X67" s="27" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Y67" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z67" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA67" s="27" t="str">
         <f t="shared" si="24"/>
@@ -9461,19 +9459,19 @@
         <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G68" s="53" t="s">
         <v>9</v>
@@ -9535,13 +9533,13 @@
         <v>Key-CIRCU-68</v>
       </c>
       <c r="X68" s="27" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Y68" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z68" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA68" s="27" t="str">
         <f t="shared" si="24"/>
@@ -9553,19 +9551,19 @@
         <v>69</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E69" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="G69" s="7" t="s">
         <v>9</v>
@@ -9627,13 +9625,13 @@
         <v>Key-CIRCU-69</v>
       </c>
       <c r="X69" s="27" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Y69" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z69" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA69" s="27" t="str">
         <f t="shared" si="24"/>
@@ -9645,19 +9643,19 @@
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>9</v>
@@ -9719,13 +9717,13 @@
         <v>Key-CIRCU-70</v>
       </c>
       <c r="X70" s="27" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Y70" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z70" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA70" s="27" t="str">
         <f t="shared" si="24"/>
@@ -9737,19 +9735,19 @@
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>9</v>
@@ -9811,13 +9809,13 @@
         <v>Key-CIRCU-71</v>
       </c>
       <c r="X71" s="27" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Y71" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z71" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA71" s="27" t="str">
         <f t="shared" si="24"/>
@@ -9829,19 +9827,19 @@
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>9</v>
@@ -9903,13 +9901,13 @@
         <v>Key-CIRCU-72</v>
       </c>
       <c r="X72" s="27" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Y72" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z72" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA72" s="27" t="str">
         <f t="shared" si="24"/>
@@ -9921,16 +9919,16 @@
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>178</v>
@@ -9995,13 +9993,13 @@
         <v>Key-CIRCU-73</v>
       </c>
       <c r="X73" s="27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Y73" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z73" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA73" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10013,16 +10011,16 @@
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>182</v>
@@ -10087,13 +10085,13 @@
         <v>Key-CIRCU-74</v>
       </c>
       <c r="X74" s="27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y74" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z74" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA74" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10105,16 +10103,16 @@
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>186</v>
@@ -10179,13 +10177,13 @@
         <v>Key-CIRCU-75</v>
       </c>
       <c r="X75" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Y75" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z75" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA75" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10197,16 +10195,16 @@
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>189</v>
@@ -10271,13 +10269,13 @@
         <v>Key-CIRCU-76</v>
       </c>
       <c r="X76" s="27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y76" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z76" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA76" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10289,19 +10287,19 @@
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>9</v>
@@ -10363,13 +10361,13 @@
         <v>Key-CIRCU-77</v>
       </c>
       <c r="X77" s="27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Y77" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z77" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA77" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10381,19 +10379,19 @@
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>9</v>
@@ -10455,13 +10453,13 @@
         <v>Key-CIRCU-78</v>
       </c>
       <c r="X78" s="27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y78" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z78" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA78" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10473,19 +10471,19 @@
         <v>79</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>9</v>
@@ -10547,13 +10545,13 @@
         <v>Key-CIRCU-79</v>
       </c>
       <c r="X79" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Y79" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z79" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA79" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10565,19 +10563,19 @@
         <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G80" s="7" t="s">
         <v>9</v>
@@ -10639,13 +10637,13 @@
         <v>Key-CIRCU-80</v>
       </c>
       <c r="X80" s="27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y80" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z80" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA80" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10657,19 +10655,19 @@
         <v>81</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>547</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>9</v>
@@ -10731,13 +10729,13 @@
         <v>Key-CIRCU-81</v>
       </c>
       <c r="X81" s="27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Y81" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z81" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA81" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10749,19 +10747,19 @@
         <v>82</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G82" s="7" t="s">
         <v>9</v>
@@ -10823,13 +10821,13 @@
         <v>Key-CIRCU-82</v>
       </c>
       <c r="X82" s="27" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Y82" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z82" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA82" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10841,19 +10839,19 @@
         <v>83</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>9</v>
@@ -10915,13 +10913,13 @@
         <v>Key-CIRCU-83</v>
       </c>
       <c r="X83" s="27" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Y83" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z83" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA83" s="27" t="str">
         <f t="shared" si="24"/>
@@ -10933,19 +10931,19 @@
         <v>84</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>9</v>
@@ -11007,13 +11005,13 @@
         <v>Key-CIRCU-84</v>
       </c>
       <c r="X84" s="27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y84" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z84" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA84" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11025,13 +11023,13 @@
         <v>85</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>192</v>
@@ -11099,13 +11097,13 @@
         <v>Key-CIRCU-85</v>
       </c>
       <c r="X85" s="27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Y85" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z85" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA85" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11117,19 +11115,19 @@
         <v>86</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>9</v>
@@ -11191,13 +11189,13 @@
         <v>Key-CIRCU-86</v>
       </c>
       <c r="X86" s="27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Y86" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z86" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA86" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11209,19 +11207,19 @@
         <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>9</v>
@@ -11283,13 +11281,13 @@
         <v>Key-CIRCU-87</v>
       </c>
       <c r="X87" s="27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Y87" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z87" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA87" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11301,19 +11299,19 @@
         <v>88</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>9</v>
@@ -11375,13 +11373,13 @@
         <v>Key-CIRCU-88</v>
       </c>
       <c r="X88" s="27" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Y88" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z88" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA88" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11393,19 +11391,19 @@
         <v>89</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>9</v>
@@ -11467,13 +11465,13 @@
         <v>Key-CIRCU-89</v>
       </c>
       <c r="X89" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Y89" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z89" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA89" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11485,19 +11483,19 @@
         <v>90</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>9</v>
@@ -11559,13 +11557,13 @@
         <v>Key-CIRCU-90</v>
       </c>
       <c r="X90" s="27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y90" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z90" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA90" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11577,19 +11575,19 @@
         <v>91</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>9</v>
@@ -11651,13 +11649,13 @@
         <v>Key-CIRCU-91</v>
       </c>
       <c r="X91" s="27" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Y91" s="26" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Z91" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA91" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11669,19 +11667,19 @@
         <v>92</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>9</v>
@@ -11743,13 +11741,13 @@
         <v>Key-CIRCU-92</v>
       </c>
       <c r="X92" s="27" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Y92" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z92" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA92" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11761,19 +11759,19 @@
         <v>93</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G93" s="7" t="s">
         <v>9</v>
@@ -11835,13 +11833,13 @@
         <v>Key-CIRCU-93</v>
       </c>
       <c r="X93" s="27" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="Y93" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z93" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA93" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11853,19 +11851,19 @@
         <v>94</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>9</v>
@@ -11927,13 +11925,13 @@
         <v>Key-CIRCU-94</v>
       </c>
       <c r="X94" s="27" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Y94" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z94" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA94" s="27" t="str">
         <f t="shared" si="24"/>
@@ -11945,19 +11943,19 @@
         <v>95</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G95" s="7" t="s">
         <v>9</v>
@@ -12019,13 +12017,13 @@
         <v>Key-CIRCU-95</v>
       </c>
       <c r="X95" s="27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Y95" s="26" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z95" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA95" s="27" t="str">
         <f t="shared" si="24"/>
@@ -12037,19 +12035,19 @@
         <v>96</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>192</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G96" s="7" t="s">
         <v>9</v>
@@ -12111,13 +12109,13 @@
         <v>Key-CIRCU-96</v>
       </c>
       <c r="X96" s="27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Y96" s="26" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Z96" s="50" t="s">
-        <v>345</v>
+        <v>592</v>
       </c>
       <c r="AA96" s="27" t="str">
         <f t="shared" si="24"/>
@@ -12129,19 +12127,19 @@
         <v>97</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>208</v>
       </c>
       <c r="F97" s="31" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>9</v>
@@ -12203,13 +12201,13 @@
         <v>Key-CIRCU-97</v>
       </c>
       <c r="X97" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y97" s="26" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Z97" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA97" s="27" t="str">
         <f t="shared" si="24"/>
@@ -12221,13 +12219,13 @@
         <v>98</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>208</v>
@@ -12295,13 +12293,13 @@
         <v>Key-CIRCU-98</v>
       </c>
       <c r="X98" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y98" s="26" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Z98" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA98" s="27" t="str">
         <f t="shared" ref="AA98:AA114" si="33">_xlfn.TRANSLATE(P98,"pt","en")</f>
@@ -12313,19 +12311,19 @@
         <v>99</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>208</v>
       </c>
       <c r="F99" s="31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>9</v>
@@ -12387,13 +12385,13 @@
         <v>Key-CIRCU-99</v>
       </c>
       <c r="X99" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y99" s="26" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Z99" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA99" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12405,13 +12403,13 @@
         <v>100</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>208</v>
@@ -12479,13 +12477,13 @@
         <v>Key-CIRCU-100</v>
       </c>
       <c r="X100" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y100" s="26" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Z100" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA100" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12497,13 +12495,13 @@
         <v>101</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>208</v>
@@ -12571,13 +12569,13 @@
         <v>Key-CIRCU-101</v>
       </c>
       <c r="X101" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y101" s="26" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Z101" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA101" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12589,19 +12587,19 @@
         <v>102</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>208</v>
       </c>
       <c r="F102" s="31" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G102" s="53" t="s">
         <v>9</v>
@@ -12663,13 +12661,13 @@
         <v>Key-CIRCU-102</v>
       </c>
       <c r="X102" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y102" s="26" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Z102" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA102" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12681,13 +12679,13 @@
         <v>103</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>208</v>
@@ -12755,13 +12753,13 @@
         <v>Key-CIRCU-103</v>
       </c>
       <c r="X103" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y103" s="26" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Z103" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA103" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12773,13 +12771,13 @@
         <v>104</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>208</v>
@@ -12847,13 +12845,13 @@
         <v>Key-CIRCU-104</v>
       </c>
       <c r="X104" s="27" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y104" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z104" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA104" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12865,13 +12863,13 @@
         <v>105</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>208</v>
@@ -12939,13 +12937,13 @@
         <v>Key-CIRCU-105</v>
       </c>
       <c r="X105" s="27" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="Y105" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z105" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA105" s="27" t="str">
         <f t="shared" si="33"/>
@@ -12957,13 +12955,13 @@
         <v>106</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>208</v>
@@ -13031,13 +13029,13 @@
         <v>Key-CIRCU-106</v>
       </c>
       <c r="X106" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Y106" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z106" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA106" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13049,13 +13047,13 @@
         <v>107</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>208</v>
@@ -13123,13 +13121,13 @@
         <v>Key-CIRCU-107</v>
       </c>
       <c r="X107" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y107" s="26" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Z107" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA107" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13141,13 +13139,13 @@
         <v>108</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>208</v>
@@ -13215,13 +13213,13 @@
         <v>Key-CIRCU-108</v>
       </c>
       <c r="X108" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y108" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Z108" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA108" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13233,13 +13231,13 @@
         <v>109</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>208</v>
@@ -13307,13 +13305,13 @@
         <v>Key-CIRCU-109</v>
       </c>
       <c r="X109" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y109" s="26" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Z109" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA109" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13325,19 +13323,19 @@
         <v>110</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G110" s="53" t="s">
         <v>9</v>
@@ -13399,13 +13397,13 @@
         <v>Key-CIRCU-110</v>
       </c>
       <c r="X110" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="Y110" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z110" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA110" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13417,19 +13415,19 @@
         <v>111</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G111" s="53" t="s">
         <v>9</v>
@@ -13491,13 +13489,13 @@
         <v>Key-CIRCU-111</v>
       </c>
       <c r="X111" s="27" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Y111" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z111" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA111" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13509,19 +13507,19 @@
         <v>112</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D112" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="F112" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="F112" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="G112" s="53" t="s">
         <v>9</v>
@@ -13583,13 +13581,13 @@
         <v>Key-CIRCU-112</v>
       </c>
       <c r="X112" s="27" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Y112" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z112" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA112" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13601,19 +13599,19 @@
         <v>113</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G113" s="53" t="s">
         <v>9</v>
@@ -13675,13 +13673,13 @@
         <v>Key-CIRCU-113</v>
       </c>
       <c r="X113" s="27" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="Y113" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z113" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA113" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13693,19 +13691,19 @@
         <v>114</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G114" s="53" t="s">
         <v>9</v>
@@ -13767,13 +13765,13 @@
         <v>Key-CIRCU-114</v>
       </c>
       <c r="X114" s="27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Y114" s="27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Z114" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA114" s="27" t="str">
         <f t="shared" si="33"/>
@@ -13785,19 +13783,19 @@
         <v>115</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E115" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>522</v>
       </c>
       <c r="G115" s="7" t="s">
         <v>9</v>
@@ -13831,10 +13829,10 @@
         <v>Acessibilidade</v>
       </c>
       <c r="P115" s="27" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q115" s="27" t="s">
         <v>518</v>
-      </c>
-      <c r="Q115" s="27" t="s">
-        <v>519</v>
       </c>
       <c r="R115" s="50" t="s">
         <v>9</v>
@@ -13859,16 +13857,16 @@
         <v>Key-CIRCU-115</v>
       </c>
       <c r="X115" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="Y115" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="Z115" s="50" t="s">
+        <v>515</v>
+      </c>
+      <c r="AA115" s="27" t="s">
         <v>516</v>
-      </c>
-      <c r="Y115" s="27" t="s">
-        <v>516</v>
-      </c>
-      <c r="Z115" s="50" t="s">
-        <v>516</v>
-      </c>
-      <c r="AA115" s="27" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="116" spans="1:27" s="51" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -13876,16 +13874,16 @@
         <v>116</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F116" s="31" t="s">
         <v>239</v>
@@ -13922,7 +13920,7 @@
         <v>Escada</v>
       </c>
       <c r="P116" s="27" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="Q116" s="27" t="str">
         <f>_xlfn.TRANSLATE(P116,"pt","es")</f>
@@ -13951,13 +13949,13 @@
         <v>Key-CIRCU-116</v>
       </c>
       <c r="X116" s="27" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y116" s="26" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Z116" s="50" t="s">
-        <v>345</v>
+        <v>591</v>
       </c>
       <c r="AA116" s="27" t="str">
         <f>_xlfn.TRANSLATE(P116,"pt","en")</f>
@@ -13969,16 +13967,16 @@
         <v>117</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F117" s="31" t="s">
         <v>202</v>
@@ -14015,7 +14013,7 @@
         <v>Elevador</v>
       </c>
       <c r="P117" s="27" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q117" s="27" t="str">
         <f>_xlfn.TRANSLATE(P117,"pt","es")</f>
@@ -14044,13 +14042,13 @@
         <v>Key-CIRCU-117</v>
       </c>
       <c r="X117" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y117" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z117" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA117" s="27" t="str">
         <f>_xlfn.TRANSLATE(P117,"pt","en")</f>
@@ -14062,19 +14060,19 @@
         <v>118</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F118" s="31" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G118" s="7" t="s">
         <v>9</v>
@@ -14108,7 +14106,7 @@
         <v>Plataforma</v>
       </c>
       <c r="P118" s="27" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="Q118" s="27" t="str">
         <f>_xlfn.TRANSLATE(P118,"pt","es")</f>
@@ -14137,13 +14135,13 @@
         <v>Key-CIRCU-118</v>
       </c>
       <c r="X118" s="27" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="Y118" s="26" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Z118" s="50" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AA118" s="27" t="str">
         <f>_xlfn.TRANSLATE(P118,"pt","en")</f>
@@ -14155,16 +14153,16 @@
         <v>119</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F119" s="31" t="s">
         <v>209</v>
@@ -14201,7 +14199,7 @@
         <v>Rampa</v>
       </c>
       <c r="P119" s="27" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q119" s="27" t="str">
         <f>_xlfn.TRANSLATE(P119,"pt","es")</f>
@@ -14230,13 +14228,13 @@
         <v>Key-CIRCU-119</v>
       </c>
       <c r="X119" s="27" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Y119" s="26" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Z119" s="50" t="s">
-        <v>345</v>
+        <v>593</v>
       </c>
       <c r="AA119" s="27" t="str">
         <f>_xlfn.TRANSLATE(P119,"pt","en")</f>
@@ -14248,75 +14246,75 @@
     <sortCondition ref="E1:E119"/>
   </sortState>
   <conditionalFormatting sqref="A2:B119 D69:E119">
-    <cfRule type="cellIs" dxfId="22" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:E2 P2:Q3 Y2:XFD3 D3:E3 C3:C119 V5:V115 P14:Q115 Y14:XFD115">
-    <cfRule type="cellIs" dxfId="21" priority="40" operator="equal">
+  <conditionalFormatting sqref="C2:E2 P2:Q3 Y2:XFD3 D3:E3 C3:C119 V5:V115 P14:Q115 Y115:XFD115 Y14:Y114 AA14:XFD114">
+    <cfRule type="cellIs" dxfId="20" priority="40" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D5:E9">
-    <cfRule type="cellIs" dxfId="20" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E63:E68 D66:D68">
-    <cfRule type="cellIs" dxfId="19" priority="43" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="43" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L116:Q119 S116:V119">
-    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P6:Q7 Y6:Y7 AA6:XFD7 D47:E65">
-    <cfRule type="cellIs" dxfId="16" priority="118" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="118" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V3">
-    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y118">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y116:Z116">
-    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
+  <conditionalFormatting sqref="Y116">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y119:Z119">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+  <conditionalFormatting sqref="Y119">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="cellIs" dxfId="11" priority="117" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="117" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA4:AA5">
-    <cfRule type="cellIs" dxfId="10" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="36" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA8:AA12 D10:D46 E10:E52">
-    <cfRule type="cellIs" dxfId="9" priority="70" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="70" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA116:XFD119">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14532,7 +14530,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14607,22 +14605,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="5" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="3" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14765,7 +14763,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="62" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C2" s="61" t="s">
         <v>230</v>
@@ -14798,7 +14796,7 @@
         <v>78</v>
       </c>
       <c r="M2" s="64" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N2" s="63" t="s">
         <v>9</v>
@@ -14860,7 +14858,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="62" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C3" s="61" t="s">
         <v>220</v>
@@ -14893,7 +14891,7 @@
         <v>78</v>
       </c>
       <c r="M3" s="64" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N3" s="63" t="s">
         <v>9</v>
@@ -14955,7 +14953,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="62" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C4" s="61" t="s">
         <v>282</v>
@@ -14988,7 +14986,7 @@
         <v>78</v>
       </c>
       <c r="M4" s="64" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N4" s="63" t="s">
         <v>9</v>
@@ -15050,7 +15048,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C5" s="61" t="s">
         <v>255</v>
@@ -15083,7 +15081,7 @@
         <v>78</v>
       </c>
       <c r="M5" s="64" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="N5" s="63" t="s">
         <v>9</v>
@@ -15145,10 +15143,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C6" s="61" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D6" s="58" t="s">
         <v>9</v>
@@ -15178,19 +15176,19 @@
         <v>78</v>
       </c>
       <c r="M6" s="64" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="N6" s="63" t="s">
         <v>79</v>
       </c>
       <c r="O6" s="64" t="s">
+        <v>577</v>
+      </c>
+      <c r="P6" s="63" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q6" s="64" t="s">
         <v>578</v>
-      </c>
-      <c r="P6" s="63" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q6" s="64" t="s">
-        <v>579</v>
       </c>
       <c r="R6" s="63" t="s">
         <v>9</v>
@@ -15240,16 +15238,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C7" s="61" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F7" s="58" t="s">
         <v>9</v>
@@ -15273,19 +15271,19 @@
         <v>78</v>
       </c>
       <c r="M7" s="64" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N7" s="63" t="s">
         <v>79</v>
       </c>
       <c r="O7" s="64" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="P7" s="63" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q7" s="64" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="R7" s="63" t="s">
         <v>9</v>
@@ -15335,7 +15333,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C8" s="61" t="s">
         <v>239</v>
@@ -15344,13 +15342,13 @@
         <v>106</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G8" s="59" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H8" s="58" t="s">
         <v>9</v>
@@ -15368,37 +15366,37 @@
         <v>78</v>
       </c>
       <c r="M8" s="64" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="N8" s="63" t="s">
         <v>79</v>
       </c>
       <c r="O8" s="64" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="P8" s="63" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q8" s="64" t="s">
         <v>523</v>
       </c>
-      <c r="Q8" s="64" t="s">
-        <v>524</v>
-      </c>
       <c r="R8" s="63" t="s">
+        <v>525</v>
+      </c>
+      <c r="S8" s="64" t="s">
+        <v>528</v>
+      </c>
+      <c r="T8" s="63" t="s">
         <v>526</v>
       </c>
-      <c r="S8" s="64" t="s">
+      <c r="U8" s="64" t="s">
         <v>529</v>
       </c>
-      <c r="T8" s="63" t="s">
+      <c r="V8" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="U8" s="64" t="s">
-        <v>530</v>
-      </c>
-      <c r="V8" s="63" t="s">
-        <v>528</v>
-      </c>
       <c r="W8" s="64" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="X8" s="63" t="s">
         <v>9</v>
@@ -15430,7 +15428,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C9" s="61" t="s">
         <v>239</v>
@@ -15439,13 +15437,13 @@
         <v>106</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F9" s="58" t="s">
+        <v>587</v>
+      </c>
+      <c r="G9" s="59" t="s">
         <v>588</v>
-      </c>
-      <c r="G9" s="59" t="s">
-        <v>589</v>
       </c>
       <c r="H9" s="58" t="s">
         <v>9</v>
@@ -15463,37 +15461,37 @@
         <v>78</v>
       </c>
       <c r="M9" s="64" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="N9" s="63" t="s">
         <v>79</v>
       </c>
       <c r="O9" s="64" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="P9" s="63" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q9" s="64" t="s">
+        <v>524</v>
+      </c>
+      <c r="R9" s="63" t="s">
         <v>525</v>
       </c>
-      <c r="R9" s="63" t="s">
+      <c r="S9" s="64" t="s">
+        <v>528</v>
+      </c>
+      <c r="T9" s="63" t="s">
         <v>526</v>
       </c>
-      <c r="S9" s="64" t="s">
+      <c r="U9" s="64" t="s">
         <v>529</v>
       </c>
-      <c r="T9" s="63" t="s">
+      <c r="V9" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="U9" s="64" t="s">
-        <v>530</v>
-      </c>
-      <c r="V9" s="63" t="s">
-        <v>528</v>
-      </c>
       <c r="W9" s="64" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="X9" s="63" t="s">
         <v>9</v>
@@ -15525,7 +15523,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="62" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C10" s="61" t="s">
         <v>209</v>
@@ -15534,13 +15532,13 @@
         <v>106</v>
       </c>
       <c r="E10" s="59" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G10" s="59" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H10" s="58" t="s">
         <v>9</v>
@@ -15558,58 +15556,58 @@
         <v>78</v>
       </c>
       <c r="M10" s="64" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="N10" s="63" t="s">
         <v>79</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="P10" s="63" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="Q10" s="64" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="R10" s="63" t="s">
+        <v>525</v>
+      </c>
+      <c r="S10" s="64" t="s">
+        <v>531</v>
+      </c>
+      <c r="T10" s="63" t="s">
         <v>526</v>
       </c>
-      <c r="S10" s="64" t="s">
-        <v>532</v>
-      </c>
-      <c r="T10" s="63" t="s">
+      <c r="U10" s="64" t="s">
+        <v>530</v>
+      </c>
+      <c r="V10" s="63" t="s">
         <v>527</v>
       </c>
-      <c r="U10" s="64" t="s">
-        <v>531</v>
-      </c>
-      <c r="V10" s="63" t="s">
-        <v>528</v>
-      </c>
       <c r="W10" s="64" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="X10" s="63" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="Y10" s="66">
         <v>5</v>
       </c>
       <c r="Z10" s="63" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AA10" s="66">
         <v>5</v>
       </c>
       <c r="AB10" s="63" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="AC10" s="66">
         <v>1.2</v>
       </c>
       <c r="AD10" s="63" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AE10" s="66">
         <v>1.2</v>

--- a/Versão5/ARQ/Ontologia_Circulacao.xlsx
+++ b/Versão5/ARQ/Ontologia_Circulacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A2DEF4-9F7B-4461-8AB0-62529E5923FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A21ECED-69EE-48B3-B1DE-284CCF25B07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2858" uniqueCount="709">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1824,9 +1824,6 @@
     <t>Layout - Nodos</t>
   </si>
   <si>
-    <t>Documental</t>
-  </si>
-  <si>
     <t>[ OST_LayoutNodes ]</t>
   </si>
   <si>
@@ -1854,9 +1851,6 @@
     <t>Trajetos</t>
   </si>
   <si>
-    <t>[ OST_PathOfTravelLines : PATH_OF_TRAVEL_FROM_ROOM :  PATH_OF_TRAVEL_TO_ROOM : CURVE_ELEM_LENGTH ]</t>
-  </si>
-  <si>
     <t>Ramp slope value</t>
   </si>
   <si>
@@ -2179,6 +2173,33 @@
   </si>
   <si>
     <t>Código ABNT</t>
+  </si>
+  <si>
+    <t>[ PATH_OF_TRAVEL_FROM_ROOM :  PATH_OF_TRAVEL_TO_ROOM : CURVE_ELEM_LENGTH ]</t>
+  </si>
+  <si>
+    <t>[ OST_PathOfTravelLines ]</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
@@ -2276,7 +2297,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2403,6 +2424,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="8">
     <border>
@@ -2503,7 +2530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2683,11 +2710,54 @@
     <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="25">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2750,14 +2820,6 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3510,7 +3572,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46253.629699537036</v>
+        <v>46258.590519212965</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>172</v>
@@ -3591,7 +3653,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
-  <dimension ref="A1:AC120"/>
+  <dimension ref="A1:AC121"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="42" bestFit="1" customWidth="1"/>
@@ -3614,7 +3676,7 @@
     <col min="23" max="23" width="7" style="40" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="9.28515625" style="40" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="52.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="55.7109375" style="40" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="21.140625" style="40" customWidth="1"/>
     <col min="28" max="28" width="8.28515625" style="40" customWidth="1"/>
     <col min="29" max="29" width="10.42578125" style="46" bestFit="1" customWidth="1"/>
@@ -3698,16 +3760,16 @@
         <v>167</v>
       </c>
       <c r="Z1" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="AA1" s="33" t="s">
+        <v>695</v>
+      </c>
+      <c r="AB1" s="33" t="s">
+        <v>698</v>
+      </c>
+      <c r="AC1" s="49" t="s">
         <v>699</v>
-      </c>
-      <c r="AA1" s="33" t="s">
-        <v>697</v>
-      </c>
-      <c r="AB1" s="33" t="s">
-        <v>700</v>
-      </c>
-      <c r="AC1" s="49" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3767,7 +3829,7 @@
         <v>505</v>
       </c>
       <c r="R2" s="27" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="S2" s="45" t="s">
         <v>9</v>
@@ -3795,13 +3857,13 @@
         <v>9</v>
       </c>
       <c r="Z2" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA2" s="27" t="s">
         <v>9</v>
       </c>
       <c r="AB2" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC2" s="27" t="s">
         <v>9</v>
@@ -3864,7 +3926,7 @@
         <v>440</v>
       </c>
       <c r="R3" s="27" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="S3" s="45" t="s">
         <v>9</v>
@@ -3892,13 +3954,13 @@
         <v>549</v>
       </c>
       <c r="Z3" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA3" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB3" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC3" s="45" t="s">
         <v>441</v>
@@ -3961,7 +4023,7 @@
         <v>196</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="S4" s="45" t="s">
         <v>9</v>
@@ -3989,13 +4051,13 @@
         <v>549</v>
       </c>
       <c r="Z4" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA4" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB4" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC4" s="45" t="s">
         <v>441</v>
@@ -4058,7 +4120,7 @@
         <v>444</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="S5" s="45" t="s">
         <v>9</v>
@@ -4086,13 +4148,13 @@
         <v>549</v>
       </c>
       <c r="Z5" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA5" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB5" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC5" s="45" t="s">
         <v>441</v>
@@ -4155,7 +4217,7 @@
         <v>447</v>
       </c>
       <c r="R6" s="27" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="S6" s="45" t="s">
         <v>9</v>
@@ -4183,13 +4245,13 @@
         <v>549</v>
       </c>
       <c r="Z6" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA6" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB6" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC6" s="45" t="s">
         <v>441</v>
@@ -4252,7 +4314,7 @@
         <v>199</v>
       </c>
       <c r="R7" s="27" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="S7" s="45" t="s">
         <v>9</v>
@@ -4280,13 +4342,13 @@
         <v>549</v>
       </c>
       <c r="Z7" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA7" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB7" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC7" s="45" t="s">
         <v>441</v>
@@ -4349,7 +4411,7 @@
         <v>448</v>
       </c>
       <c r="R8" s="27" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="S8" s="45" t="s">
         <v>9</v>
@@ -4377,13 +4439,13 @@
         <v>549</v>
       </c>
       <c r="Z8" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA8" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB8" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC8" s="45" t="s">
         <v>450</v>
@@ -4446,7 +4508,7 @@
         <v>453</v>
       </c>
       <c r="R9" s="27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="S9" s="45" t="s">
         <v>9</v>
@@ -4474,13 +4536,13 @@
         <v>549</v>
       </c>
       <c r="Z9" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA9" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB9" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC9" s="45" t="s">
         <v>450</v>
@@ -4543,7 +4605,7 @@
         <v>456</v>
       </c>
       <c r="R10" s="27" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="S10" s="45" t="s">
         <v>9</v>
@@ -4571,13 +4633,13 @@
         <v>549</v>
       </c>
       <c r="Z10" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA10" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB10" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC10" s="45" t="s">
         <v>450</v>
@@ -4640,7 +4702,7 @@
         <v>459</v>
       </c>
       <c r="R11" s="27" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="S11" s="45" t="s">
         <v>9</v>
@@ -4668,13 +4730,13 @@
         <v>460</v>
       </c>
       <c r="Z11" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA11" s="26" t="s">
         <v>461</v>
       </c>
       <c r="AB11" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC11" s="45" t="s">
         <v>462</v>
@@ -4737,7 +4799,7 @@
         <v>153</v>
       </c>
       <c r="R12" s="27" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="S12" s="45" t="s">
         <v>9</v>
@@ -4765,13 +4827,13 @@
         <v>380</v>
       </c>
       <c r="Z12" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA12" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB12" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC12" s="45" t="s">
         <v>578</v>
@@ -4834,7 +4896,7 @@
         <v>164</v>
       </c>
       <c r="R13" s="27" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="S13" s="45" t="s">
         <v>9</v>
@@ -4862,13 +4924,13 @@
         <v>381</v>
       </c>
       <c r="Z13" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA13" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB13" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC13" s="45" t="s">
         <v>578</v>
@@ -4931,7 +4993,7 @@
         <v>155</v>
       </c>
       <c r="R14" s="27" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="S14" s="45" t="s">
         <v>9</v>
@@ -4959,13 +5021,13 @@
         <v>383</v>
       </c>
       <c r="Z14" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA14" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB14" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC14" s="45" t="s">
         <v>578</v>
@@ -5028,7 +5090,7 @@
         <v>156</v>
       </c>
       <c r="R15" s="27" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S15" s="45" t="s">
         <v>9</v>
@@ -5056,13 +5118,13 @@
         <v>384</v>
       </c>
       <c r="Z15" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA15" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB15" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC15" s="45" t="s">
         <v>578</v>
@@ -5125,7 +5187,7 @@
         <v>157</v>
       </c>
       <c r="R16" s="27" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="S16" s="45" t="s">
         <v>9</v>
@@ -5153,13 +5215,13 @@
         <v>385</v>
       </c>
       <c r="Z16" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA16" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB16" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC16" s="45" t="s">
         <v>578</v>
@@ -5222,7 +5284,7 @@
         <v>163</v>
       </c>
       <c r="R17" s="27" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="S17" s="45" t="s">
         <v>9</v>
@@ -5250,13 +5312,13 @@
         <v>387</v>
       </c>
       <c r="Z17" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA17" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB17" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC17" s="45" t="s">
         <v>578</v>
@@ -5319,7 +5381,7 @@
         <v>158</v>
       </c>
       <c r="R18" s="27" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="S18" s="45" t="s">
         <v>9</v>
@@ -5347,13 +5409,13 @@
         <v>388</v>
       </c>
       <c r="Z18" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA18" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB18" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC18" s="45" t="s">
         <v>578</v>
@@ -5416,7 +5478,7 @@
         <v>159</v>
       </c>
       <c r="R19" s="27" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="S19" s="45" t="s">
         <v>9</v>
@@ -5444,13 +5506,13 @@
         <v>389</v>
       </c>
       <c r="Z19" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA19" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB19" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC19" s="45" t="s">
         <v>578</v>
@@ -5513,7 +5575,7 @@
         <v>160</v>
       </c>
       <c r="R20" s="27" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="S20" s="45" t="s">
         <v>9</v>
@@ -5541,13 +5603,13 @@
         <v>390</v>
       </c>
       <c r="Z20" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA20" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB20" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC20" s="45" t="s">
         <v>578</v>
@@ -5610,7 +5672,7 @@
         <v>161</v>
       </c>
       <c r="R21" s="27" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="S21" s="45" t="s">
         <v>9</v>
@@ -5638,13 +5700,13 @@
         <v>391</v>
       </c>
       <c r="Z21" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA21" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB21" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC21" s="45" t="s">
         <v>578</v>
@@ -5707,7 +5769,7 @@
         <v>317</v>
       </c>
       <c r="R22" s="27" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="S22" s="45" t="s">
         <v>9</v>
@@ -5735,13 +5797,13 @@
         <v>392</v>
       </c>
       <c r="Z22" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA22" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB22" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC22" s="45" t="s">
         <v>578</v>
@@ -5804,7 +5866,7 @@
         <v>320</v>
       </c>
       <c r="R23" s="27" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="S23" s="45" t="s">
         <v>9</v>
@@ -5832,13 +5894,13 @@
         <v>394</v>
       </c>
       <c r="Z23" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA23" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB23" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC23" s="45" t="s">
         <v>578</v>
@@ -5901,7 +5963,7 @@
         <v>323</v>
       </c>
       <c r="R24" s="27" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="S24" s="45" t="s">
         <v>9</v>
@@ -5929,13 +5991,13 @@
         <v>393</v>
       </c>
       <c r="Z24" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA24" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB24" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC24" s="45" t="s">
         <v>578</v>
@@ -5998,7 +6060,7 @@
         <v>326</v>
       </c>
       <c r="R25" s="27" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="S25" s="45" t="s">
         <v>9</v>
@@ -6026,13 +6088,13 @@
         <v>395</v>
       </c>
       <c r="Z25" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA25" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB25" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC25" s="45" t="s">
         <v>578</v>
@@ -6095,7 +6157,7 @@
         <v>233</v>
       </c>
       <c r="R26" s="27" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S26" s="45" t="s">
         <v>9</v>
@@ -6123,13 +6185,13 @@
         <v>364</v>
       </c>
       <c r="Z26" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA26" s="26" t="s">
         <v>418</v>
       </c>
       <c r="AB26" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC26" s="45" t="s">
         <v>578</v>
@@ -6192,7 +6254,7 @@
         <v>240</v>
       </c>
       <c r="R27" s="27" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="S27" s="45" t="s">
         <v>9</v>
@@ -6220,13 +6282,13 @@
         <v>364</v>
       </c>
       <c r="Z27" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA27" s="26" t="s">
         <v>425</v>
       </c>
       <c r="AB27" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC27" s="45" t="s">
         <v>578</v>
@@ -6289,7 +6351,7 @@
         <v>243</v>
       </c>
       <c r="R28" s="27" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="S28" s="45" t="s">
         <v>9</v>
@@ -6317,13 +6379,13 @@
         <v>364</v>
       </c>
       <c r="Z28" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA28" s="26" t="s">
         <v>426</v>
       </c>
       <c r="AB28" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC28" s="45" t="s">
         <v>578</v>
@@ -6386,7 +6448,7 @@
         <v>246</v>
       </c>
       <c r="R29" s="27" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="S29" s="45" t="s">
         <v>9</v>
@@ -6414,13 +6476,13 @@
         <v>364</v>
       </c>
       <c r="Z29" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA29" s="26" t="s">
         <v>427</v>
       </c>
       <c r="AB29" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC29" s="45" t="s">
         <v>578</v>
@@ -6483,7 +6545,7 @@
         <v>98</v>
       </c>
       <c r="R30" s="27" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="S30" s="45" t="s">
         <v>9</v>
@@ -6511,13 +6573,13 @@
         <v>364</v>
       </c>
       <c r="Z30" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA30" s="26" t="s">
         <v>428</v>
       </c>
       <c r="AB30" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC30" s="45" t="s">
         <v>578</v>
@@ -6580,7 +6642,7 @@
         <v>249</v>
       </c>
       <c r="R31" s="27" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="S31" s="45" t="s">
         <v>9</v>
@@ -6608,13 +6670,13 @@
         <v>364</v>
       </c>
       <c r="Z31" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA31" s="26" t="s">
         <v>429</v>
       </c>
       <c r="AB31" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC31" s="45" t="s">
         <v>578</v>
@@ -6677,7 +6739,7 @@
         <v>252</v>
       </c>
       <c r="R32" s="27" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="S32" s="45" t="s">
         <v>9</v>
@@ -6705,13 +6767,13 @@
         <v>364</v>
       </c>
       <c r="Z32" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA32" s="26" t="s">
         <v>403</v>
       </c>
       <c r="AB32" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC32" s="45" t="s">
         <v>578</v>
@@ -6774,7 +6836,7 @@
         <v>255</v>
       </c>
       <c r="R33" s="27" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="S33" s="45" t="s">
         <v>9</v>
@@ -6802,13 +6864,13 @@
         <v>364</v>
       </c>
       <c r="Z33" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA33" s="26" t="s">
         <v>430</v>
       </c>
       <c r="AB33" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC33" s="45" t="s">
         <v>578</v>
@@ -6871,7 +6933,7 @@
         <v>258</v>
       </c>
       <c r="R34" s="27" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="S34" s="45" t="s">
         <v>9</v>
@@ -6899,13 +6961,13 @@
         <v>364</v>
       </c>
       <c r="Z34" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA34" s="26" t="s">
         <v>404</v>
       </c>
       <c r="AB34" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC34" s="45" t="s">
         <v>578</v>
@@ -6968,7 +7030,7 @@
         <v>261</v>
       </c>
       <c r="R35" s="27" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="S35" s="45" t="s">
         <v>9</v>
@@ -6996,13 +7058,13 @@
         <v>364</v>
       </c>
       <c r="Z35" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA35" s="26" t="s">
         <v>431</v>
       </c>
       <c r="AB35" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC35" s="45" t="s">
         <v>578</v>
@@ -7065,7 +7127,7 @@
         <v>264</v>
       </c>
       <c r="R36" s="27" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="S36" s="45" t="s">
         <v>9</v>
@@ -7093,13 +7155,13 @@
         <v>364</v>
       </c>
       <c r="Z36" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA36" s="26" t="s">
         <v>432</v>
       </c>
       <c r="AB36" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC36" s="45" t="s">
         <v>578</v>
@@ -7162,7 +7224,7 @@
         <v>267</v>
       </c>
       <c r="R37" s="27" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="S37" s="45" t="s">
         <v>9</v>
@@ -7190,13 +7252,13 @@
         <v>364</v>
       </c>
       <c r="Z37" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA37" s="26" t="s">
         <v>433</v>
       </c>
       <c r="AB37" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC37" s="45" t="s">
         <v>578</v>
@@ -7259,7 +7321,7 @@
         <v>270</v>
       </c>
       <c r="R38" s="27" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="S38" s="45" t="s">
         <v>9</v>
@@ -7287,13 +7349,13 @@
         <v>364</v>
       </c>
       <c r="Z38" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA38" s="26" t="s">
         <v>434</v>
       </c>
       <c r="AB38" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC38" s="45" t="s">
         <v>578</v>
@@ -7356,7 +7418,7 @@
         <v>273</v>
       </c>
       <c r="R39" s="27" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="S39" s="45" t="s">
         <v>9</v>
@@ -7384,13 +7446,13 @@
         <v>364</v>
       </c>
       <c r="Z39" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA39" s="26" t="s">
         <v>435</v>
       </c>
       <c r="AB39" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC39" s="45" t="s">
         <v>578</v>
@@ -7453,7 +7515,7 @@
         <v>276</v>
       </c>
       <c r="R40" s="27" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="S40" s="45" t="s">
         <v>9</v>
@@ -7481,13 +7543,13 @@
         <v>364</v>
       </c>
       <c r="Z40" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA40" s="26" t="s">
         <v>436</v>
       </c>
       <c r="AB40" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC40" s="45" t="s">
         <v>578</v>
@@ -7550,7 +7612,7 @@
         <v>279</v>
       </c>
       <c r="R41" s="27" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="S41" s="45" t="s">
         <v>9</v>
@@ -7578,13 +7640,13 @@
         <v>364</v>
       </c>
       <c r="Z41" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA41" s="26" t="s">
         <v>437</v>
       </c>
       <c r="AB41" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC41" s="45" t="s">
         <v>578</v>
@@ -7647,7 +7709,7 @@
         <v>281</v>
       </c>
       <c r="R42" s="27" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="S42" s="45" t="s">
         <v>9</v>
@@ -7675,13 +7737,13 @@
         <v>374</v>
       </c>
       <c r="Z42" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA42" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB42" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC42" s="45" t="s">
         <v>578</v>
@@ -7744,7 +7806,7 @@
         <v>150</v>
       </c>
       <c r="R43" s="27" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="S43" s="45" t="s">
         <v>9</v>
@@ -7772,13 +7834,13 @@
         <v>377</v>
       </c>
       <c r="Z43" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA43" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB43" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC43" s="45" t="s">
         <v>578</v>
@@ -7841,7 +7903,7 @@
         <v>151</v>
       </c>
       <c r="R44" s="27" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="S44" s="45" t="s">
         <v>9</v>
@@ -7869,13 +7931,13 @@
         <v>378</v>
       </c>
       <c r="Z44" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA44" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB44" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC44" s="45" t="s">
         <v>578</v>
@@ -7938,7 +8000,7 @@
         <v>152</v>
       </c>
       <c r="R45" s="27" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="S45" s="45" t="s">
         <v>9</v>
@@ -7966,13 +8028,13 @@
         <v>379</v>
       </c>
       <c r="Z45" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA45" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB45" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC45" s="45" t="s">
         <v>578</v>
@@ -8035,7 +8097,7 @@
         <v>162</v>
       </c>
       <c r="R46" s="27" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="S46" s="45" t="s">
         <v>9</v>
@@ -8063,13 +8125,13 @@
         <v>386</v>
       </c>
       <c r="Z46" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA46" s="27" t="s">
         <v>419</v>
       </c>
       <c r="AB46" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC46" s="45" t="s">
         <v>578</v>
@@ -8132,7 +8194,7 @@
         <v>93</v>
       </c>
       <c r="R47" s="27" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="S47" s="45" t="s">
         <v>9</v>
@@ -8160,13 +8222,13 @@
         <v>364</v>
       </c>
       <c r="Z47" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA47" s="26" t="s">
         <v>421</v>
       </c>
       <c r="AB47" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC47" s="45" t="s">
         <v>578</v>
@@ -8229,7 +8291,7 @@
         <v>94</v>
       </c>
       <c r="R48" s="27" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="S48" s="45" t="s">
         <v>9</v>
@@ -8257,13 +8319,13 @@
         <v>364</v>
       </c>
       <c r="Z48" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA48" s="26" t="s">
         <v>420</v>
       </c>
       <c r="AB48" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC48" s="45" t="s">
         <v>578</v>
@@ -8326,7 +8388,7 @@
         <v>95</v>
       </c>
       <c r="R49" s="27" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="S49" s="45" t="s">
         <v>9</v>
@@ -8354,13 +8416,13 @@
         <v>364</v>
       </c>
       <c r="Z49" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA49" s="26" t="s">
         <v>422</v>
       </c>
       <c r="AB49" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC49" s="45" t="s">
         <v>578</v>
@@ -8423,7 +8485,7 @@
         <v>96</v>
       </c>
       <c r="R50" s="27" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="S50" s="45" t="s">
         <v>9</v>
@@ -8451,13 +8513,13 @@
         <v>364</v>
       </c>
       <c r="Z50" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA50" s="26" t="s">
         <v>423</v>
       </c>
       <c r="AB50" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC50" s="45" t="s">
         <v>578</v>
@@ -8520,7 +8582,7 @@
         <v>97</v>
       </c>
       <c r="R51" s="27" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="S51" s="45" t="s">
         <v>9</v>
@@ -8548,13 +8610,13 @@
         <v>364</v>
       </c>
       <c r="Z51" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA51" s="26" t="s">
         <v>424</v>
       </c>
       <c r="AB51" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC51" s="45" t="s">
         <v>578</v>
@@ -8617,7 +8679,7 @@
         <v>165</v>
       </c>
       <c r="R52" s="27" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S52" s="45" t="s">
         <v>9</v>
@@ -8645,13 +8707,13 @@
         <v>375</v>
       </c>
       <c r="Z52" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA52" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB52" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC52" s="45" t="s">
         <v>578</v>
@@ -8714,7 +8776,7 @@
         <v>166</v>
       </c>
       <c r="R53" s="27" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="S53" s="45" t="s">
         <v>9</v>
@@ -8742,13 +8804,13 @@
         <v>376</v>
       </c>
       <c r="Z53" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA53" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB53" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC53" s="45" t="s">
         <v>578</v>
@@ -8811,7 +8873,7 @@
         <v>328</v>
       </c>
       <c r="R54" s="27" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="S54" s="45" t="s">
         <v>9</v>
@@ -8839,13 +8901,13 @@
         <v>396</v>
       </c>
       <c r="Z54" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA54" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB54" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC54" s="45" t="s">
         <v>578</v>
@@ -8908,7 +8970,7 @@
         <v>154</v>
       </c>
       <c r="R55" s="27" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="S55" s="45" t="s">
         <v>9</v>
@@ -8936,13 +8998,13 @@
         <v>382</v>
       </c>
       <c r="Z55" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA55" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB55" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC55" s="45" t="s">
         <v>578</v>
@@ -9005,7 +9067,7 @@
         <v>155</v>
       </c>
       <c r="R56" s="27" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="S56" s="45" t="s">
         <v>9</v>
@@ -9033,13 +9095,13 @@
         <v>383</v>
       </c>
       <c r="Z56" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA56" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB56" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC56" s="45" t="s">
         <v>578</v>
@@ -9102,7 +9164,7 @@
         <v>334</v>
       </c>
       <c r="R57" s="27" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="S57" s="45" t="s">
         <v>9</v>
@@ -9130,13 +9192,13 @@
         <v>399</v>
       </c>
       <c r="Z57" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA57" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB57" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC57" s="45" t="s">
         <v>578</v>
@@ -9199,7 +9261,7 @@
         <v>330</v>
       </c>
       <c r="R58" s="27" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="S58" s="45" t="s">
         <v>9</v>
@@ -9227,13 +9289,13 @@
         <v>397</v>
       </c>
       <c r="Z58" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA58" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB58" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC58" s="45" t="s">
         <v>578</v>
@@ -9296,7 +9358,7 @@
         <v>336</v>
       </c>
       <c r="R59" s="27" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="S59" s="45" t="s">
         <v>9</v>
@@ -9324,13 +9386,13 @@
         <v>400</v>
       </c>
       <c r="Z59" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA59" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB59" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC59" s="45" t="s">
         <v>578</v>
@@ -9393,7 +9455,7 @@
         <v>332</v>
       </c>
       <c r="R60" s="27" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="S60" s="45" t="s">
         <v>9</v>
@@ -9421,13 +9483,13 @@
         <v>398</v>
       </c>
       <c r="Z60" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA60" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB60" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC60" s="45" t="s">
         <v>578</v>
@@ -9490,7 +9552,7 @@
         <v>105</v>
       </c>
       <c r="R61" s="27" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="S61" s="45" t="s">
         <v>9</v>
@@ -9518,13 +9580,13 @@
         <v>342</v>
       </c>
       <c r="Z61" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA61" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB61" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC61" s="45" t="s">
         <v>579</v>
@@ -9587,7 +9649,7 @@
         <v>135</v>
       </c>
       <c r="R62" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="S62" s="45" t="s">
         <v>9</v>
@@ -9615,13 +9677,13 @@
         <v>343</v>
       </c>
       <c r="Z62" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA62" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB62" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC62" s="45" t="s">
         <v>579</v>
@@ -9684,7 +9746,7 @@
         <v>135</v>
       </c>
       <c r="R63" s="27" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="S63" s="45" t="s">
         <v>9</v>
@@ -9712,13 +9774,13 @@
         <v>344</v>
       </c>
       <c r="Z63" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA63" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB63" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC63" s="45" t="s">
         <v>579</v>
@@ -9781,7 +9843,7 @@
         <v>136</v>
       </c>
       <c r="R64" s="27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S64" s="45" t="s">
         <v>9</v>
@@ -9809,13 +9871,13 @@
         <v>346</v>
       </c>
       <c r="Z64" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA64" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB64" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC64" s="45" t="s">
         <v>579</v>
@@ -9878,7 +9940,7 @@
         <v>136</v>
       </c>
       <c r="R65" s="27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S65" s="45" t="s">
         <v>9</v>
@@ -9906,13 +9968,13 @@
         <v>345</v>
       </c>
       <c r="Z65" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA65" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB65" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC65" s="45" t="s">
         <v>579</v>
@@ -9975,7 +10037,7 @@
         <v>147</v>
       </c>
       <c r="R66" s="27" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="S66" s="45" t="s">
         <v>9</v>
@@ -9996,20 +10058,20 @@
         <v>43</v>
       </c>
       <c r="X66" s="43" t="str">
-        <f t="shared" ref="X66:X120" si="30">CONCATENATE("Key-CIRCU-",A66)</f>
+        <f t="shared" ref="X66:X121" si="30">CONCATENATE("Key-CIRCU-",A66)</f>
         <v>Key-CIRCU-66</v>
       </c>
       <c r="Y66" s="27" t="s">
         <v>338</v>
       </c>
       <c r="Z66" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA66" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB66" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC66" s="45" t="s">
         <v>579</v>
@@ -10072,7 +10134,7 @@
         <v>149</v>
       </c>
       <c r="R67" s="27" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="S67" s="45" t="s">
         <v>9</v>
@@ -10100,13 +10162,13 @@
         <v>347</v>
       </c>
       <c r="Z67" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA67" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB67" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC67" s="45" t="s">
         <v>579</v>
@@ -10169,7 +10231,7 @@
         <v>136</v>
       </c>
       <c r="R68" s="27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S68" s="45" t="s">
         <v>9</v>
@@ -10197,13 +10259,13 @@
         <v>349</v>
       </c>
       <c r="Z68" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA68" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB68" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC68" s="45" t="s">
         <v>579</v>
@@ -10266,7 +10328,7 @@
         <v>136</v>
       </c>
       <c r="R69" s="27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S69" s="45" t="s">
         <v>9</v>
@@ -10294,13 +10356,13 @@
         <v>348</v>
       </c>
       <c r="Z69" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA69" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB69" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC69" s="45" t="s">
         <v>579</v>
@@ -10363,7 +10425,7 @@
         <v>137</v>
       </c>
       <c r="R70" s="27" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="S70" s="45" t="s">
         <v>9</v>
@@ -10391,13 +10453,13 @@
         <v>350</v>
       </c>
       <c r="Z70" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA70" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB70" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC70" s="45" t="s">
         <v>579</v>
@@ -10460,7 +10522,7 @@
         <v>146</v>
       </c>
       <c r="R71" s="27" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="S71" s="45" t="s">
         <v>9</v>
@@ -10488,13 +10550,13 @@
         <v>351</v>
       </c>
       <c r="Z71" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA71" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB71" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC71" s="45" t="s">
         <v>579</v>
@@ -10557,7 +10619,7 @@
         <v>180</v>
       </c>
       <c r="R72" s="27" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="S72" s="45" t="s">
         <v>9</v>
@@ -10585,13 +10647,13 @@
         <v>337</v>
       </c>
       <c r="Z72" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA72" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB72" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC72" s="45" t="s">
         <v>579</v>
@@ -10654,7 +10716,7 @@
         <v>184</v>
       </c>
       <c r="R73" s="27" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="S73" s="45" t="s">
         <v>9</v>
@@ -10682,13 +10744,13 @@
         <v>339</v>
       </c>
       <c r="Z73" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA73" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB73" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC73" s="45" t="s">
         <v>579</v>
@@ -10751,7 +10813,7 @@
         <v>187</v>
       </c>
       <c r="R74" s="27" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="S74" s="45" t="s">
         <v>9</v>
@@ -10779,13 +10841,13 @@
         <v>340</v>
       </c>
       <c r="Z74" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA74" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB74" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC74" s="45" t="s">
         <v>579</v>
@@ -10848,7 +10910,7 @@
         <v>190</v>
       </c>
       <c r="R75" s="27" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="S75" s="45" t="s">
         <v>9</v>
@@ -10876,13 +10938,13 @@
         <v>341</v>
       </c>
       <c r="Z75" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA75" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB75" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC75" s="45" t="s">
         <v>579</v>
@@ -10945,7 +11007,7 @@
         <v>180</v>
       </c>
       <c r="R76" s="27" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="S76" s="45" t="s">
         <v>9</v>
@@ -10973,13 +11035,13 @@
         <v>337</v>
       </c>
       <c r="Z76" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA76" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB76" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC76" s="45" t="s">
         <v>579</v>
@@ -11042,7 +11104,7 @@
         <v>184</v>
       </c>
       <c r="R77" s="27" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="S77" s="45" t="s">
         <v>9</v>
@@ -11070,13 +11132,13 @@
         <v>339</v>
       </c>
       <c r="Z77" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA77" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB77" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC77" s="45" t="s">
         <v>579</v>
@@ -11139,7 +11201,7 @@
         <v>187</v>
       </c>
       <c r="R78" s="27" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="S78" s="45" t="s">
         <v>9</v>
@@ -11167,13 +11229,13 @@
         <v>340</v>
       </c>
       <c r="Z78" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA78" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB78" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC78" s="45" t="s">
         <v>579</v>
@@ -11236,7 +11298,7 @@
         <v>190</v>
       </c>
       <c r="R79" s="27" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="S79" s="45" t="s">
         <v>9</v>
@@ -11264,13 +11326,13 @@
         <v>341</v>
       </c>
       <c r="Z79" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA79" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB79" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC79" s="45" t="s">
         <v>579</v>
@@ -11333,7 +11395,7 @@
         <v>180</v>
       </c>
       <c r="R80" s="27" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="S80" s="45" t="s">
         <v>9</v>
@@ -11361,13 +11423,13 @@
         <v>337</v>
       </c>
       <c r="Z80" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA80" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB80" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC80" s="45" t="s">
         <v>579</v>
@@ -11430,7 +11492,7 @@
         <v>184</v>
       </c>
       <c r="R81" s="27" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="S81" s="45" t="s">
         <v>9</v>
@@ -11458,13 +11520,13 @@
         <v>339</v>
       </c>
       <c r="Z81" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA81" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB81" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC81" s="45" t="s">
         <v>579</v>
@@ -11527,7 +11589,7 @@
         <v>187</v>
       </c>
       <c r="R82" s="27" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="S82" s="45" t="s">
         <v>9</v>
@@ -11555,13 +11617,13 @@
         <v>340</v>
       </c>
       <c r="Z82" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA82" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB82" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC82" s="45" t="s">
         <v>579</v>
@@ -11624,7 +11686,7 @@
         <v>190</v>
       </c>
       <c r="R83" s="27" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="S83" s="45" t="s">
         <v>9</v>
@@ -11652,13 +11714,13 @@
         <v>341</v>
       </c>
       <c r="Z83" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA83" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB83" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC83" s="45" t="s">
         <v>579</v>
@@ -11721,7 +11783,7 @@
         <v>138</v>
       </c>
       <c r="R84" s="27" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="S84" s="45" t="s">
         <v>9</v>
@@ -11749,13 +11811,13 @@
         <v>352</v>
       </c>
       <c r="Z84" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA84" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB84" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC84" s="45" t="s">
         <v>579</v>
@@ -11818,7 +11880,7 @@
         <v>139</v>
       </c>
       <c r="R85" s="27" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="S85" s="45" t="s">
         <v>9</v>
@@ -11846,13 +11908,13 @@
         <v>353</v>
       </c>
       <c r="Z85" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA85" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB85" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC85" s="45" t="s">
         <v>579</v>
@@ -11915,7 +11977,7 @@
         <v>136</v>
       </c>
       <c r="R86" s="27" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="S86" s="45" t="s">
         <v>9</v>
@@ -11943,13 +12005,13 @@
         <v>354</v>
       </c>
       <c r="Z86" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA86" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB86" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC86" s="45" t="s">
         <v>579</v>
@@ -12012,7 +12074,7 @@
         <v>140</v>
       </c>
       <c r="R87" s="27" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="S87" s="45" t="s">
         <v>9</v>
@@ -12040,13 +12102,13 @@
         <v>355</v>
       </c>
       <c r="Z87" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA87" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB87" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC87" s="45" t="s">
         <v>579</v>
@@ -12109,7 +12171,7 @@
         <v>141</v>
       </c>
       <c r="R88" s="27" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="S88" s="45" t="s">
         <v>9</v>
@@ -12137,13 +12199,13 @@
         <v>356</v>
       </c>
       <c r="Z88" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA88" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB88" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC88" s="45" t="s">
         <v>579</v>
@@ -12206,7 +12268,7 @@
         <v>142</v>
       </c>
       <c r="R89" s="27" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="S89" s="45" t="s">
         <v>9</v>
@@ -12234,13 +12296,13 @@
         <v>357</v>
       </c>
       <c r="Z89" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA89" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB89" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC89" s="45" t="s">
         <v>579</v>
@@ -12303,7 +12365,7 @@
         <v>143</v>
       </c>
       <c r="R90" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="S90" s="45" t="s">
         <v>9</v>
@@ -12331,13 +12393,13 @@
         <v>358</v>
       </c>
       <c r="Z90" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA90" s="26" t="s">
         <v>416</v>
       </c>
       <c r="AB90" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC90" s="45" t="s">
         <v>579</v>
@@ -12400,7 +12462,7 @@
         <v>144</v>
       </c>
       <c r="R91" s="27" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="S91" s="45" t="s">
         <v>9</v>
@@ -12428,13 +12490,13 @@
         <v>359</v>
       </c>
       <c r="Z91" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA91" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB91" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC91" s="45" t="s">
         <v>579</v>
@@ -12497,7 +12559,7 @@
         <v>145</v>
       </c>
       <c r="R92" s="27" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="S92" s="45" t="s">
         <v>9</v>
@@ -12525,13 +12587,13 @@
         <v>361</v>
       </c>
       <c r="Z92" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA92" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB92" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC92" s="45" t="s">
         <v>579</v>
@@ -12594,7 +12656,7 @@
         <v>146</v>
       </c>
       <c r="R93" s="27" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="S93" s="45" t="s">
         <v>9</v>
@@ -12622,13 +12684,13 @@
         <v>362</v>
       </c>
       <c r="Z93" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA93" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB93" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC93" s="45" t="s">
         <v>579</v>
@@ -12691,7 +12753,7 @@
         <v>147</v>
       </c>
       <c r="R94" s="27" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="S94" s="45" t="s">
         <v>9</v>
@@ -12719,13 +12781,13 @@
         <v>360</v>
       </c>
       <c r="Z94" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA94" s="26" t="s">
         <v>415</v>
       </c>
       <c r="AB94" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC94" s="45" t="s">
         <v>579</v>
@@ -12788,7 +12850,7 @@
         <v>148</v>
       </c>
       <c r="R95" s="27" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="S95" s="45" t="s">
         <v>9</v>
@@ -12816,13 +12878,13 @@
         <v>363</v>
       </c>
       <c r="Z95" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA95" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AB95" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC95" s="45" t="s">
         <v>579</v>
@@ -12885,7 +12947,7 @@
         <v>203</v>
       </c>
       <c r="R96" s="27" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="S96" s="45" t="s">
         <v>9</v>
@@ -12913,13 +12975,13 @@
         <v>365</v>
       </c>
       <c r="Z96" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA96" s="26" t="s">
         <v>407</v>
       </c>
       <c r="AB96" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC96" s="45" t="s">
         <v>580</v>
@@ -12982,7 +13044,7 @@
         <v>224</v>
       </c>
       <c r="R97" s="27" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="S97" s="45" t="s">
         <v>9</v>
@@ -13010,13 +13072,13 @@
         <v>365</v>
       </c>
       <c r="Z97" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA97" s="26" t="s">
         <v>412</v>
       </c>
       <c r="AB97" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC97" s="45" t="s">
         <v>580</v>
@@ -13079,7 +13141,7 @@
         <v>226</v>
       </c>
       <c r="R98" s="27" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="S98" s="45" t="s">
         <v>9</v>
@@ -13107,13 +13169,13 @@
         <v>365</v>
       </c>
       <c r="Z98" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA98" s="26" t="s">
         <v>417</v>
       </c>
       <c r="AB98" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC98" s="45" t="s">
         <v>580</v>
@@ -13176,7 +13238,7 @@
         <v>214</v>
       </c>
       <c r="R99" s="27" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="S99" s="45" t="s">
         <v>9</v>
@@ -13204,13 +13266,13 @@
         <v>365</v>
       </c>
       <c r="Z99" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA99" s="26" t="s">
         <v>410</v>
       </c>
       <c r="AB99" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC99" s="45" t="s">
         <v>580</v>
@@ -13273,7 +13335,7 @@
         <v>217</v>
       </c>
       <c r="R100" s="27" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="S100" s="45" t="s">
         <v>9</v>
@@ -13301,13 +13363,13 @@
         <v>365</v>
       </c>
       <c r="Z100" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA100" s="26" t="s">
         <v>414</v>
       </c>
       <c r="AB100" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC100" s="45" t="s">
         <v>580</v>
@@ -13370,7 +13432,7 @@
         <v>219</v>
       </c>
       <c r="R101" s="27" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="S101" s="45" t="s">
         <v>9</v>
@@ -13398,13 +13460,13 @@
         <v>365</v>
       </c>
       <c r="Z101" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA101" s="26" t="s">
         <v>411</v>
       </c>
       <c r="AB101" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC101" s="45" t="s">
         <v>580</v>
@@ -13467,7 +13529,7 @@
         <v>221</v>
       </c>
       <c r="R102" s="27" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="S102" s="45" t="s">
         <v>9</v>
@@ -13495,13 +13557,13 @@
         <v>365</v>
       </c>
       <c r="Z102" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA102" s="26" t="s">
         <v>413</v>
       </c>
       <c r="AB102" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC102" s="45" t="s">
         <v>580</v>
@@ -13564,7 +13626,7 @@
         <v>110</v>
       </c>
       <c r="R103" s="27" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="S103" s="45" t="s">
         <v>9</v>
@@ -13592,13 +13654,13 @@
         <v>366</v>
       </c>
       <c r="Z103" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA103" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB103" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC103" s="45" t="s">
         <v>580</v>
@@ -13661,7 +13723,7 @@
         <v>111</v>
       </c>
       <c r="R104" s="27" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="S104" s="45" t="s">
         <v>9</v>
@@ -13689,13 +13751,13 @@
         <v>369</v>
       </c>
       <c r="Z104" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA104" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB104" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC104" s="45" t="s">
         <v>580</v>
@@ -13758,7 +13820,7 @@
         <v>119</v>
       </c>
       <c r="R105" s="27" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="S105" s="45" t="s">
         <v>9</v>
@@ -13786,13 +13848,13 @@
         <v>367</v>
       </c>
       <c r="Z105" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA105" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB105" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC105" s="45" t="s">
         <v>580</v>
@@ -13855,7 +13917,7 @@
         <v>206</v>
       </c>
       <c r="R106" s="27" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="S106" s="45" t="s">
         <v>9</v>
@@ -13883,13 +13945,13 @@
         <v>365</v>
       </c>
       <c r="Z106" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA106" s="26" t="s">
         <v>408</v>
       </c>
       <c r="AB106" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC106" s="45" t="s">
         <v>580</v>
@@ -13952,7 +14014,7 @@
         <v>209</v>
       </c>
       <c r="R107" s="27" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="S107" s="45" t="s">
         <v>9</v>
@@ -13980,13 +14042,13 @@
         <v>365</v>
       </c>
       <c r="Z107" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA107" s="26" t="s">
         <v>402</v>
       </c>
       <c r="AB107" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC107" s="45" t="s">
         <v>580</v>
@@ -14049,7 +14111,7 @@
         <v>211</v>
       </c>
       <c r="R108" s="27" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="S108" s="45" t="s">
         <v>9</v>
@@ -14077,13 +14139,13 @@
         <v>365</v>
       </c>
       <c r="Z108" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA108" s="26" t="s">
         <v>409</v>
       </c>
       <c r="AB108" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC108" s="45" t="s">
         <v>580</v>
@@ -14146,7 +14208,7 @@
         <v>115</v>
       </c>
       <c r="R109" s="27" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="S109" s="45" t="s">
         <v>9</v>
@@ -14174,13 +14236,13 @@
         <v>373</v>
       </c>
       <c r="Z109" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA109" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB109" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC109" s="45" t="s">
         <v>580</v>
@@ -14243,7 +14305,7 @@
         <v>116</v>
       </c>
       <c r="R110" s="27" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="S110" s="45" t="s">
         <v>9</v>
@@ -14271,13 +14333,13 @@
         <v>370</v>
       </c>
       <c r="Z110" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA110" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB110" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC110" s="45" t="s">
         <v>580</v>
@@ -14340,7 +14402,7 @@
         <v>118</v>
       </c>
       <c r="R111" s="27" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="S111" s="45" t="s">
         <v>9</v>
@@ -14368,13 +14430,13 @@
         <v>368</v>
       </c>
       <c r="Z111" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA111" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB111" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC111" s="45" t="s">
         <v>580</v>
@@ -14437,7 +14499,7 @@
         <v>117</v>
       </c>
       <c r="R112" s="27" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="S112" s="45" t="s">
         <v>9</v>
@@ -14465,13 +14527,13 @@
         <v>372</v>
       </c>
       <c r="Z112" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA112" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB112" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC112" s="45" t="s">
         <v>580</v>
@@ -14534,7 +14596,7 @@
         <v>114</v>
       </c>
       <c r="R113" s="27" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="S113" s="45" t="s">
         <v>9</v>
@@ -14562,13 +14624,13 @@
         <v>371</v>
       </c>
       <c r="Z113" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA113" s="27" t="s">
         <v>405</v>
       </c>
       <c r="AB113" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC113" s="45" t="s">
         <v>580</v>
@@ -14585,10 +14647,10 @@
         <v>527</v>
       </c>
       <c r="D114" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>591</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>592</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>581</v>
@@ -14632,7 +14694,7 @@
         <v>Distribución - Nodos</v>
       </c>
       <c r="R114" s="27" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="S114" s="45" t="s">
         <v>9</v>
@@ -14649,24 +14711,24 @@
         <f t="shared" si="35"/>
         <v>Trajetos</v>
       </c>
-      <c r="W114" s="45" t="s">
-        <v>583</v>
+      <c r="W114" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="X114" s="43" t="str">
         <f t="shared" si="30"/>
         <v>Key-CIRCU-114</v>
       </c>
       <c r="Y114" s="65" t="s">
+        <v>583</v>
+      </c>
+      <c r="Z114" s="27" t="s">
+        <v>696</v>
+      </c>
+      <c r="AA114" s="66" t="s">
         <v>584</v>
       </c>
-      <c r="Z114" s="27" t="s">
-        <v>698</v>
-      </c>
-      <c r="AA114" s="66" t="s">
-        <v>585</v>
-      </c>
       <c r="AB114" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC114" s="45" t="s">
         <v>9</v>
@@ -14683,13 +14745,13 @@
         <v>527</v>
       </c>
       <c r="D115" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="E115" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="F115" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="G115" s="47" t="s">
         <v>9</v>
@@ -14723,14 +14785,14 @@
         <v>Caminho Trajeto</v>
       </c>
       <c r="P115" s="64" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="Q115" s="45" t="str">
         <f t="shared" ref="Q115:Q116" si="38">_xlfn.TRANSLATE(P115,"pt","es")</f>
         <v>Distribución - Bases del camino</v>
       </c>
       <c r="R115" s="27" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="S115" s="45" t="s">
         <v>9</v>
@@ -14747,24 +14809,24 @@
         <f t="shared" si="39"/>
         <v>Trajetos</v>
       </c>
-      <c r="W115" s="45" t="s">
-        <v>583</v>
+      <c r="W115" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="X115" s="43" t="str">
         <f t="shared" si="30"/>
         <v>Key-CIRCU-115</v>
       </c>
       <c r="Y115" s="65" t="s">
-        <v>593</v>
+        <v>701</v>
       </c>
       <c r="Z115" s="27" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="AA115" s="66" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AB115" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC115" s="45" t="s">
         <v>9</v>
@@ -14781,13 +14843,13 @@
         <v>527</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>592</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="G116" s="47" t="s">
         <v>9</v>
@@ -14821,14 +14883,14 @@
         <v>Caminho Tubulação</v>
       </c>
       <c r="P116" s="64" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="Q116" s="45" t="str">
         <f t="shared" si="38"/>
         <v>Distribución - Bases de la tubería traídas</v>
       </c>
       <c r="R116" s="27" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="S116" s="45" t="s">
         <v>9</v>
@@ -14845,24 +14907,24 @@
         <f t="shared" si="39"/>
         <v>Trajetos</v>
       </c>
-      <c r="W116" s="45" t="s">
-        <v>583</v>
+      <c r="W116" s="27" t="s">
+        <v>43</v>
       </c>
       <c r="X116" s="43" t="str">
         <f t="shared" si="30"/>
         <v>Key-CIRCU-116</v>
       </c>
       <c r="Y116" s="65" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="Z116" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA116" s="66" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AB116" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC116" s="45" t="s">
         <v>9</v>
@@ -14926,13 +14988,13 @@
         <v>Escalera existente en el edificio.</v>
       </c>
       <c r="R117" s="27" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="S117" s="45" t="s">
         <v>9</v>
       </c>
       <c r="T117" s="45" t="str">
-        <f t="shared" ref="T117:V120" si="40">SUBSTITUTE(C117, ".", " ")</f>
+        <f t="shared" ref="T117:V121" si="40">SUBSTITUTE(C117, ".", " ")</f>
         <v>De Circulação</v>
       </c>
       <c r="U117" s="45" t="str">
@@ -14954,13 +15016,13 @@
         <v>364</v>
       </c>
       <c r="Z117" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA117" s="26" t="s">
         <v>418</v>
       </c>
       <c r="AB117" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC117" s="45" t="s">
         <v>578</v>
@@ -15024,7 +15086,7 @@
         <v>Ascensor existente en el edificio.</v>
       </c>
       <c r="R118" s="27" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="S118" s="45" t="s">
         <v>9</v>
@@ -15052,13 +15114,13 @@
         <v>549</v>
       </c>
       <c r="Z118" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA118" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB118" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC118" s="45" t="s">
         <v>450</v>
@@ -15122,7 +15184,7 @@
         <v>Plataforma elevadora en el edificio.</v>
       </c>
       <c r="R119" s="27" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="S119" s="45" t="s">
         <v>9</v>
@@ -15150,13 +15212,13 @@
         <v>549</v>
       </c>
       <c r="Z119" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA119" s="26" t="s">
         <v>406</v>
       </c>
       <c r="AB119" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC119" s="45" t="s">
         <v>450</v>
@@ -15220,7 +15282,7 @@
         <v>Rampa existente en el edificio.</v>
       </c>
       <c r="R120" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="S120" s="45" t="s">
         <v>9</v>
@@ -15248,16 +15310,113 @@
         <v>365</v>
       </c>
       <c r="Z120" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA120" s="26" t="s">
         <v>407</v>
       </c>
       <c r="AB120" s="27" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AC120" s="45" t="s">
         <v>580</v>
+      </c>
+    </row>
+    <row r="121" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="41">
+        <v>121</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C121" s="44" t="s">
+        <v>702</v>
+      </c>
+      <c r="D121" s="44" t="s">
+        <v>703</v>
+      </c>
+      <c r="E121" s="44" t="s">
+        <v>704</v>
+      </c>
+      <c r="F121" s="44" t="s">
+        <v>705</v>
+      </c>
+      <c r="G121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L121" s="32" t="str">
+        <f t="shared" ref="L121:O121" si="41">SUBSTITUTE(CONCATENATE("", C121), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M121" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N121" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="O121" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P121" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q121" s="27" t="s">
+        <v>707</v>
+      </c>
+      <c r="R121" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="S121" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="T121" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="U121" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V121" s="45" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="W121" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="X121" s="43" t="str">
+        <f t="shared" si="30"/>
+        <v>Key-CIRCU-121</v>
+      </c>
+      <c r="Y121" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z121" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA121" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB121" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC121" s="68" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15265,73 +15424,86 @@
     <sortCondition ref="E1:E120"/>
   </sortState>
   <conditionalFormatting sqref="B2:E2 P2:Q4 W2:W4">
-    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:E3 D4:E4">
-    <cfRule type="cellIs" dxfId="20" priority="54" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="57" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D47 E11:E53">
-    <cfRule type="cellIs" dxfId="19" priority="84" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="87" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E10">
-    <cfRule type="cellIs" dxfId="18" priority="52" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68:E116">
-    <cfRule type="cellIs" dxfId="17" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E67 D65:D67">
-    <cfRule type="cellIs" dxfId="16" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114:F116">
-    <cfRule type="duplicateValues" dxfId="15" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F117:F1048576 F1:F113">
-    <cfRule type="duplicateValues" dxfId="14" priority="20"/>
+  <conditionalFormatting sqref="F117:F120 F1:F113 F122:F1048576">
+    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L117:Q120 T117:W120">
-    <cfRule type="cellIs" dxfId="13" priority="26" operator="equal">
+  <conditionalFormatting sqref="L117:Q120 T117:V120">
+    <cfRule type="cellIs" dxfId="16" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q8 AA7:AA8">
-    <cfRule type="cellIs" dxfId="12" priority="132" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="135" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R120">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA117">
-    <cfRule type="cellIs" dxfId="10" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA119:AA120">
-    <cfRule type="cellIs" dxfId="9" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1">
-    <cfRule type="cellIs" dxfId="8" priority="131" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="134" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD4 A2:A120 AA3:AA4 AC3:AC4 B3:B113 C4:C113 W6:W113 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120">
-    <cfRule type="cellIs" dxfId="7" priority="25" operator="equal">
+  <conditionalFormatting sqref="AD2:XFD4 AA3:AA4 AC3:AC4 B3:B113 C4:C113 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120 A2:A121 W6:W121">
+    <cfRule type="cellIs" dxfId="0" priority="28" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B121">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R121">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15547,7 +15719,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15622,22 +15794,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Circulacao.xlsx
+++ b/Versão5/ARQ/Ontologia_Circulacao.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A21ECED-69EE-48B3-B1DE-284CCF25B07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597F5549-80F3-4F3A-A771-0EA087654512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -2723,41 +2723,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -2872,6 +2838,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2889,6 +2863,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -3370,14 +3362,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="1"/>
-    <col min="2" max="2" width="69.5703125" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.53515625" customWidth="1"/>
+    <col min="2" max="2" width="69.53515625" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>45</v>
       </c>
@@ -3388,7 +3380,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>47</v>
       </c>
@@ -3399,7 +3391,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>49</v>
       </c>
@@ -3410,7 +3402,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>50</v>
       </c>
@@ -3421,7 +3413,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>51</v>
       </c>
@@ -3433,7 +3425,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>52</v>
       </c>
@@ -3445,7 +3437,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>53</v>
       </c>
@@ -3456,7 +3448,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="35" t="s">
         <v>55</v>
       </c>
@@ -3467,7 +3459,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>56</v>
       </c>
@@ -3478,7 +3470,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>58</v>
       </c>
@@ -3489,7 +3481,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>60</v>
       </c>
@@ -3500,7 +3492,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -3511,7 +3503,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>62</v>
       </c>
@@ -3522,7 +3514,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>63</v>
       </c>
@@ -3533,7 +3525,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>64</v>
       </c>
@@ -3544,7 +3536,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>65</v>
       </c>
@@ -3555,7 +3547,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>66</v>
       </c>
@@ -3566,19 +3558,19 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46258.590519212965</v>
+        <v>46264.563293402774</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>68</v>
       </c>
@@ -3589,7 +3581,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>70</v>
       </c>
@@ -3600,7 +3592,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>71</v>
       </c>
@@ -3611,7 +3603,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3622,7 +3614,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3634,7 +3626,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>170</v>
       </c>
@@ -3654,36 +3646,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <dimension ref="A1:AC121"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="112.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="111.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="98.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.15234375" style="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.84375" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.15234375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.84375" style="40" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="112.84375" style="40" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="111.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="98.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.15234375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.69140625" style="40" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7" style="40" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="52.85546875" style="40" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="55.7109375" style="40" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.140625" style="40" customWidth="1"/>
-    <col min="28" max="28" width="8.28515625" style="40" customWidth="1"/>
-    <col min="29" max="29" width="10.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="40"/>
+    <col min="24" max="24" width="9.3046875" style="40" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="52.84375" style="40" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="55.69140625" style="40" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.15234375" style="40" customWidth="1"/>
+    <col min="28" max="28" width="8.3046875" style="40" customWidth="1"/>
+    <col min="29" max="29" width="10.3828125" style="46" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.15234375" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="63" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:29" s="63" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="60">
         <v>1</v>
       </c>
@@ -3772,7 +3764,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="41">
         <v>2</v>
       </c>
@@ -3869,7 +3861,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="41">
         <v>3</v>
       </c>
@@ -3966,7 +3958,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="41">
         <v>4</v>
       </c>
@@ -4063,7 +4055,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="41">
         <v>5</v>
       </c>
@@ -4160,7 +4152,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="41">
         <v>6</v>
       </c>
@@ -4257,7 +4249,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="41">
         <v>7</v>
       </c>
@@ -4354,7 +4346,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="41">
         <v>8</v>
       </c>
@@ -4451,7 +4443,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="41">
         <v>9</v>
       </c>
@@ -4548,7 +4540,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="41">
         <v>10</v>
       </c>
@@ -4645,7 +4637,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="41">
         <v>11</v>
       </c>
@@ -4742,7 +4734,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="41">
         <v>12</v>
       </c>
@@ -4839,7 +4831,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="41">
         <v>13</v>
       </c>
@@ -4936,7 +4928,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="41">
         <v>14</v>
       </c>
@@ -5033,7 +5025,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="41">
         <v>15</v>
       </c>
@@ -5130,7 +5122,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="41">
         <v>16</v>
       </c>
@@ -5227,7 +5219,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="41">
         <v>17</v>
       </c>
@@ -5324,7 +5316,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="41">
         <v>18</v>
       </c>
@@ -5421,7 +5413,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="41">
         <v>19</v>
       </c>
@@ -5518,7 +5510,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="41">
         <v>20</v>
       </c>
@@ -5615,7 +5607,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="41">
         <v>21</v>
       </c>
@@ -5712,7 +5704,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="41">
         <v>22</v>
       </c>
@@ -5809,7 +5801,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="41">
         <v>23</v>
       </c>
@@ -5906,7 +5898,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="41">
         <v>24</v>
       </c>
@@ -6003,7 +5995,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="41">
         <v>25</v>
       </c>
@@ -6100,7 +6092,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="41">
         <v>26</v>
       </c>
@@ -6197,7 +6189,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="41">
         <v>27</v>
       </c>
@@ -6294,7 +6286,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="41">
         <v>28</v>
       </c>
@@ -6391,7 +6383,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="41">
         <v>29</v>
       </c>
@@ -6488,7 +6480,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="41">
         <v>30</v>
       </c>
@@ -6585,7 +6577,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="41">
         <v>31</v>
       </c>
@@ -6682,7 +6674,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="41">
         <v>32</v>
       </c>
@@ -6779,7 +6771,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="41">
         <v>33</v>
       </c>
@@ -6876,7 +6868,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="41">
         <v>34</v>
       </c>
@@ -6973,7 +6965,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="41">
         <v>35</v>
       </c>
@@ -7070,7 +7062,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="41">
         <v>36</v>
       </c>
@@ -7167,7 +7159,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="41">
         <v>37</v>
       </c>
@@ -7264,7 +7256,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="41">
         <v>38</v>
       </c>
@@ -7361,7 +7353,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="41">
         <v>39</v>
       </c>
@@ -7458,7 +7450,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="41">
         <v>40</v>
       </c>
@@ -7555,7 +7547,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="41">
         <v>41</v>
       </c>
@@ -7652,7 +7644,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="41">
         <v>42</v>
       </c>
@@ -7749,7 +7741,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="41">
         <v>43</v>
       </c>
@@ -7846,7 +7838,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="41">
         <v>44</v>
       </c>
@@ -7943,7 +7935,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="41">
         <v>45</v>
       </c>
@@ -8040,7 +8032,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="41">
         <v>46</v>
       </c>
@@ -8137,7 +8129,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="41">
         <v>47</v>
       </c>
@@ -8234,7 +8226,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="41">
         <v>48</v>
       </c>
@@ -8331,7 +8323,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="41">
         <v>49</v>
       </c>
@@ -8428,7 +8420,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="41">
         <v>50</v>
       </c>
@@ -8525,7 +8517,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="41">
         <v>51</v>
       </c>
@@ -8622,7 +8614,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="41">
         <v>52</v>
       </c>
@@ -8719,7 +8711,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="41">
         <v>53</v>
       </c>
@@ -8816,7 +8808,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="41">
         <v>54</v>
       </c>
@@ -8913,7 +8905,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="41">
         <v>55</v>
       </c>
@@ -9010,7 +9002,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="41">
         <v>56</v>
       </c>
@@ -9107,7 +9099,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="41">
         <v>57</v>
       </c>
@@ -9204,7 +9196,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="41">
         <v>58</v>
       </c>
@@ -9301,7 +9293,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="41">
         <v>59</v>
       </c>
@@ -9398,7 +9390,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="41">
         <v>60</v>
       </c>
@@ -9495,7 +9487,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="41">
         <v>61</v>
       </c>
@@ -9592,7 +9584,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="41">
         <v>62</v>
       </c>
@@ -9689,7 +9681,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="41">
         <v>63</v>
       </c>
@@ -9786,7 +9778,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="41">
         <v>64</v>
       </c>
@@ -9883,7 +9875,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="41">
         <v>65</v>
       </c>
@@ -9980,7 +9972,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="41">
         <v>66</v>
       </c>
@@ -10077,7 +10069,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="41">
         <v>67</v>
       </c>
@@ -10174,7 +10166,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="41">
         <v>68</v>
       </c>
@@ -10271,7 +10263,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="41">
         <v>69</v>
       </c>
@@ -10368,7 +10360,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="41">
         <v>70</v>
       </c>
@@ -10465,7 +10457,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="41">
         <v>71</v>
       </c>
@@ -10562,7 +10554,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="41">
         <v>72</v>
       </c>
@@ -10659,7 +10651,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="41">
         <v>73</v>
       </c>
@@ -10756,7 +10748,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="41">
         <v>74</v>
       </c>
@@ -10853,7 +10845,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="41">
         <v>75</v>
       </c>
@@ -10950,7 +10942,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="41">
         <v>76</v>
       </c>
@@ -11047,7 +11039,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="41">
         <v>77</v>
       </c>
@@ -11144,7 +11136,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="41">
         <v>78</v>
       </c>
@@ -11241,7 +11233,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="41">
         <v>79</v>
       </c>
@@ -11338,7 +11330,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="41">
         <v>80</v>
       </c>
@@ -11435,7 +11427,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="41">
         <v>81</v>
       </c>
@@ -11532,7 +11524,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="41">
         <v>82</v>
       </c>
@@ -11629,7 +11621,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="41">
         <v>83</v>
       </c>
@@ -11726,7 +11718,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="41">
         <v>84</v>
       </c>
@@ -11823,7 +11815,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="41">
         <v>85</v>
       </c>
@@ -11920,7 +11912,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="41">
         <v>86</v>
       </c>
@@ -12017,7 +12009,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="41">
         <v>87</v>
       </c>
@@ -12114,7 +12106,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="41">
         <v>88</v>
       </c>
@@ -12211,7 +12203,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="41">
         <v>89</v>
       </c>
@@ -12308,7 +12300,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="41">
         <v>90</v>
       </c>
@@ -12405,7 +12397,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="41">
         <v>91</v>
       </c>
@@ -12502,7 +12494,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="41">
         <v>92</v>
       </c>
@@ -12599,7 +12591,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="41">
         <v>93</v>
       </c>
@@ -12696,7 +12688,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="41">
         <v>94</v>
       </c>
@@ -12793,7 +12785,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="41">
         <v>95</v>
       </c>
@@ -12890,7 +12882,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="41">
         <v>96</v>
       </c>
@@ -12987,7 +12979,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="41">
         <v>97</v>
       </c>
@@ -13084,7 +13076,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="41">
         <v>98</v>
       </c>
@@ -13181,7 +13173,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="41">
         <v>99</v>
       </c>
@@ -13278,7 +13270,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="41">
         <v>100</v>
       </c>
@@ -13375,7 +13367,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="41">
         <v>101</v>
       </c>
@@ -13472,7 +13464,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="41">
         <v>102</v>
       </c>
@@ -13569,7 +13561,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="41">
         <v>103</v>
       </c>
@@ -13666,7 +13658,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="41">
         <v>104</v>
       </c>
@@ -13763,7 +13755,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="41">
         <v>105</v>
       </c>
@@ -13860,7 +13852,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="41">
         <v>106</v>
       </c>
@@ -13957,7 +13949,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="41">
         <v>107</v>
       </c>
@@ -14054,7 +14046,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="41">
         <v>108</v>
       </c>
@@ -14151,7 +14143,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="41">
         <v>109</v>
       </c>
@@ -14248,7 +14240,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="41">
         <v>110</v>
       </c>
@@ -14345,7 +14337,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="41">
         <v>111</v>
       </c>
@@ -14442,7 +14434,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="41">
         <v>112</v>
       </c>
@@ -14539,7 +14531,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="41">
         <v>113</v>
       </c>
@@ -14636,7 +14628,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="114" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="41">
         <v>114</v>
       </c>
@@ -14734,7 +14726,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="41">
         <v>115</v>
       </c>
@@ -14832,7 +14824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="41">
         <v>116</v>
       </c>
@@ -14930,7 +14922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="41">
         <v>117</v>
       </c>
@@ -15028,7 +15020,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="118" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="41">
         <v>118</v>
       </c>
@@ -15126,7 +15118,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="119" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="41">
         <v>119</v>
       </c>
@@ -15224,7 +15216,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="120" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="41">
         <v>120</v>
       </c>
@@ -15322,7 +15314,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="121" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="41">
         <v>121</v>
       </c>
@@ -15333,10 +15325,10 @@
         <v>702</v>
       </c>
       <c r="D121" s="44" t="s">
+        <v>704</v>
+      </c>
+      <c r="E121" s="44" t="s">
         <v>703</v>
-      </c>
-      <c r="E121" s="44" t="s">
-        <v>704</v>
       </c>
       <c r="F121" s="44" t="s">
         <v>705</v>
@@ -15362,11 +15354,11 @@
       </c>
       <c r="M121" s="32" t="str">
         <f t="shared" si="41"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N121" s="32" t="str">
         <f t="shared" si="41"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O121" s="32" t="str">
         <f t="shared" si="41"/>
@@ -15390,11 +15382,11 @@
       </c>
       <c r="U121" s="27" t="str">
         <f t="shared" si="40"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V121" s="45" t="str">
         <f t="shared" si="40"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W121" s="27" t="s">
         <v>43</v>
@@ -15423,87 +15415,82 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AC120">
     <sortCondition ref="E1:E120"/>
   </sortState>
+  <conditionalFormatting sqref="B121">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:E2 P2:Q4 W2:W4">
-    <cfRule type="cellIs" dxfId="24" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:E3 D4:E4">
-    <cfRule type="cellIs" dxfId="23" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="57" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D47 E11:E53">
-    <cfRule type="cellIs" dxfId="22" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="87" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E10">
-    <cfRule type="cellIs" dxfId="21" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="55" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68:E116">
-    <cfRule type="cellIs" dxfId="20" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E67 D65:D67">
-    <cfRule type="cellIs" dxfId="19" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114:F116">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117:F120 F1:F113 F122:F1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L117:Q120 T117:V120">
-    <cfRule type="cellIs" dxfId="16" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="29" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q8 AA7:AA8">
-    <cfRule type="cellIs" dxfId="15" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="135" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R120">
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+  <conditionalFormatting sqref="R1:R121">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA117">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA119:AA120">
-    <cfRule type="cellIs" dxfId="12" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1">
-    <cfRule type="cellIs" dxfId="11" priority="134" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="134" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD4 AA3:AA4 AC3:AC4 B3:B113 C4:C113 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120 A2:A121 W6:W121">
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B121">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F121">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R121">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="AD2:XFD4 A2:A121 AA3:AA4 AC3:AC4 B3:B113 C4:C113 W6:W121 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120">
+    <cfRule type="cellIs" dxfId="7" priority="28" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15514,15 +15501,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -15587,7 +15574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -15652,7 +15639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -15719,7 +15706,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15734,15 +15721,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.15234375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="28">
         <v>0</v>
       </c>
@@ -15765,7 +15752,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="29">
         <v>2</v>
       </c>
@@ -15794,22 +15781,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="8" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15820,39 +15807,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56FE74A-92F3-4401-B3DB-ACCAA98B3F78}">
   <dimension ref="A1:AE10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="3.5703125" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.3046875" customWidth="1"/>
+    <col min="4" max="4" width="7.53515625" customWidth="1"/>
+    <col min="5" max="5" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.53515625" customWidth="1"/>
+    <col min="7" max="7" width="8.53515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="3.53515625" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.53515625" customWidth="1"/>
+    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.3046875" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.85546875" customWidth="1"/>
-    <col min="19" max="19" width="7.42578125" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" customWidth="1"/>
-    <col min="22" max="22" width="6.42578125" customWidth="1"/>
+    <col min="18" max="18" width="6.84375" customWidth="1"/>
+    <col min="19" max="19" width="7.3828125" customWidth="1"/>
+    <col min="20" max="20" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.69140625" customWidth="1"/>
+    <col min="22" max="22" width="6.3828125" customWidth="1"/>
     <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" customWidth="1"/>
+    <col min="24" max="24" width="8.69140625" customWidth="1"/>
     <col min="25" max="25" width="3" style="42" customWidth="1"/>
-    <col min="26" max="26" width="6.85546875" customWidth="1"/>
-    <col min="27" max="27" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" customWidth="1"/>
-    <col min="29" max="29" width="3.140625" style="42" customWidth="1"/>
-    <col min="30" max="30" width="5.5703125" customWidth="1"/>
+    <col min="26" max="26" width="6.84375" customWidth="1"/>
+    <col min="27" max="27" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" customWidth="1"/>
+    <col min="29" max="29" width="3.15234375" style="42" customWidth="1"/>
+    <col min="30" max="30" width="5.53515625" customWidth="1"/>
     <col min="31" max="31" width="3" style="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -15947,7 +15934,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A2" s="53">
         <v>2</v>
       </c>
@@ -16042,7 +16029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A3" s="53">
         <v>3</v>
       </c>
@@ -16137,7 +16124,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A4" s="53">
         <v>4</v>
       </c>
@@ -16232,7 +16219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A5" s="53">
         <v>5</v>
       </c>
@@ -16327,7 +16314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A6" s="53">
         <v>6</v>
       </c>
@@ -16422,7 +16409,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A7" s="53">
         <v>7</v>
       </c>
@@ -16517,7 +16504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A8" s="53">
         <v>8</v>
       </c>
@@ -16612,7 +16599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A9" s="53">
         <v>9</v>
       </c>
@@ -16707,7 +16694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
       <c r="A10" s="53">
         <v>10</v>
       </c>

--- a/Versão5/ARQ/Ontologia_Circulacao.xlsx
+++ b/Versão5/ARQ/Ontologia_Circulacao.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597F5549-80F3-4F3A-A771-0EA087654512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DF2EA9-9CED-49E2-853A-5A06303034BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2858" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="726">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2163,9 +2163,6 @@
     <t>Classe Ifc</t>
   </si>
   <si>
-    <t>[ - ]</t>
-  </si>
-  <si>
     <t>Parametro Rvt</t>
   </si>
   <si>
@@ -2190,16 +2187,70 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Interdisciplinar</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
   </si>
 </sst>
 </file>
@@ -2530,7 +2581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2719,11 +2770,50 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2786,14 +2876,6 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3362,14 +3444,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.53515625" customWidth="1"/>
-    <col min="2" max="2" width="69.53515625" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="39" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" customWidth="1"/>
+    <col min="2" max="2" width="69.5703125" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>45</v>
       </c>
@@ -3380,7 +3462,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>47</v>
       </c>
@@ -3391,7 +3473,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>49</v>
       </c>
@@ -3402,7 +3484,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>50</v>
       </c>
@@ -3413,7 +3495,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>51</v>
       </c>
@@ -3425,7 +3507,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>52</v>
       </c>
@@ -3437,7 +3519,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>53</v>
       </c>
@@ -3448,7 +3530,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
         <v>55</v>
       </c>
@@ -3459,7 +3541,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>56</v>
       </c>
@@ -3470,7 +3552,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>58</v>
       </c>
@@ -3481,7 +3563,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>60</v>
       </c>
@@ -3492,7 +3574,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>61</v>
       </c>
@@ -3503,7 +3585,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>62</v>
       </c>
@@ -3514,7 +3596,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>63</v>
       </c>
@@ -3525,7 +3607,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>64</v>
       </c>
@@ -3536,7 +3618,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>65</v>
       </c>
@@ -3547,7 +3629,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>66</v>
       </c>
@@ -3558,19 +3640,19 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46264.563293402774</v>
+        <v>46268.51357638889</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>68</v>
       </c>
@@ -3581,7 +3663,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>70</v>
       </c>
@@ -3592,7 +3674,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>71</v>
       </c>
@@ -3603,7 +3685,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>72</v>
       </c>
@@ -3614,7 +3696,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>73</v>
       </c>
@@ -3626,7 +3708,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" s="36" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>170</v>
       </c>
@@ -3645,37 +3727,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
-  <dimension ref="A1:AC121"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC125"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.15234375" style="42" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.84375" style="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.15234375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="13.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.84375" style="40" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="112.84375" style="40" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="111.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="98.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="13.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7" style="40" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.3046875" style="40" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="52.84375" style="40" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="55.69140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.15234375" style="40" customWidth="1"/>
-    <col min="28" max="28" width="8.3046875" style="40" customWidth="1"/>
-    <col min="29" max="29" width="10.3828125" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.15234375" style="40"/>
+    <col min="1" max="1" width="3.140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="112.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="111.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="98.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.28515625" style="40" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="27.5703125" style="40" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="55.7109375" style="40" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="21.140625" style="40" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="63" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" s="63" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="60">
         <v>1</v>
       </c>
@@ -3752,19 +3834,19 @@
         <v>167</v>
       </c>
       <c r="Z1" s="33" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AA1" s="33" t="s">
         <v>695</v>
       </c>
       <c r="AB1" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="AC1" s="49" t="s">
         <v>698</v>
       </c>
-      <c r="AC1" s="49" t="s">
-        <v>699</v>
-      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="41">
         <v>2</v>
       </c>
@@ -3848,20 +3930,20 @@
       <c r="Y2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="27" t="s">
-        <v>696</v>
+      <c r="Z2" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AB2" s="27" t="s">
-        <v>696</v>
+      <c r="AB2" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC2" s="27" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>3</v>
       </c>
@@ -3945,20 +4027,20 @@
       <c r="Y3" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z3" s="27" t="s">
-        <v>696</v>
+      <c r="Z3" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA3" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB3" s="27" t="s">
-        <v>696</v>
+      <c r="AB3" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC3" s="45" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>4</v>
       </c>
@@ -4042,20 +4124,20 @@
       <c r="Y4" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z4" s="27" t="s">
-        <v>696</v>
+      <c r="Z4" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA4" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB4" s="27" t="s">
-        <v>696</v>
+      <c r="AB4" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC4" s="45" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>5</v>
       </c>
@@ -4139,20 +4221,20 @@
       <c r="Y5" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z5" s="27" t="s">
-        <v>696</v>
+      <c r="Z5" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB5" s="27" t="s">
-        <v>696</v>
+      <c r="AB5" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC5" s="45" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>6</v>
       </c>
@@ -4236,20 +4318,20 @@
       <c r="Y6" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z6" s="27" t="s">
-        <v>696</v>
+      <c r="Z6" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB6" s="27" t="s">
-        <v>696</v>
+      <c r="AB6" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC6" s="45" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>7</v>
       </c>
@@ -4333,20 +4415,20 @@
       <c r="Y7" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z7" s="27" t="s">
-        <v>696</v>
+      <c r="Z7" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA7" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB7" s="27" t="s">
-        <v>696</v>
+      <c r="AB7" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC7" s="45" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>8</v>
       </c>
@@ -4430,20 +4512,20 @@
       <c r="Y8" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z8" s="27" t="s">
-        <v>696</v>
+      <c r="Z8" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA8" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB8" s="27" t="s">
-        <v>696</v>
+      <c r="AB8" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC8" s="45" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>9</v>
       </c>
@@ -4527,20 +4609,20 @@
       <c r="Y9" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z9" s="27" t="s">
-        <v>696</v>
+      <c r="Z9" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA9" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB9" s="27" t="s">
-        <v>696</v>
+      <c r="AB9" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC9" s="45" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41">
         <v>10</v>
       </c>
@@ -4624,20 +4706,20 @@
       <c r="Y10" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z10" s="27" t="s">
-        <v>696</v>
+      <c r="Z10" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA10" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB10" s="27" t="s">
-        <v>696</v>
+      <c r="AB10" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC10" s="45" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41">
         <v>11</v>
       </c>
@@ -4721,20 +4803,20 @@
       <c r="Y11" s="27" t="s">
         <v>460</v>
       </c>
-      <c r="Z11" s="27" t="s">
-        <v>696</v>
+      <c r="Z11" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA11" s="26" t="s">
         <v>461</v>
       </c>
-      <c r="AB11" s="27" t="s">
-        <v>696</v>
+      <c r="AB11" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC11" s="45" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>12</v>
       </c>
@@ -4818,20 +4900,20 @@
       <c r="Y12" s="27" t="s">
         <v>380</v>
       </c>
-      <c r="Z12" s="27" t="s">
-        <v>696</v>
+      <c r="Z12" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA12" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB12" s="27" t="s">
-        <v>696</v>
+      <c r="AB12" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC12" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41">
         <v>13</v>
       </c>
@@ -4915,20 +4997,20 @@
       <c r="Y13" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="Z13" s="27" t="s">
-        <v>696</v>
+      <c r="Z13" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA13" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB13" s="27" t="s">
-        <v>696</v>
+      <c r="AB13" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC13" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41">
         <v>14</v>
       </c>
@@ -5012,20 +5094,20 @@
       <c r="Y14" s="27" t="s">
         <v>383</v>
       </c>
-      <c r="Z14" s="27" t="s">
-        <v>696</v>
+      <c r="Z14" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA14" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB14" s="27" t="s">
-        <v>696</v>
+      <c r="AB14" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC14" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41">
         <v>15</v>
       </c>
@@ -5109,20 +5191,20 @@
       <c r="Y15" s="27" t="s">
         <v>384</v>
       </c>
-      <c r="Z15" s="27" t="s">
-        <v>696</v>
+      <c r="Z15" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA15" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB15" s="27" t="s">
-        <v>696</v>
+      <c r="AB15" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC15" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>16</v>
       </c>
@@ -5206,20 +5288,20 @@
       <c r="Y16" s="27" t="s">
         <v>385</v>
       </c>
-      <c r="Z16" s="27" t="s">
-        <v>696</v>
+      <c r="Z16" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA16" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB16" s="27" t="s">
-        <v>696</v>
+      <c r="AB16" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC16" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="41">
         <v>17</v>
       </c>
@@ -5303,20 +5385,20 @@
       <c r="Y17" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="Z17" s="27" t="s">
-        <v>696</v>
+      <c r="Z17" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA17" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB17" s="27" t="s">
-        <v>696</v>
+      <c r="AB17" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC17" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>18</v>
       </c>
@@ -5400,20 +5482,20 @@
       <c r="Y18" s="27" t="s">
         <v>388</v>
       </c>
-      <c r="Z18" s="27" t="s">
-        <v>696</v>
+      <c r="Z18" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA18" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB18" s="27" t="s">
-        <v>696</v>
+      <c r="AB18" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC18" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>19</v>
       </c>
@@ -5497,20 +5579,20 @@
       <c r="Y19" s="27" t="s">
         <v>389</v>
       </c>
-      <c r="Z19" s="27" t="s">
-        <v>696</v>
+      <c r="Z19" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA19" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB19" s="27" t="s">
-        <v>696</v>
+      <c r="AB19" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC19" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>20</v>
       </c>
@@ -5594,20 +5676,20 @@
       <c r="Y20" s="27" t="s">
         <v>390</v>
       </c>
-      <c r="Z20" s="27" t="s">
-        <v>696</v>
+      <c r="Z20" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA20" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB20" s="27" t="s">
-        <v>696</v>
+      <c r="AB20" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC20" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <v>21</v>
       </c>
@@ -5691,20 +5773,20 @@
       <c r="Y21" s="27" t="s">
         <v>391</v>
       </c>
-      <c r="Z21" s="27" t="s">
-        <v>696</v>
+      <c r="Z21" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA21" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB21" s="27" t="s">
-        <v>696</v>
+      <c r="AB21" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC21" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <v>22</v>
       </c>
@@ -5788,20 +5870,20 @@
       <c r="Y22" s="27" t="s">
         <v>392</v>
       </c>
-      <c r="Z22" s="27" t="s">
-        <v>696</v>
+      <c r="Z22" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA22" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB22" s="27" t="s">
-        <v>696</v>
+      <c r="AB22" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC22" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41">
         <v>23</v>
       </c>
@@ -5885,20 +5967,20 @@
       <c r="Y23" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="Z23" s="27" t="s">
-        <v>696</v>
+      <c r="Z23" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA23" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB23" s="27" t="s">
-        <v>696</v>
+      <c r="AB23" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC23" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>24</v>
       </c>
@@ -5982,20 +6064,20 @@
       <c r="Y24" s="27" t="s">
         <v>393</v>
       </c>
-      <c r="Z24" s="27" t="s">
-        <v>696</v>
+      <c r="Z24" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA24" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB24" s="27" t="s">
-        <v>696</v>
+      <c r="AB24" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC24" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>25</v>
       </c>
@@ -6079,20 +6161,20 @@
       <c r="Y25" s="27" t="s">
         <v>395</v>
       </c>
-      <c r="Z25" s="27" t="s">
-        <v>696</v>
+      <c r="Z25" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA25" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB25" s="27" t="s">
-        <v>696</v>
+      <c r="AB25" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC25" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>26</v>
       </c>
@@ -6176,20 +6258,20 @@
       <c r="Y26" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z26" s="27" t="s">
-        <v>696</v>
+      <c r="Z26" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA26" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="AB26" s="27" t="s">
-        <v>696</v>
+      <c r="AB26" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC26" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>27</v>
       </c>
@@ -6273,20 +6355,20 @@
       <c r="Y27" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z27" s="27" t="s">
-        <v>696</v>
+      <c r="Z27" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA27" s="26" t="s">
         <v>425</v>
       </c>
-      <c r="AB27" s="27" t="s">
-        <v>696</v>
+      <c r="AB27" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC27" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>28</v>
       </c>
@@ -6370,20 +6452,20 @@
       <c r="Y28" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z28" s="27" t="s">
-        <v>696</v>
+      <c r="Z28" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA28" s="26" t="s">
         <v>426</v>
       </c>
-      <c r="AB28" s="27" t="s">
-        <v>696</v>
+      <c r="AB28" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC28" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="41">
         <v>29</v>
       </c>
@@ -6467,20 +6549,20 @@
       <c r="Y29" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z29" s="27" t="s">
-        <v>696</v>
+      <c r="Z29" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA29" s="26" t="s">
         <v>427</v>
       </c>
-      <c r="AB29" s="27" t="s">
-        <v>696</v>
+      <c r="AB29" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC29" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>30</v>
       </c>
@@ -6564,20 +6646,20 @@
       <c r="Y30" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z30" s="27" t="s">
-        <v>696</v>
+      <c r="Z30" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA30" s="26" t="s">
         <v>428</v>
       </c>
-      <c r="AB30" s="27" t="s">
-        <v>696</v>
+      <c r="AB30" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC30" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>31</v>
       </c>
@@ -6661,20 +6743,20 @@
       <c r="Y31" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z31" s="27" t="s">
-        <v>696</v>
+      <c r="Z31" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA31" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="AB31" s="27" t="s">
-        <v>696</v>
+      <c r="AB31" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC31" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>32</v>
       </c>
@@ -6758,20 +6840,20 @@
       <c r="Y32" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z32" s="27" t="s">
-        <v>696</v>
+      <c r="Z32" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA32" s="26" t="s">
         <v>403</v>
       </c>
-      <c r="AB32" s="27" t="s">
-        <v>696</v>
+      <c r="AB32" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC32" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>33</v>
       </c>
@@ -6855,20 +6937,20 @@
       <c r="Y33" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z33" s="27" t="s">
-        <v>696</v>
+      <c r="Z33" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA33" s="26" t="s">
         <v>430</v>
       </c>
-      <c r="AB33" s="27" t="s">
-        <v>696</v>
+      <c r="AB33" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC33" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <v>34</v>
       </c>
@@ -6952,20 +7034,20 @@
       <c r="Y34" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z34" s="27" t="s">
-        <v>696</v>
+      <c r="Z34" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA34" s="26" t="s">
         <v>404</v>
       </c>
-      <c r="AB34" s="27" t="s">
-        <v>696</v>
+      <c r="AB34" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC34" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <v>35</v>
       </c>
@@ -7049,20 +7131,20 @@
       <c r="Y35" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z35" s="27" t="s">
-        <v>696</v>
+      <c r="Z35" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA35" s="26" t="s">
         <v>431</v>
       </c>
-      <c r="AB35" s="27" t="s">
-        <v>696</v>
+      <c r="AB35" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC35" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>36</v>
       </c>
@@ -7146,20 +7228,20 @@
       <c r="Y36" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z36" s="27" t="s">
-        <v>696</v>
+      <c r="Z36" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA36" s="26" t="s">
         <v>432</v>
       </c>
-      <c r="AB36" s="27" t="s">
-        <v>696</v>
+      <c r="AB36" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC36" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>37</v>
       </c>
@@ -7243,20 +7325,20 @@
       <c r="Y37" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z37" s="27" t="s">
-        <v>696</v>
+      <c r="Z37" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA37" s="26" t="s">
         <v>433</v>
       </c>
-      <c r="AB37" s="27" t="s">
-        <v>696</v>
+      <c r="AB37" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC37" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>38</v>
       </c>
@@ -7340,20 +7422,20 @@
       <c r="Y38" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z38" s="27" t="s">
-        <v>696</v>
+      <c r="Z38" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA38" s="26" t="s">
         <v>434</v>
       </c>
-      <c r="AB38" s="27" t="s">
-        <v>696</v>
+      <c r="AB38" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC38" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="41">
         <v>39</v>
       </c>
@@ -7437,20 +7519,20 @@
       <c r="Y39" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z39" s="27" t="s">
-        <v>696</v>
+      <c r="Z39" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA39" s="26" t="s">
         <v>435</v>
       </c>
-      <c r="AB39" s="27" t="s">
-        <v>696</v>
+      <c r="AB39" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC39" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="41">
         <v>40</v>
       </c>
@@ -7534,20 +7616,20 @@
       <c r="Y40" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z40" s="27" t="s">
-        <v>696</v>
+      <c r="Z40" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA40" s="26" t="s">
         <v>436</v>
       </c>
-      <c r="AB40" s="27" t="s">
-        <v>696</v>
+      <c r="AB40" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC40" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41">
         <v>41</v>
       </c>
@@ -7631,20 +7713,20 @@
       <c r="Y41" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z41" s="27" t="s">
-        <v>696</v>
+      <c r="Z41" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA41" s="26" t="s">
         <v>437</v>
       </c>
-      <c r="AB41" s="27" t="s">
-        <v>696</v>
+      <c r="AB41" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC41" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>42</v>
       </c>
@@ -7728,20 +7810,20 @@
       <c r="Y42" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="Z42" s="27" t="s">
-        <v>696</v>
+      <c r="Z42" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA42" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB42" s="27" t="s">
-        <v>696</v>
+      <c r="AB42" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC42" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41">
         <v>43</v>
       </c>
@@ -7825,20 +7907,20 @@
       <c r="Y43" s="27" t="s">
         <v>377</v>
       </c>
-      <c r="Z43" s="27" t="s">
-        <v>696</v>
+      <c r="Z43" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA43" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB43" s="27" t="s">
-        <v>696</v>
+      <c r="AB43" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC43" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41">
         <v>44</v>
       </c>
@@ -7922,20 +8004,20 @@
       <c r="Y44" s="27" t="s">
         <v>378</v>
       </c>
-      <c r="Z44" s="27" t="s">
-        <v>696</v>
+      <c r="Z44" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA44" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB44" s="27" t="s">
-        <v>696</v>
+      <c r="AB44" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC44" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="41">
         <v>45</v>
       </c>
@@ -8019,20 +8101,20 @@
       <c r="Y45" s="27" t="s">
         <v>379</v>
       </c>
-      <c r="Z45" s="27" t="s">
-        <v>696</v>
+      <c r="Z45" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA45" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB45" s="27" t="s">
-        <v>696</v>
+      <c r="AB45" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC45" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="41">
         <v>46</v>
       </c>
@@ -8116,20 +8198,20 @@
       <c r="Y46" s="27" t="s">
         <v>386</v>
       </c>
-      <c r="Z46" s="27" t="s">
-        <v>696</v>
+      <c r="Z46" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA46" s="27" t="s">
         <v>419</v>
       </c>
-      <c r="AB46" s="27" t="s">
-        <v>696</v>
+      <c r="AB46" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC46" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41">
         <v>47</v>
       </c>
@@ -8213,20 +8295,20 @@
       <c r="Y47" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z47" s="27" t="s">
-        <v>696</v>
+      <c r="Z47" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA47" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="AB47" s="27" t="s">
-        <v>696</v>
+      <c r="AB47" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC47" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>48</v>
       </c>
@@ -8310,20 +8392,20 @@
       <c r="Y48" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z48" s="27" t="s">
-        <v>696</v>
+      <c r="Z48" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA48" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="AB48" s="27" t="s">
-        <v>696</v>
+      <c r="AB48" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC48" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41">
         <v>49</v>
       </c>
@@ -8407,20 +8489,20 @@
       <c r="Y49" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z49" s="27" t="s">
-        <v>696</v>
+      <c r="Z49" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA49" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="AB49" s="27" t="s">
-        <v>696</v>
+      <c r="AB49" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC49" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>50</v>
       </c>
@@ -8504,20 +8586,20 @@
       <c r="Y50" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z50" s="27" t="s">
-        <v>696</v>
+      <c r="Z50" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA50" s="26" t="s">
         <v>423</v>
       </c>
-      <c r="AB50" s="27" t="s">
-        <v>696</v>
+      <c r="AB50" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC50" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="41">
         <v>51</v>
       </c>
@@ -8601,20 +8683,20 @@
       <c r="Y51" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z51" s="27" t="s">
-        <v>696</v>
+      <c r="Z51" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA51" s="26" t="s">
         <v>424</v>
       </c>
-      <c r="AB51" s="27" t="s">
-        <v>696</v>
+      <c r="AB51" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC51" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="41">
         <v>52</v>
       </c>
@@ -8698,20 +8780,20 @@
       <c r="Y52" s="27" t="s">
         <v>375</v>
       </c>
-      <c r="Z52" s="27" t="s">
-        <v>696</v>
+      <c r="Z52" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA52" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB52" s="27" t="s">
-        <v>696</v>
+      <c r="AB52" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC52" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="41">
         <v>53</v>
       </c>
@@ -8795,20 +8877,20 @@
       <c r="Y53" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="Z53" s="27" t="s">
-        <v>696</v>
+      <c r="Z53" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA53" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB53" s="27" t="s">
-        <v>696</v>
+      <c r="AB53" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC53" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="41">
         <v>54</v>
       </c>
@@ -8892,20 +8974,20 @@
       <c r="Y54" s="27" t="s">
         <v>396</v>
       </c>
-      <c r="Z54" s="27" t="s">
-        <v>696</v>
+      <c r="Z54" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA54" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB54" s="27" t="s">
-        <v>696</v>
+      <c r="AB54" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC54" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="41">
         <v>55</v>
       </c>
@@ -8989,20 +9071,20 @@
       <c r="Y55" s="27" t="s">
         <v>382</v>
       </c>
-      <c r="Z55" s="27" t="s">
-        <v>696</v>
+      <c r="Z55" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA55" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB55" s="27" t="s">
-        <v>696</v>
+      <c r="AB55" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC55" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="41">
         <v>56</v>
       </c>
@@ -9086,20 +9168,20 @@
       <c r="Y56" s="27" t="s">
         <v>383</v>
       </c>
-      <c r="Z56" s="27" t="s">
-        <v>696</v>
+      <c r="Z56" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA56" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB56" s="27" t="s">
-        <v>696</v>
+      <c r="AB56" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC56" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="41">
         <v>57</v>
       </c>
@@ -9183,20 +9265,20 @@
       <c r="Y57" s="27" t="s">
         <v>399</v>
       </c>
-      <c r="Z57" s="27" t="s">
-        <v>696</v>
+      <c r="Z57" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA57" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB57" s="27" t="s">
-        <v>696</v>
+      <c r="AB57" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC57" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="41">
         <v>58</v>
       </c>
@@ -9280,20 +9362,20 @@
       <c r="Y58" s="27" t="s">
         <v>397</v>
       </c>
-      <c r="Z58" s="27" t="s">
-        <v>696</v>
+      <c r="Z58" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA58" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB58" s="27" t="s">
-        <v>696</v>
+      <c r="AB58" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC58" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="41">
         <v>59</v>
       </c>
@@ -9377,20 +9459,20 @@
       <c r="Y59" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="Z59" s="27" t="s">
-        <v>696</v>
+      <c r="Z59" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA59" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB59" s="27" t="s">
-        <v>696</v>
+      <c r="AB59" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC59" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="41">
         <v>60</v>
       </c>
@@ -9474,20 +9556,20 @@
       <c r="Y60" s="27" t="s">
         <v>398</v>
       </c>
-      <c r="Z60" s="27" t="s">
-        <v>696</v>
+      <c r="Z60" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA60" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB60" s="27" t="s">
-        <v>696</v>
+      <c r="AB60" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC60" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="41">
         <v>61</v>
       </c>
@@ -9571,20 +9653,20 @@
       <c r="Y61" s="27" t="s">
         <v>342</v>
       </c>
-      <c r="Z61" s="27" t="s">
-        <v>696</v>
+      <c r="Z61" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA61" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB61" s="27" t="s">
-        <v>696</v>
+      <c r="AB61" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC61" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="41">
         <v>62</v>
       </c>
@@ -9668,20 +9750,20 @@
       <c r="Y62" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="Z62" s="27" t="s">
-        <v>696</v>
+      <c r="Z62" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA62" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB62" s="27" t="s">
-        <v>696</v>
+      <c r="AB62" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC62" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="41">
         <v>63</v>
       </c>
@@ -9765,20 +9847,20 @@
       <c r="Y63" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="Z63" s="27" t="s">
-        <v>696</v>
+      <c r="Z63" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA63" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB63" s="27" t="s">
-        <v>696</v>
+      <c r="AB63" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC63" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="41">
         <v>64</v>
       </c>
@@ -9862,20 +9944,20 @@
       <c r="Y64" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="Z64" s="27" t="s">
-        <v>696</v>
+      <c r="Z64" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA64" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB64" s="27" t="s">
-        <v>696</v>
+      <c r="AB64" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC64" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="41">
         <v>65</v>
       </c>
@@ -9959,20 +10041,20 @@
       <c r="Y65" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="Z65" s="27" t="s">
-        <v>696</v>
+      <c r="Z65" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA65" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB65" s="27" t="s">
-        <v>696</v>
+      <c r="AB65" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC65" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="41">
         <v>66</v>
       </c>
@@ -10056,20 +10138,20 @@
       <c r="Y66" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="Z66" s="27" t="s">
-        <v>696</v>
+      <c r="Z66" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA66" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB66" s="27" t="s">
-        <v>696</v>
+      <c r="AB66" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC66" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="41">
         <v>67</v>
       </c>
@@ -10153,20 +10235,20 @@
       <c r="Y67" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="Z67" s="27" t="s">
-        <v>696</v>
+      <c r="Z67" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA67" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB67" s="27" t="s">
-        <v>696</v>
+      <c r="AB67" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC67" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="68" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="41">
         <v>68</v>
       </c>
@@ -10250,20 +10332,20 @@
       <c r="Y68" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="Z68" s="27" t="s">
-        <v>696</v>
+      <c r="Z68" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA68" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB68" s="27" t="s">
-        <v>696</v>
+      <c r="AB68" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC68" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="69" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="41">
         <v>69</v>
       </c>
@@ -10347,20 +10429,20 @@
       <c r="Y69" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="Z69" s="27" t="s">
-        <v>696</v>
+      <c r="Z69" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA69" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB69" s="27" t="s">
-        <v>696</v>
+      <c r="AB69" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC69" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="70" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="41">
         <v>70</v>
       </c>
@@ -10444,20 +10526,20 @@
       <c r="Y70" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="Z70" s="27" t="s">
-        <v>696</v>
+      <c r="Z70" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA70" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB70" s="27" t="s">
-        <v>696</v>
+      <c r="AB70" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC70" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="71" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="41">
         <v>71</v>
       </c>
@@ -10541,20 +10623,20 @@
       <c r="Y71" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="Z71" s="27" t="s">
-        <v>696</v>
+      <c r="Z71" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA71" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB71" s="27" t="s">
-        <v>696</v>
+      <c r="AB71" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC71" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="72" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="41">
         <v>72</v>
       </c>
@@ -10638,20 +10720,20 @@
       <c r="Y72" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="Z72" s="27" t="s">
-        <v>696</v>
+      <c r="Z72" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA72" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB72" s="27" t="s">
-        <v>696</v>
+      <c r="AB72" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC72" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="73" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="41">
         <v>73</v>
       </c>
@@ -10735,20 +10817,20 @@
       <c r="Y73" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="Z73" s="27" t="s">
-        <v>696</v>
+      <c r="Z73" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA73" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB73" s="27" t="s">
-        <v>696</v>
+      <c r="AB73" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC73" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="74" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="41">
         <v>74</v>
       </c>
@@ -10832,20 +10914,20 @@
       <c r="Y74" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="Z74" s="27" t="s">
-        <v>696</v>
+      <c r="Z74" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA74" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB74" s="27" t="s">
-        <v>696</v>
+      <c r="AB74" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC74" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="75" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="41">
         <v>75</v>
       </c>
@@ -10929,20 +11011,20 @@
       <c r="Y75" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="Z75" s="27" t="s">
-        <v>696</v>
+      <c r="Z75" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA75" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB75" s="27" t="s">
-        <v>696</v>
+      <c r="AB75" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC75" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="76" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="41">
         <v>76</v>
       </c>
@@ -11026,20 +11108,20 @@
       <c r="Y76" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="Z76" s="27" t="s">
-        <v>696</v>
+      <c r="Z76" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA76" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB76" s="27" t="s">
-        <v>696</v>
+      <c r="AB76" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC76" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="77" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="41">
         <v>77</v>
       </c>
@@ -11123,20 +11205,20 @@
       <c r="Y77" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="Z77" s="27" t="s">
-        <v>696</v>
+      <c r="Z77" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA77" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB77" s="27" t="s">
-        <v>696</v>
+      <c r="AB77" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC77" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="78" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="41">
         <v>78</v>
       </c>
@@ -11220,20 +11302,20 @@
       <c r="Y78" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="Z78" s="27" t="s">
-        <v>696</v>
+      <c r="Z78" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA78" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB78" s="27" t="s">
-        <v>696</v>
+      <c r="AB78" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC78" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="79" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="41">
         <v>79</v>
       </c>
@@ -11317,20 +11399,20 @@
       <c r="Y79" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="Z79" s="27" t="s">
-        <v>696</v>
+      <c r="Z79" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA79" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB79" s="27" t="s">
-        <v>696</v>
+      <c r="AB79" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC79" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="80" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="41">
         <v>80</v>
       </c>
@@ -11414,20 +11496,20 @@
       <c r="Y80" s="27" t="s">
         <v>337</v>
       </c>
-      <c r="Z80" s="27" t="s">
-        <v>696</v>
+      <c r="Z80" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA80" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB80" s="27" t="s">
-        <v>696</v>
+      <c r="AB80" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC80" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="81" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="41">
         <v>81</v>
       </c>
@@ -11511,20 +11593,20 @@
       <c r="Y81" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="Z81" s="27" t="s">
-        <v>696</v>
+      <c r="Z81" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA81" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB81" s="27" t="s">
-        <v>696</v>
+      <c r="AB81" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC81" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="82" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="41">
         <v>82</v>
       </c>
@@ -11608,20 +11690,20 @@
       <c r="Y82" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="Z82" s="27" t="s">
-        <v>696</v>
+      <c r="Z82" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA82" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB82" s="27" t="s">
-        <v>696</v>
+      <c r="AB82" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC82" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="83" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="41">
         <v>83</v>
       </c>
@@ -11705,20 +11787,20 @@
       <c r="Y83" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="Z83" s="27" t="s">
-        <v>696</v>
+      <c r="Z83" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA83" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB83" s="27" t="s">
-        <v>696</v>
+      <c r="AB83" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC83" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="84" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="41">
         <v>84</v>
       </c>
@@ -11802,20 +11884,20 @@
       <c r="Y84" s="27" t="s">
         <v>352</v>
       </c>
-      <c r="Z84" s="27" t="s">
-        <v>696</v>
+      <c r="Z84" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA84" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB84" s="27" t="s">
-        <v>696</v>
+      <c r="AB84" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC84" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="85" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="41">
         <v>85</v>
       </c>
@@ -11899,20 +11981,20 @@
       <c r="Y85" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="Z85" s="27" t="s">
-        <v>696</v>
+      <c r="Z85" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA85" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB85" s="27" t="s">
-        <v>696</v>
+      <c r="AB85" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC85" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="86" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="41">
         <v>86</v>
       </c>
@@ -11996,20 +12078,20 @@
       <c r="Y86" s="27" t="s">
         <v>354</v>
       </c>
-      <c r="Z86" s="27" t="s">
-        <v>696</v>
+      <c r="Z86" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA86" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB86" s="27" t="s">
-        <v>696</v>
+      <c r="AB86" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC86" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="87" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="41">
         <v>87</v>
       </c>
@@ -12093,20 +12175,20 @@
       <c r="Y87" s="27" t="s">
         <v>355</v>
       </c>
-      <c r="Z87" s="27" t="s">
-        <v>696</v>
+      <c r="Z87" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA87" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB87" s="27" t="s">
-        <v>696</v>
+      <c r="AB87" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC87" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="88" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="41">
         <v>88</v>
       </c>
@@ -12190,20 +12272,20 @@
       <c r="Y88" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="Z88" s="27" t="s">
-        <v>696</v>
+      <c r="Z88" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA88" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB88" s="27" t="s">
-        <v>696</v>
+      <c r="AB88" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC88" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="89" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="41">
         <v>89</v>
       </c>
@@ -12287,20 +12369,20 @@
       <c r="Y89" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="Z89" s="27" t="s">
-        <v>696</v>
+      <c r="Z89" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA89" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB89" s="27" t="s">
-        <v>696</v>
+      <c r="AB89" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC89" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="90" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="41">
         <v>90</v>
       </c>
@@ -12384,20 +12466,20 @@
       <c r="Y90" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="Z90" s="27" t="s">
-        <v>696</v>
+      <c r="Z90" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA90" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="AB90" s="27" t="s">
-        <v>696</v>
+      <c r="AB90" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC90" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="91" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="41">
         <v>91</v>
       </c>
@@ -12481,20 +12563,20 @@
       <c r="Y91" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="Z91" s="27" t="s">
-        <v>696</v>
+      <c r="Z91" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA91" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB91" s="27" t="s">
-        <v>696</v>
+      <c r="AB91" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC91" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="92" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="41">
         <v>92</v>
       </c>
@@ -12578,20 +12660,20 @@
       <c r="Y92" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="Z92" s="27" t="s">
-        <v>696</v>
+      <c r="Z92" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA92" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB92" s="27" t="s">
-        <v>696</v>
+      <c r="AB92" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC92" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="93" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="41">
         <v>93</v>
       </c>
@@ -12675,20 +12757,20 @@
       <c r="Y93" s="27" t="s">
         <v>362</v>
       </c>
-      <c r="Z93" s="27" t="s">
-        <v>696</v>
+      <c r="Z93" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA93" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB93" s="27" t="s">
-        <v>696</v>
+      <c r="AB93" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC93" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="94" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="41">
         <v>94</v>
       </c>
@@ -12772,20 +12854,20 @@
       <c r="Y94" s="27" t="s">
         <v>360</v>
       </c>
-      <c r="Z94" s="27" t="s">
-        <v>696</v>
+      <c r="Z94" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA94" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="AB94" s="27" t="s">
-        <v>696</v>
+      <c r="AB94" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC94" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="95" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="41">
         <v>95</v>
       </c>
@@ -12869,20 +12951,20 @@
       <c r="Y95" s="27" t="s">
         <v>363</v>
       </c>
-      <c r="Z95" s="27" t="s">
-        <v>696</v>
+      <c r="Z95" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA95" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AB95" s="27" t="s">
-        <v>696</v>
+      <c r="AB95" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC95" s="45" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="96" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="41">
         <v>96</v>
       </c>
@@ -12966,20 +13048,20 @@
       <c r="Y96" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z96" s="27" t="s">
-        <v>696</v>
+      <c r="Z96" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA96" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="AB96" s="27" t="s">
-        <v>696</v>
+      <c r="AB96" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC96" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="97" spans="1:29" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="41">
         <v>97</v>
       </c>
@@ -13063,20 +13145,20 @@
       <c r="Y97" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z97" s="27" t="s">
-        <v>696</v>
+      <c r="Z97" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA97" s="26" t="s">
         <v>412</v>
       </c>
-      <c r="AB97" s="27" t="s">
-        <v>696</v>
+      <c r="AB97" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC97" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="41">
         <v>98</v>
       </c>
@@ -13160,20 +13242,20 @@
       <c r="Y98" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z98" s="27" t="s">
-        <v>696</v>
+      <c r="Z98" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA98" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="AB98" s="27" t="s">
-        <v>696</v>
+      <c r="AB98" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC98" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="41">
         <v>99</v>
       </c>
@@ -13257,20 +13339,20 @@
       <c r="Y99" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z99" s="27" t="s">
-        <v>696</v>
+      <c r="Z99" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA99" s="26" t="s">
         <v>410</v>
       </c>
-      <c r="AB99" s="27" t="s">
-        <v>696</v>
+      <c r="AB99" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC99" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="41">
         <v>100</v>
       </c>
@@ -13354,20 +13436,20 @@
       <c r="Y100" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z100" s="27" t="s">
-        <v>696</v>
+      <c r="Z100" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA100" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="AB100" s="27" t="s">
-        <v>696</v>
+      <c r="AB100" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC100" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="41">
         <v>101</v>
       </c>
@@ -13451,20 +13533,20 @@
       <c r="Y101" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z101" s="27" t="s">
-        <v>696</v>
+      <c r="Z101" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA101" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="AB101" s="27" t="s">
-        <v>696</v>
+      <c r="AB101" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC101" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="41">
         <v>102</v>
       </c>
@@ -13548,20 +13630,20 @@
       <c r="Y102" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z102" s="27" t="s">
-        <v>696</v>
+      <c r="Z102" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA102" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="AB102" s="27" t="s">
-        <v>696</v>
+      <c r="AB102" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC102" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="41">
         <v>103</v>
       </c>
@@ -13645,20 +13727,20 @@
       <c r="Y103" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="Z103" s="27" t="s">
-        <v>696</v>
+      <c r="Z103" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA103" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB103" s="27" t="s">
-        <v>696</v>
+      <c r="AB103" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC103" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="41">
         <v>104</v>
       </c>
@@ -13742,20 +13824,20 @@
       <c r="Y104" s="27" t="s">
         <v>369</v>
       </c>
-      <c r="Z104" s="27" t="s">
-        <v>696</v>
+      <c r="Z104" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA104" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB104" s="27" t="s">
-        <v>696</v>
+      <c r="AB104" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC104" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="41">
         <v>105</v>
       </c>
@@ -13839,20 +13921,20 @@
       <c r="Y105" s="27" t="s">
         <v>367</v>
       </c>
-      <c r="Z105" s="27" t="s">
-        <v>696</v>
+      <c r="Z105" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA105" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB105" s="27" t="s">
-        <v>696</v>
+      <c r="AB105" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC105" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="41">
         <v>106</v>
       </c>
@@ -13936,20 +14018,20 @@
       <c r="Y106" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z106" s="27" t="s">
-        <v>696</v>
+      <c r="Z106" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA106" s="26" t="s">
         <v>408</v>
       </c>
-      <c r="AB106" s="27" t="s">
-        <v>696</v>
+      <c r="AB106" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC106" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="41">
         <v>107</v>
       </c>
@@ -14033,20 +14115,20 @@
       <c r="Y107" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z107" s="27" t="s">
-        <v>696</v>
+      <c r="Z107" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA107" s="26" t="s">
         <v>402</v>
       </c>
-      <c r="AB107" s="27" t="s">
-        <v>696</v>
+      <c r="AB107" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC107" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="41">
         <v>108</v>
       </c>
@@ -14130,20 +14212,20 @@
       <c r="Y108" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z108" s="27" t="s">
-        <v>696</v>
+      <c r="Z108" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA108" s="26" t="s">
         <v>409</v>
       </c>
-      <c r="AB108" s="27" t="s">
-        <v>696</v>
+      <c r="AB108" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC108" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="41">
         <v>109</v>
       </c>
@@ -14227,20 +14309,20 @@
       <c r="Y109" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="Z109" s="27" t="s">
-        <v>696</v>
+      <c r="Z109" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA109" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB109" s="27" t="s">
-        <v>696</v>
+      <c r="AB109" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC109" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="41">
         <v>110</v>
       </c>
@@ -14324,20 +14406,20 @@
       <c r="Y110" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="Z110" s="27" t="s">
-        <v>696</v>
+      <c r="Z110" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA110" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB110" s="27" t="s">
-        <v>696</v>
+      <c r="AB110" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC110" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="41">
         <v>111</v>
       </c>
@@ -14421,20 +14503,20 @@
       <c r="Y111" s="27" t="s">
         <v>368</v>
       </c>
-      <c r="Z111" s="27" t="s">
-        <v>696</v>
+      <c r="Z111" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA111" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB111" s="27" t="s">
-        <v>696</v>
+      <c r="AB111" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC111" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="41">
         <v>112</v>
       </c>
@@ -14518,20 +14600,20 @@
       <c r="Y112" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="Z112" s="27" t="s">
-        <v>696</v>
+      <c r="Z112" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA112" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB112" s="27" t="s">
-        <v>696</v>
+      <c r="AB112" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC112" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="41">
         <v>113</v>
       </c>
@@ -14615,20 +14697,20 @@
       <c r="Y113" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="Z113" s="27" t="s">
-        <v>696</v>
+      <c r="Z113" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA113" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="AB113" s="27" t="s">
-        <v>696</v>
+      <c r="AB113" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC113" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="114" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="41">
         <v>114</v>
       </c>
@@ -14713,20 +14795,20 @@
       <c r="Y114" s="65" t="s">
         <v>583</v>
       </c>
-      <c r="Z114" s="27" t="s">
-        <v>696</v>
+      <c r="Z114" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA114" s="66" t="s">
         <v>584</v>
       </c>
-      <c r="AB114" s="27" t="s">
-        <v>696</v>
+      <c r="AB114" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC114" s="45" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="115" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="41">
         <v>115</v>
       </c>
@@ -14809,22 +14891,22 @@
         <v>Key-CIRCU-115</v>
       </c>
       <c r="Y115" s="65" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="Z115" s="27" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AA115" s="66" t="s">
         <v>584</v>
       </c>
-      <c r="AB115" s="27" t="s">
-        <v>696</v>
+      <c r="AB115" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC115" s="45" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="116" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="41">
         <v>116</v>
       </c>
@@ -14909,20 +14991,20 @@
       <c r="Y116" s="65" t="s">
         <v>589</v>
       </c>
-      <c r="Z116" s="27" t="s">
-        <v>696</v>
+      <c r="Z116" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA116" s="66" t="s">
         <v>584</v>
       </c>
-      <c r="AB116" s="27" t="s">
-        <v>696</v>
+      <c r="AB116" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC116" s="45" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="117" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="41">
         <v>117</v>
       </c>
@@ -14986,7 +15068,7 @@
         <v>9</v>
       </c>
       <c r="T117" s="45" t="str">
-        <f t="shared" ref="T117:V121" si="40">SUBSTITUTE(C117, ".", " ")</f>
+        <f t="shared" ref="T117:V125" si="40">SUBSTITUTE(C117, ".", " ")</f>
         <v>De Circulação</v>
       </c>
       <c r="U117" s="45" t="str">
@@ -15007,20 +15089,20 @@
       <c r="Y117" s="27" t="s">
         <v>364</v>
       </c>
-      <c r="Z117" s="27" t="s">
-        <v>696</v>
+      <c r="Z117" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA117" s="26" t="s">
         <v>418</v>
       </c>
-      <c r="AB117" s="27" t="s">
-        <v>696</v>
+      <c r="AB117" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC117" s="45" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="118" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="41">
         <v>118</v>
       </c>
@@ -15105,20 +15187,20 @@
       <c r="Y118" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z118" s="27" t="s">
-        <v>696</v>
+      <c r="Z118" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA118" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB118" s="27" t="s">
-        <v>696</v>
+      <c r="AB118" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC118" s="45" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="119" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="41">
         <v>119</v>
       </c>
@@ -15203,20 +15285,20 @@
       <c r="Y119" s="27" t="s">
         <v>549</v>
       </c>
-      <c r="Z119" s="27" t="s">
-        <v>696</v>
+      <c r="Z119" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA119" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="AB119" s="27" t="s">
-        <v>696</v>
+      <c r="AB119" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC119" s="45" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="120" spans="1:29" s="46" customFormat="1" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="41">
         <v>120</v>
       </c>
@@ -15301,20 +15383,20 @@
       <c r="Y120" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="Z120" s="27" t="s">
-        <v>696</v>
+      <c r="Z120" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AA120" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="AB120" s="27" t="s">
-        <v>696</v>
+      <c r="AB120" s="68" t="s">
+        <v>9</v>
       </c>
       <c r="AC120" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="121" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="41">
         <v>121</v>
       </c>
@@ -15322,17 +15404,17 @@
         <v>523</v>
       </c>
       <c r="C121" s="44" t="s">
+        <v>701</v>
+      </c>
+      <c r="D121" s="44" t="s">
+        <v>703</v>
+      </c>
+      <c r="E121" s="44" t="s">
         <v>702</v>
       </c>
-      <c r="D121" s="44" t="s">
+      <c r="F121" s="44" t="s">
         <v>704</v>
       </c>
-      <c r="E121" s="44" t="s">
-        <v>703</v>
-      </c>
-      <c r="F121" s="44" t="s">
-        <v>705</v>
-      </c>
       <c r="G121" s="67" t="s">
         <v>9</v>
       </c>
@@ -15349,7 +15431,7 @@
         <v>9</v>
       </c>
       <c r="L121" s="32" t="str">
-        <f t="shared" ref="L121:O121" si="41">SUBSTITUTE(CONCATENATE("", C121), ".", " ")</f>
+        <f t="shared" ref="L121:O125" si="41">SUBSTITUTE(CONCATENATE("", C121), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M121" s="32" t="str">
@@ -15362,16 +15444,16 @@
       </c>
       <c r="O121" s="32" t="str">
         <f t="shared" si="41"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P121" s="27" t="s">
+        <v>705</v>
+      </c>
+      <c r="Q121" s="27" t="s">
         <v>706</v>
       </c>
-      <c r="Q121" s="27" t="s">
+      <c r="R121" s="27" t="s">
         <v>707</v>
-      </c>
-      <c r="R121" s="27" t="s">
-        <v>708</v>
       </c>
       <c r="S121" s="27" t="s">
         <v>9</v>
@@ -15389,11 +15471,11 @@
         <v>Métodos</v>
       </c>
       <c r="W121" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="X121" s="43" t="str">
-        <f t="shared" si="30"/>
-        <v>Key-CIRCU-121</v>
+        <v>708</v>
+      </c>
+      <c r="X121" s="70" t="str">
+        <f t="shared" ref="X121:X125" si="42">CONCATENATE("Key-ABNT-",A121)</f>
+        <v>Key-ABNT-121</v>
       </c>
       <c r="Y121" s="68" t="s">
         <v>9</v>
@@ -15408,6 +15490,394 @@
         <v>9</v>
       </c>
       <c r="AC121" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="41">
+        <v>122</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C122" s="44" t="s">
+        <v>701</v>
+      </c>
+      <c r="D122" s="44" t="s">
+        <v>703</v>
+      </c>
+      <c r="E122" s="44" t="s">
+        <v>702</v>
+      </c>
+      <c r="F122" s="44" t="s">
+        <v>709</v>
+      </c>
+      <c r="G122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L122" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M122" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N122" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O122" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P122" s="27" t="s">
+        <v>710</v>
+      </c>
+      <c r="Q122" s="27" t="s">
+        <v>711</v>
+      </c>
+      <c r="R122" s="27" t="s">
+        <v>712</v>
+      </c>
+      <c r="S122" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="T122" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="U122" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="V122" s="45" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W122" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="X122" s="70" t="str">
+        <f t="shared" si="42"/>
+        <v>Key-ABNT-122</v>
+      </c>
+      <c r="Y122" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z122" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA122" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB122" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC122" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="123" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="41">
+        <v>123</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C123" s="44" t="s">
+        <v>701</v>
+      </c>
+      <c r="D123" s="44" t="s">
+        <v>703</v>
+      </c>
+      <c r="E123" s="44" t="s">
+        <v>702</v>
+      </c>
+      <c r="F123" s="44" t="s">
+        <v>713</v>
+      </c>
+      <c r="G123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L123" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M123" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N123" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O123" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P123" s="27" t="s">
+        <v>714</v>
+      </c>
+      <c r="Q123" s="27" t="s">
+        <v>715</v>
+      </c>
+      <c r="R123" s="27" t="s">
+        <v>716</v>
+      </c>
+      <c r="S123" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="T123" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="U123" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="V123" s="45" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W123" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="X123" s="70" t="str">
+        <f t="shared" si="42"/>
+        <v>Key-ABNT-123</v>
+      </c>
+      <c r="Y123" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z123" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA123" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB123" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC123" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A124" s="41">
+        <v>124</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C124" s="44" t="s">
+        <v>701</v>
+      </c>
+      <c r="D124" s="44" t="s">
+        <v>703</v>
+      </c>
+      <c r="E124" s="44" t="s">
+        <v>702</v>
+      </c>
+      <c r="F124" s="44" t="s">
+        <v>717</v>
+      </c>
+      <c r="G124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L124" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M124" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N124" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O124" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P124" s="27" t="s">
+        <v>718</v>
+      </c>
+      <c r="Q124" s="27" t="s">
+        <v>719</v>
+      </c>
+      <c r="R124" s="27" t="s">
+        <v>720</v>
+      </c>
+      <c r="S124" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="T124" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="U124" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="V124" s="45" t="str">
+        <f t="shared" si="40"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W124" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="X124" s="70" t="str">
+        <f t="shared" si="42"/>
+        <v>Key-ABNT-124</v>
+      </c>
+      <c r="Y124" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z124" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA124" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB124" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC124" s="68" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="125" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A125" s="41">
+        <v>125</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C125" s="44" t="s">
+        <v>701</v>
+      </c>
+      <c r="D125" s="44" t="s">
+        <v>703</v>
+      </c>
+      <c r="E125" s="44" t="s">
+        <v>721</v>
+      </c>
+      <c r="F125" s="44" t="s">
+        <v>722</v>
+      </c>
+      <c r="G125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L125" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M125" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N125" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O125" s="32" t="str">
+        <f t="shared" si="41"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P125" s="27" t="s">
+        <v>723</v>
+      </c>
+      <c r="Q125" s="27" t="s">
+        <v>724</v>
+      </c>
+      <c r="R125" s="27" t="s">
+        <v>725</v>
+      </c>
+      <c r="S125" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="T125" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>De API</v>
+      </c>
+      <c r="U125" s="27" t="str">
+        <f t="shared" si="40"/>
+        <v>Macros</v>
+      </c>
+      <c r="V125" s="45" t="str">
+        <f t="shared" si="40"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W125" s="27" t="s">
+        <v>708</v>
+      </c>
+      <c r="X125" s="70" t="str">
+        <f t="shared" si="42"/>
+        <v>Key-ABNT-125</v>
+      </c>
+      <c r="Y125" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z125" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA125" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB125" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC125" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -15415,84 +15885,87 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AC120">
     <sortCondition ref="E1:E120"/>
   </sortState>
-  <conditionalFormatting sqref="B121">
-    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2:E2 P2:Q4 W2:W4">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:E3 D4:E4">
-    <cfRule type="cellIs" dxfId="21" priority="57" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D47 E11:E53">
-    <cfRule type="cellIs" dxfId="20" priority="87" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="90" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E10">
-    <cfRule type="cellIs" dxfId="19" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68:E116">
-    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E67 D65:D67">
-    <cfRule type="cellIs" dxfId="17" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F114:F116">
-    <cfRule type="duplicateValues" dxfId="16" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F117:F120 F1:F113 F122:F1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F121">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+  <conditionalFormatting sqref="F117:F120 F1:F113 F126:F1048576">
+    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L117:Q120 T117:V120">
-    <cfRule type="cellIs" dxfId="13" priority="29" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q8 AA7:AA8">
-    <cfRule type="cellIs" dxfId="12" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="138" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R121">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R120">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA117">
-    <cfRule type="cellIs" dxfId="10" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA119:AA120">
-    <cfRule type="cellIs" dxfId="9" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1">
-    <cfRule type="cellIs" dxfId="8" priority="134" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="137" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD4 A2:A121 AA3:AA4 AC3:AC4 B3:B113 C4:C113 W6:W121 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120">
-    <cfRule type="cellIs" dxfId="7" priority="28" operator="equal">
+  <conditionalFormatting sqref="AD2:XFD4 AA3:AA4 AC3:AC4 B3:B113 C4:C113 W6:W120 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120 A2:A125">
+    <cfRule type="cellIs" dxfId="0" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B121:B125">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E125:F125">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121:F124">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15501,15 +15974,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.84375" style="10" customWidth="1"/>
-    <col min="2" max="10" width="6.53515625" style="11" customWidth="1"/>
-    <col min="11" max="21" width="6.53515625" style="9" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="9"/>
+    <col min="1" max="1" width="2.85546875" style="10" customWidth="1"/>
+    <col min="2" max="10" width="6.5703125" style="11" customWidth="1"/>
+    <col min="11" max="21" width="6.5703125" style="9" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -15574,7 +16047,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -15639,7 +16112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -15706,7 +16179,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15721,15 +16194,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.15234375" style="23" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.84375" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.3046875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.84375" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.85546875" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28">
         <v>0</v>
       </c>
@@ -15752,7 +16225,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29">
         <v>2</v>
       </c>
@@ -15781,22 +16254,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15807,39 +16280,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56FE74A-92F3-4401-B3DB-ACCAA98B3F78}">
   <dimension ref="A1:AE10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.3046875" customWidth="1"/>
-    <col min="4" max="4" width="7.53515625" customWidth="1"/>
-    <col min="5" max="5" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.53515625" customWidth="1"/>
-    <col min="7" max="7" width="8.53515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="3.53515625" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.53515625" customWidth="1"/>
-    <col min="14" max="14" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.3046875" customWidth="1"/>
-    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="3.5703125" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" customWidth="1"/>
+    <col min="14" max="14" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="5" customWidth="1"/>
-    <col min="18" max="18" width="6.84375" customWidth="1"/>
-    <col min="19" max="19" width="7.3828125" customWidth="1"/>
-    <col min="20" max="20" width="4.3046875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.69140625" customWidth="1"/>
-    <col min="22" max="22" width="6.3828125" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" customWidth="1"/>
+    <col min="19" max="19" width="7.42578125" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.7109375" customWidth="1"/>
+    <col min="22" max="22" width="6.42578125" customWidth="1"/>
     <col min="23" max="23" width="8" customWidth="1"/>
-    <col min="24" max="24" width="8.69140625" customWidth="1"/>
+    <col min="24" max="24" width="8.7109375" customWidth="1"/>
     <col min="25" max="25" width="3" style="42" customWidth="1"/>
-    <col min="26" max="26" width="6.84375" customWidth="1"/>
-    <col min="27" max="27" width="3.3828125" style="42" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" customWidth="1"/>
-    <col min="29" max="29" width="3.15234375" style="42" customWidth="1"/>
-    <col min="30" max="30" width="5.53515625" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" customWidth="1"/>
+    <col min="27" max="27" width="3.42578125" style="42" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" customWidth="1"/>
+    <col min="29" max="29" width="3.140625" style="42" customWidth="1"/>
+    <col min="30" max="30" width="5.5703125" customWidth="1"/>
     <col min="31" max="31" width="3" style="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:31" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -15934,7 +16407,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A2" s="53">
         <v>2</v>
       </c>
@@ -16029,7 +16502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A3" s="53">
         <v>3</v>
       </c>
@@ -16124,7 +16597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A4" s="53">
         <v>4</v>
       </c>
@@ -16219,7 +16692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A5" s="53">
         <v>5</v>
       </c>
@@ -16314,7 +16787,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A6" s="53">
         <v>6</v>
       </c>
@@ -16409,7 +16882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A7" s="53">
         <v>7</v>
       </c>
@@ -16504,7 +16977,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A8" s="53">
         <v>8</v>
       </c>
@@ -16599,7 +17072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A9" s="53">
         <v>9</v>
       </c>
@@ -16694,7 +17167,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="50" customFormat="1" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" s="50" customFormat="1" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A10" s="53">
         <v>10</v>
       </c>

--- a/Versão5/ARQ/Ontologia_Circulacao.xlsx
+++ b/Versão5/ARQ/Ontologia_Circulacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DF2EA9-9CED-49E2-853A-5A06303034BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE3D29C-2AB3-404D-B926-697B2C95C609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2938" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="726">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2199,9 +2199,6 @@
     <t>Define a Helper Role in an application</t>
   </si>
   <si>
-    <t>Interdisciplinar</t>
-  </si>
-  <si>
     <t>Função.Global</t>
   </si>
   <si>
@@ -2251,6 +2248,9 @@
   </si>
   <si>
     <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -2581,7 +2581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2770,50 +2770,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <b val="0"/>
@@ -2925,6 +2886,24 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3646,7 +3625,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46268.51357638889</v>
+        <v>46268.689674652778</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>172</v>
@@ -3727,7 +3706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
-  <dimension ref="A1:AC125"/>
+  <dimension ref="A1:AD125"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.140625" style="42" bestFit="1" customWidth="1"/>
@@ -3754,10 +3733,11 @@
     <col min="27" max="27" width="21.140625" style="40" customWidth="1"/>
     <col min="28" max="28" width="6.85546875" style="40" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="10.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="40"/>
+    <col min="30" max="30" width="6.85546875" style="40" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="63" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:30" s="63" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="60">
         <v>1</v>
       </c>
@@ -3845,8 +3825,11 @@
       <c r="AC1" s="49" t="s">
         <v>698</v>
       </c>
+      <c r="AD1" s="33" t="s">
+        <v>725</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="41">
         <v>2</v>
       </c>
@@ -3942,8 +3925,11 @@
       <c r="AC2" s="27" t="s">
         <v>9</v>
       </c>
+      <c r="AD2" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41">
         <v>3</v>
       </c>
@@ -4039,8 +4025,11 @@
       <c r="AC3" s="45" t="s">
         <v>441</v>
       </c>
+      <c r="AD3" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>4</v>
       </c>
@@ -4136,8 +4125,11 @@
       <c r="AC4" s="45" t="s">
         <v>441</v>
       </c>
+      <c r="AD4" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="41">
         <v>5</v>
       </c>
@@ -4233,8 +4225,11 @@
       <c r="AC5" s="45" t="s">
         <v>441</v>
       </c>
+      <c r="AD5" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="41">
         <v>6</v>
       </c>
@@ -4330,8 +4325,11 @@
       <c r="AC6" s="45" t="s">
         <v>441</v>
       </c>
+      <c r="AD6" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>7</v>
       </c>
@@ -4427,8 +4425,11 @@
       <c r="AC7" s="45" t="s">
         <v>441</v>
       </c>
+      <c r="AD7" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="41">
         <v>8</v>
       </c>
@@ -4524,8 +4525,11 @@
       <c r="AC8" s="45" t="s">
         <v>450</v>
       </c>
+      <c r="AD8" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="41">
         <v>9</v>
       </c>
@@ -4621,8 +4625,11 @@
       <c r="AC9" s="45" t="s">
         <v>450</v>
       </c>
+      <c r="AD9" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41">
         <v>10</v>
       </c>
@@ -4718,8 +4725,11 @@
       <c r="AC10" s="45" t="s">
         <v>450</v>
       </c>
+      <c r="AD10" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="41">
         <v>11</v>
       </c>
@@ -4815,8 +4825,11 @@
       <c r="AC11" s="45" t="s">
         <v>462</v>
       </c>
+      <c r="AD11" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="41">
         <v>12</v>
       </c>
@@ -4912,8 +4925,11 @@
       <c r="AC12" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD12" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="41">
         <v>13</v>
       </c>
@@ -5009,8 +5025,11 @@
       <c r="AC13" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD13" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="41">
         <v>14</v>
       </c>
@@ -5106,8 +5125,11 @@
       <c r="AC14" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD14" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="15" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="41">
         <v>15</v>
       </c>
@@ -5203,8 +5225,11 @@
       <c r="AC15" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD15" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="16" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>16</v>
       </c>
@@ -5300,8 +5325,11 @@
       <c r="AC16" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD16" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="17" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="41">
         <v>17</v>
       </c>
@@ -5397,8 +5425,11 @@
       <c r="AC17" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD17" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="18" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>18</v>
       </c>
@@ -5494,8 +5525,11 @@
       <c r="AC18" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD18" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="41">
         <v>19</v>
       </c>
@@ -5591,8 +5625,11 @@
       <c r="AC19" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD19" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="20" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="41">
         <v>20</v>
       </c>
@@ -5688,8 +5725,11 @@
       <c r="AC20" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD20" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="21" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="41">
         <v>21</v>
       </c>
@@ -5785,8 +5825,11 @@
       <c r="AC21" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD21" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="22" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <v>22</v>
       </c>
@@ -5882,8 +5925,11 @@
       <c r="AC22" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD22" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="23" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="41">
         <v>23</v>
       </c>
@@ -5979,8 +6025,11 @@
       <c r="AC23" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD23" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="24" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>24</v>
       </c>
@@ -6076,8 +6125,11 @@
       <c r="AC24" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD24" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="25" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>25</v>
       </c>
@@ -6173,8 +6225,11 @@
       <c r="AC25" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD25" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="26" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>26</v>
       </c>
@@ -6270,8 +6325,11 @@
       <c r="AC26" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD26" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="27" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="41">
         <v>27</v>
       </c>
@@ -6367,8 +6425,11 @@
       <c r="AC27" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD27" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="28" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>28</v>
       </c>
@@ -6464,8 +6525,11 @@
       <c r="AC28" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD28" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="29" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="41">
         <v>29</v>
       </c>
@@ -6561,8 +6625,11 @@
       <c r="AC29" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD29" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="30" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>30</v>
       </c>
@@ -6658,8 +6725,11 @@
       <c r="AC30" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD30" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="31" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="41">
         <v>31</v>
       </c>
@@ -6755,8 +6825,11 @@
       <c r="AC31" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD31" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="32" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>32</v>
       </c>
@@ -6852,8 +6925,11 @@
       <c r="AC32" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD32" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="33" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="41">
         <v>33</v>
       </c>
@@ -6949,8 +7025,11 @@
       <c r="AC33" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD33" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="34" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="41">
         <v>34</v>
       </c>
@@ -7046,8 +7125,11 @@
       <c r="AC34" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD34" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="35" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="41">
         <v>35</v>
       </c>
@@ -7143,8 +7225,11 @@
       <c r="AC35" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD35" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="41">
         <v>36</v>
       </c>
@@ -7240,8 +7325,11 @@
       <c r="AC36" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD36" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="37" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="41">
         <v>37</v>
       </c>
@@ -7337,8 +7425,11 @@
       <c r="AC37" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD37" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="38" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="41">
         <v>38</v>
       </c>
@@ -7434,8 +7525,11 @@
       <c r="AC38" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD38" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="39" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="41">
         <v>39</v>
       </c>
@@ -7531,8 +7625,11 @@
       <c r="AC39" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD39" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="40" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="41">
         <v>40</v>
       </c>
@@ -7628,8 +7725,11 @@
       <c r="AC40" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD40" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="41" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="41">
         <v>41</v>
       </c>
@@ -7725,8 +7825,11 @@
       <c r="AC41" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD41" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="42" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="41">
         <v>42</v>
       </c>
@@ -7822,8 +7925,11 @@
       <c r="AC42" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD42" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="43" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="41">
         <v>43</v>
       </c>
@@ -7919,8 +8025,11 @@
       <c r="AC43" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD43" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="44" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="41">
         <v>44</v>
       </c>
@@ -8016,8 +8125,11 @@
       <c r="AC44" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD44" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="41">
         <v>45</v>
       </c>
@@ -8113,8 +8225,11 @@
       <c r="AC45" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD45" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="46" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="41">
         <v>46</v>
       </c>
@@ -8210,8 +8325,11 @@
       <c r="AC46" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD46" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="47" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="41">
         <v>47</v>
       </c>
@@ -8307,8 +8425,11 @@
       <c r="AC47" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD47" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="48" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="41">
         <v>48</v>
       </c>
@@ -8404,8 +8525,11 @@
       <c r="AC48" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD48" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="49" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="41">
         <v>49</v>
       </c>
@@ -8501,8 +8625,11 @@
       <c r="AC49" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD49" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="50" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="41">
         <v>50</v>
       </c>
@@ -8598,8 +8725,11 @@
       <c r="AC50" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD50" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="51" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="41">
         <v>51</v>
       </c>
@@ -8695,8 +8825,11 @@
       <c r="AC51" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD51" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="52" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="41">
         <v>52</v>
       </c>
@@ -8792,8 +8925,11 @@
       <c r="AC52" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD52" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="53" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="41">
         <v>53</v>
       </c>
@@ -8889,8 +9025,11 @@
       <c r="AC53" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD53" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="54" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="41">
         <v>54</v>
       </c>
@@ -8986,8 +9125,11 @@
       <c r="AC54" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD54" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="55" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="41">
         <v>55</v>
       </c>
@@ -9083,8 +9225,11 @@
       <c r="AC55" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD55" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="56" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="41">
         <v>56</v>
       </c>
@@ -9180,8 +9325,11 @@
       <c r="AC56" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD56" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="57" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="41">
         <v>57</v>
       </c>
@@ -9277,8 +9425,11 @@
       <c r="AC57" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD57" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="58" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="41">
         <v>58</v>
       </c>
@@ -9374,8 +9525,11 @@
       <c r="AC58" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD58" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="59" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="41">
         <v>59</v>
       </c>
@@ -9471,8 +9625,11 @@
       <c r="AC59" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD59" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="60" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="41">
         <v>60</v>
       </c>
@@ -9568,8 +9725,11 @@
       <c r="AC60" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD60" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="61" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="41">
         <v>61</v>
       </c>
@@ -9665,8 +9825,11 @@
       <c r="AC61" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD61" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="62" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="41">
         <v>62</v>
       </c>
@@ -9762,8 +9925,11 @@
       <c r="AC62" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD62" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="63" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="41">
         <v>63</v>
       </c>
@@ -9859,8 +10025,11 @@
       <c r="AC63" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD63" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="64" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="41">
         <v>64</v>
       </c>
@@ -9956,8 +10125,11 @@
       <c r="AC64" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD64" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="65" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="41">
         <v>65</v>
       </c>
@@ -10053,8 +10225,11 @@
       <c r="AC65" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD65" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="66" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="41">
         <v>66</v>
       </c>
@@ -10132,7 +10307,7 @@
         <v>43</v>
       </c>
       <c r="X66" s="43" t="str">
-        <f t="shared" ref="X66:X121" si="30">CONCATENATE("Key-CIRCU-",A66)</f>
+        <f t="shared" ref="X66:X120" si="30">CONCATENATE("Key-CIRCU-",A66)</f>
         <v>Key-CIRCU-66</v>
       </c>
       <c r="Y66" s="27" t="s">
@@ -10150,8 +10325,11 @@
       <c r="AC66" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD66" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="67" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="41">
         <v>67</v>
       </c>
@@ -10247,8 +10425,11 @@
       <c r="AC67" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD67" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="68" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="41">
         <v>68</v>
       </c>
@@ -10344,8 +10525,11 @@
       <c r="AC68" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD68" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="69" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="41">
         <v>69</v>
       </c>
@@ -10441,8 +10625,11 @@
       <c r="AC69" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD69" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="70" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="41">
         <v>70</v>
       </c>
@@ -10538,8 +10725,11 @@
       <c r="AC70" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD70" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="71" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="41">
         <v>71</v>
       </c>
@@ -10635,8 +10825,11 @@
       <c r="AC71" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD71" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="72" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="41">
         <v>72</v>
       </c>
@@ -10732,8 +10925,11 @@
       <c r="AC72" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD72" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="73" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="41">
         <v>73</v>
       </c>
@@ -10829,8 +11025,11 @@
       <c r="AC73" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD73" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="74" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="41">
         <v>74</v>
       </c>
@@ -10926,8 +11125,11 @@
       <c r="AC74" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD74" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="75" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="41">
         <v>75</v>
       </c>
@@ -11023,8 +11225,11 @@
       <c r="AC75" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD75" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="76" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="41">
         <v>76</v>
       </c>
@@ -11120,8 +11325,11 @@
       <c r="AC76" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD76" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="77" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="41">
         <v>77</v>
       </c>
@@ -11217,8 +11425,11 @@
       <c r="AC77" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD77" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="78" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="41">
         <v>78</v>
       </c>
@@ -11314,8 +11525,11 @@
       <c r="AC78" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD78" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="79" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="41">
         <v>79</v>
       </c>
@@ -11411,8 +11625,11 @@
       <c r="AC79" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD79" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="80" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="41">
         <v>80</v>
       </c>
@@ -11508,8 +11725,11 @@
       <c r="AC80" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD80" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="81" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="41">
         <v>81</v>
       </c>
@@ -11605,8 +11825,11 @@
       <c r="AC81" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD81" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="82" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="41">
         <v>82</v>
       </c>
@@ -11702,8 +11925,11 @@
       <c r="AC82" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD82" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="83" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="41">
         <v>83</v>
       </c>
@@ -11799,8 +12025,11 @@
       <c r="AC83" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD83" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="84" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="41">
         <v>84</v>
       </c>
@@ -11896,8 +12125,11 @@
       <c r="AC84" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD84" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="85" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="41">
         <v>85</v>
       </c>
@@ -11993,8 +12225,11 @@
       <c r="AC85" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD85" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="86" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="41">
         <v>86</v>
       </c>
@@ -12090,8 +12325,11 @@
       <c r="AC86" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD86" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="87" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="41">
         <v>87</v>
       </c>
@@ -12187,8 +12425,11 @@
       <c r="AC87" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD87" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="88" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="41">
         <v>88</v>
       </c>
@@ -12284,8 +12525,11 @@
       <c r="AC88" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD88" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="89" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="41">
         <v>89</v>
       </c>
@@ -12381,8 +12625,11 @@
       <c r="AC89" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD89" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="90" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="41">
         <v>90</v>
       </c>
@@ -12478,8 +12725,11 @@
       <c r="AC90" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD90" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="91" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="41">
         <v>91</v>
       </c>
@@ -12575,8 +12825,11 @@
       <c r="AC91" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD91" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="92" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="41">
         <v>92</v>
       </c>
@@ -12672,8 +12925,11 @@
       <c r="AC92" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD92" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="93" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="41">
         <v>93</v>
       </c>
@@ -12769,8 +13025,11 @@
       <c r="AC93" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD93" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="94" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="41">
         <v>94</v>
       </c>
@@ -12866,8 +13125,11 @@
       <c r="AC94" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD94" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="95" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="41">
         <v>95</v>
       </c>
@@ -12963,8 +13225,11 @@
       <c r="AC95" s="45" t="s">
         <v>579</v>
       </c>
+      <c r="AD95" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="96" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="41">
         <v>96</v>
       </c>
@@ -13060,8 +13325,11 @@
       <c r="AC96" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD96" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="97" spans="1:29" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="41">
         <v>97</v>
       </c>
@@ -13157,8 +13425,11 @@
       <c r="AC97" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD97" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="98" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="41">
         <v>98</v>
       </c>
@@ -13254,8 +13525,11 @@
       <c r="AC98" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD98" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="99" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="41">
         <v>99</v>
       </c>
@@ -13351,8 +13625,11 @@
       <c r="AC99" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD99" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="100" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="41">
         <v>100</v>
       </c>
@@ -13448,8 +13725,11 @@
       <c r="AC100" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD100" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="101" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="41">
         <v>101</v>
       </c>
@@ -13545,8 +13825,11 @@
       <c r="AC101" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD101" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="102" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="41">
         <v>102</v>
       </c>
@@ -13642,8 +13925,11 @@
       <c r="AC102" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD102" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="103" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="41">
         <v>103</v>
       </c>
@@ -13739,8 +14025,11 @@
       <c r="AC103" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD103" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="104" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="41">
         <v>104</v>
       </c>
@@ -13836,8 +14125,11 @@
       <c r="AC104" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD104" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="105" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="41">
         <v>105</v>
       </c>
@@ -13933,8 +14225,11 @@
       <c r="AC105" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD105" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="106" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="41">
         <v>106</v>
       </c>
@@ -14030,8 +14325,11 @@
       <c r="AC106" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD106" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="107" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="41">
         <v>107</v>
       </c>
@@ -14127,8 +14425,11 @@
       <c r="AC107" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD107" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="108" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="41">
         <v>108</v>
       </c>
@@ -14224,8 +14525,11 @@
       <c r="AC108" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD108" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="109" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="41">
         <v>109</v>
       </c>
@@ -14321,8 +14625,11 @@
       <c r="AC109" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD109" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="110" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="41">
         <v>110</v>
       </c>
@@ -14418,8 +14725,11 @@
       <c r="AC110" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD110" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="111" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="41">
         <v>111</v>
       </c>
@@ -14515,8 +14825,11 @@
       <c r="AC111" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD111" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="112" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="41">
         <v>112</v>
       </c>
@@ -14612,8 +14925,11 @@
       <c r="AC112" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD112" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="113" spans="1:29" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:30" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="41">
         <v>113</v>
       </c>
@@ -14709,8 +15025,11 @@
       <c r="AC113" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD113" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="114" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:30" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="41">
         <v>114</v>
       </c>
@@ -14807,8 +15126,11 @@
       <c r="AC114" s="45" t="s">
         <v>9</v>
       </c>
+      <c r="AD114" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="115" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:30" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="41">
         <v>115</v>
       </c>
@@ -14905,8 +15227,11 @@
       <c r="AC115" s="45" t="s">
         <v>9</v>
       </c>
+      <c r="AD115" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="116" spans="1:29" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:30" s="46" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="41">
         <v>116</v>
       </c>
@@ -15003,8 +15328,11 @@
       <c r="AC116" s="45" t="s">
         <v>9</v>
       </c>
+      <c r="AD116" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="117" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:30" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="41">
         <v>117</v>
       </c>
@@ -15101,8 +15429,11 @@
       <c r="AC117" s="45" t="s">
         <v>578</v>
       </c>
+      <c r="AD117" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="118" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:30" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="41">
         <v>118</v>
       </c>
@@ -15199,8 +15530,11 @@
       <c r="AC118" s="45" t="s">
         <v>450</v>
       </c>
+      <c r="AD118" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="119" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:30" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="41">
         <v>119</v>
       </c>
@@ -15297,8 +15631,11 @@
       <c r="AC119" s="45" t="s">
         <v>450</v>
       </c>
+      <c r="AD119" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="120" spans="1:29" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:30" s="46" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="41">
         <v>120</v>
       </c>
@@ -15395,8 +15732,11 @@
       <c r="AC120" s="45" t="s">
         <v>580</v>
       </c>
+      <c r="AD120" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="121" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="41">
         <v>121</v>
       </c>
@@ -15471,11 +15811,11 @@
         <v>Métodos</v>
       </c>
       <c r="W121" s="27" t="s">
-        <v>708</v>
-      </c>
-      <c r="X121" s="70" t="str">
-        <f t="shared" ref="X121:X125" si="42">CONCATENATE("Key-ABNT-",A121)</f>
-        <v>Key-ABNT-121</v>
+        <v>43</v>
+      </c>
+      <c r="X121" s="43" t="str">
+        <f t="shared" ref="X121:X125" si="42">CONCATENATE("Key-CIRCU-",A121)</f>
+        <v>Key-CIRCU-121</v>
       </c>
       <c r="Y121" s="68" t="s">
         <v>9</v>
@@ -15492,8 +15832,11 @@
       <c r="AC121" s="68" t="s">
         <v>9</v>
       </c>
+      <c r="AD121" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="122" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="41">
         <v>122</v>
       </c>
@@ -15510,7 +15853,7 @@
         <v>702</v>
       </c>
       <c r="F122" s="44" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G122" s="67" t="s">
         <v>9</v>
@@ -15544,13 +15887,13 @@
         <v>Função Global</v>
       </c>
       <c r="P122" s="27" t="s">
+        <v>709</v>
+      </c>
+      <c r="Q122" s="27" t="s">
         <v>710</v>
       </c>
-      <c r="Q122" s="27" t="s">
+      <c r="R122" s="27" t="s">
         <v>711</v>
-      </c>
-      <c r="R122" s="27" t="s">
-        <v>712</v>
       </c>
       <c r="S122" s="27" t="s">
         <v>9</v>
@@ -15568,11 +15911,11 @@
         <v>Métodos</v>
       </c>
       <c r="W122" s="27" t="s">
-        <v>708</v>
-      </c>
-      <c r="X122" s="70" t="str">
+        <v>43</v>
+      </c>
+      <c r="X122" s="43" t="str">
         <f t="shared" si="42"/>
-        <v>Key-ABNT-122</v>
+        <v>Key-CIRCU-122</v>
       </c>
       <c r="Y122" s="68" t="s">
         <v>9</v>
@@ -15589,8 +15932,11 @@
       <c r="AC122" s="68" t="s">
         <v>9</v>
       </c>
+      <c r="AD122" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="123" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="41">
         <v>123</v>
       </c>
@@ -15607,7 +15953,7 @@
         <v>702</v>
       </c>
       <c r="F123" s="44" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="G123" s="67" t="s">
         <v>9</v>
@@ -15641,13 +15987,13 @@
         <v>Função Local</v>
       </c>
       <c r="P123" s="27" t="s">
+        <v>713</v>
+      </c>
+      <c r="Q123" s="27" t="s">
         <v>714</v>
       </c>
-      <c r="Q123" s="27" t="s">
+      <c r="R123" s="27" t="s">
         <v>715</v>
-      </c>
-      <c r="R123" s="27" t="s">
-        <v>716</v>
       </c>
       <c r="S123" s="27" t="s">
         <v>9</v>
@@ -15665,11 +16011,11 @@
         <v>Métodos</v>
       </c>
       <c r="W123" s="27" t="s">
-        <v>708</v>
-      </c>
-      <c r="X123" s="70" t="str">
+        <v>43</v>
+      </c>
+      <c r="X123" s="43" t="str">
         <f t="shared" si="42"/>
-        <v>Key-ABNT-123</v>
+        <v>Key-CIRCU-123</v>
       </c>
       <c r="Y123" s="68" t="s">
         <v>9</v>
@@ -15686,8 +16032,11 @@
       <c r="AC123" s="68" t="s">
         <v>9</v>
       </c>
+      <c r="AD123" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="124" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="41">
         <v>124</v>
       </c>
@@ -15704,7 +16053,7 @@
         <v>702</v>
       </c>
       <c r="F124" s="44" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G124" s="67" t="s">
         <v>9</v>
@@ -15738,13 +16087,13 @@
         <v>Função Filtro</v>
       </c>
       <c r="P124" s="27" t="s">
+        <v>717</v>
+      </c>
+      <c r="Q124" s="27" t="s">
         <v>718</v>
       </c>
-      <c r="Q124" s="27" t="s">
+      <c r="R124" s="27" t="s">
         <v>719</v>
-      </c>
-      <c r="R124" s="27" t="s">
-        <v>720</v>
       </c>
       <c r="S124" s="27" t="s">
         <v>9</v>
@@ -15762,11 +16111,11 @@
         <v>Métodos</v>
       </c>
       <c r="W124" s="27" t="s">
-        <v>708</v>
-      </c>
-      <c r="X124" s="70" t="str">
+        <v>43</v>
+      </c>
+      <c r="X124" s="43" t="str">
         <f t="shared" si="42"/>
-        <v>Key-ABNT-124</v>
+        <v>Key-CIRCU-124</v>
       </c>
       <c r="Y124" s="68" t="s">
         <v>9</v>
@@ -15783,8 +16132,11 @@
       <c r="AC124" s="68" t="s">
         <v>9</v>
       </c>
+      <c r="AD124" s="68" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="125" spans="1:29" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="41">
         <v>125</v>
       </c>
@@ -15798,10 +16150,10 @@
         <v>703</v>
       </c>
       <c r="E125" s="44" t="s">
+        <v>720</v>
+      </c>
+      <c r="F125" s="44" t="s">
         <v>721</v>
-      </c>
-      <c r="F125" s="44" t="s">
-        <v>722</v>
       </c>
       <c r="G125" s="67" t="s">
         <v>9</v>
@@ -15835,13 +16187,13 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P125" s="27" t="s">
+        <v>722</v>
+      </c>
+      <c r="Q125" s="27" t="s">
         <v>723</v>
       </c>
-      <c r="Q125" s="27" t="s">
+      <c r="R125" s="27" t="s">
         <v>724</v>
-      </c>
-      <c r="R125" s="27" t="s">
-        <v>725</v>
       </c>
       <c r="S125" s="27" t="s">
         <v>9</v>
@@ -15859,11 +16211,11 @@
         <v>Códigos Visuais</v>
       </c>
       <c r="W125" s="27" t="s">
-        <v>708</v>
-      </c>
-      <c r="X125" s="70" t="str">
+        <v>43</v>
+      </c>
+      <c r="X125" s="43" t="str">
         <f t="shared" si="42"/>
-        <v>Key-ABNT-125</v>
+        <v>Key-CIRCU-125</v>
       </c>
       <c r="Y125" s="68" t="s">
         <v>9</v>
@@ -15878,6 +16230,9 @@
         <v>9</v>
       </c>
       <c r="AC125" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD125" s="68" t="s">
         <v>9</v>
       </c>
     </row>
@@ -15885,87 +16240,87 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AC120">
     <sortCondition ref="E1:E120"/>
   </sortState>
+  <conditionalFormatting sqref="B121:B125">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B2:E2 P2:Q4 W2:W4">
-    <cfRule type="cellIs" dxfId="25" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:E3 D4:E4">
-    <cfRule type="cellIs" dxfId="24" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D47 E11:E53">
-    <cfRule type="cellIs" dxfId="23" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="90" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E10">
-    <cfRule type="cellIs" dxfId="22" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="58" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68:E116">
-    <cfRule type="cellIs" dxfId="21" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E67 D65:D67">
-    <cfRule type="cellIs" dxfId="20" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E125:F125">
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F114:F116">
-    <cfRule type="duplicateValues" dxfId="19" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117:F120 F1:F113 F126:F1048576">
-    <cfRule type="duplicateValues" dxfId="18" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121:F124">
+    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L117:Q120 T117:V120">
-    <cfRule type="cellIs" dxfId="16" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q8 AA7:AA8">
-    <cfRule type="cellIs" dxfId="15" priority="138" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="138" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R120">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA117">
-    <cfRule type="cellIs" dxfId="13" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA119:AA120">
-    <cfRule type="cellIs" dxfId="12" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1">
-    <cfRule type="cellIs" dxfId="11" priority="137" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="137" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:XFD4 AA3:AA4 AC3:AC4 B3:B113 C4:C113 W6:W120 AD7:XFD8 P15:Q113 AA15:AA113 AD15:XFD113 D48:E64 B114:C116 B117:E120 AD117:XFD120 A2:A125">
-    <cfRule type="cellIs" dxfId="0" priority="31" operator="equal">
+  <conditionalFormatting sqref="AE2:XFD4 A2:A125 AA3:AA4 AC3:AC4 B3:B113 C4:C113 AE7:XFD8 P15:Q113 AA15:AA113 AE15:XFD113 D48:E64 B114:C116 B117:E120 AE117:XFD120 W6:W125">
+    <cfRule type="cellIs" dxfId="7" priority="31" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B121:B125">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E125:F125">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F121:F124">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16179,7 +16534,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16254,22 +16609,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="8" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ARQ/Ontologia_Circulacao.xlsx
+++ b/Versão5/ARQ/Ontologia_Circulacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ARQ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE3D29C-2AB3-404D-B926-697B2C95C609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C817B3-4F89-49D8-A0AF-0909087F1E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3063" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3098" uniqueCount="738">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -2178,15 +2178,6 @@
     <t>[ OST_PathOfTravelLines ]</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>Função.Auxiliar</t>
   </si>
   <si>
@@ -2235,9 +2226,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -2251,6 +2239,54 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API Método</t>
+  </si>
+  <si>
+    <t>Função Auxiliar</t>
+  </si>
+  <si>
+    <t>API Plataforma</t>
+  </si>
+  <si>
+    <t>API Macros</t>
+  </si>
+  <si>
+    <t>Função Global</t>
+  </si>
+  <si>
+    <t>Função Local</t>
+  </si>
+  <si>
+    <t>Função Filtro</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>API Método Visual</t>
+  </si>
+  <si>
+    <t>Bloco de Código</t>
+  </si>
+  <si>
+    <t>API Macros Visuais</t>
   </si>
 </sst>
 </file>
@@ -2581,7 +2617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2767,14 +2803,59 @@
     <xf numFmtId="0" fontId="4" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2837,14 +2918,6 @@
         <i/>
         <strike val="0"/>
         <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -3625,7 +3698,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46268.689674652778</v>
+        <v>46273.517850810182</v>
       </c>
       <c r="C18" s="38" t="s">
         <v>172</v>
@@ -3723,7 +3796,7 @@
     <col min="16" max="16" width="112.85546875" style="40" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="111.7109375" style="40" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="98.28515625" style="40" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.42578125" style="72" customWidth="1"/>
     <col min="20" max="20" width="8.7109375" style="40" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="13.7109375" style="40" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.5703125" style="40" bestFit="1" customWidth="1"/>
@@ -3792,7 +3865,7 @@
       <c r="R1" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="S1" s="49" t="s">
+      <c r="S1" s="71" t="s">
         <v>102</v>
       </c>
       <c r="T1" s="34" t="s">
@@ -3826,7 +3899,7 @@
         <v>698</v>
       </c>
       <c r="AD1" s="33" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3888,7 +3961,7 @@
       <c r="R2" s="27" t="s">
         <v>592</v>
       </c>
-      <c r="S2" s="45" t="s">
+      <c r="S2" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T2" s="27" t="str">
@@ -3988,7 +4061,7 @@
       <c r="R3" s="27" t="s">
         <v>593</v>
       </c>
-      <c r="S3" s="45" t="s">
+      <c r="S3" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T3" s="27" t="str">
@@ -4088,7 +4161,7 @@
       <c r="R4" s="27" t="s">
         <v>594</v>
       </c>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T4" s="27" t="str">
@@ -4188,7 +4261,7 @@
       <c r="R5" s="27" t="s">
         <v>595</v>
       </c>
-      <c r="S5" s="45" t="s">
+      <c r="S5" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T5" s="27" t="str">
@@ -4288,7 +4361,7 @@
       <c r="R6" s="27" t="s">
         <v>596</v>
       </c>
-      <c r="S6" s="45" t="s">
+      <c r="S6" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T6" s="27" t="str">
@@ -4388,7 +4461,7 @@
       <c r="R7" s="27" t="s">
         <v>597</v>
       </c>
-      <c r="S7" s="45" t="s">
+      <c r="S7" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T7" s="27" t="str">
@@ -4488,7 +4561,7 @@
       <c r="R8" s="27" t="s">
         <v>598</v>
       </c>
-      <c r="S8" s="45" t="s">
+      <c r="S8" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T8" s="27" t="str">
@@ -4588,7 +4661,7 @@
       <c r="R9" s="27" t="s">
         <v>599</v>
       </c>
-      <c r="S9" s="45" t="s">
+      <c r="S9" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T9" s="27" t="str">
@@ -4688,7 +4761,7 @@
       <c r="R10" s="27" t="s">
         <v>600</v>
       </c>
-      <c r="S10" s="45" t="s">
+      <c r="S10" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T10" s="27" t="str">
@@ -4788,7 +4861,7 @@
       <c r="R11" s="27" t="s">
         <v>601</v>
       </c>
-      <c r="S11" s="45" t="s">
+      <c r="S11" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T11" s="27" t="str">
@@ -4888,7 +4961,7 @@
       <c r="R12" s="27" t="s">
         <v>602</v>
       </c>
-      <c r="S12" s="45" t="s">
+      <c r="S12" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T12" s="27" t="str">
@@ -4988,7 +5061,7 @@
       <c r="R13" s="27" t="s">
         <v>603</v>
       </c>
-      <c r="S13" s="45" t="s">
+      <c r="S13" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T13" s="27" t="str">
@@ -5088,7 +5161,7 @@
       <c r="R14" s="27" t="s">
         <v>604</v>
       </c>
-      <c r="S14" s="45" t="s">
+      <c r="S14" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T14" s="27" t="str">
@@ -5188,7 +5261,7 @@
       <c r="R15" s="27" t="s">
         <v>605</v>
       </c>
-      <c r="S15" s="45" t="s">
+      <c r="S15" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T15" s="27" t="str">
@@ -5288,7 +5361,7 @@
       <c r="R16" s="27" t="s">
         <v>606</v>
       </c>
-      <c r="S16" s="45" t="s">
+      <c r="S16" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T16" s="27" t="str">
@@ -5388,7 +5461,7 @@
       <c r="R17" s="27" t="s">
         <v>607</v>
       </c>
-      <c r="S17" s="45" t="s">
+      <c r="S17" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T17" s="27" t="str">
@@ -5488,7 +5561,7 @@
       <c r="R18" s="27" t="s">
         <v>608</v>
       </c>
-      <c r="S18" s="45" t="s">
+      <c r="S18" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T18" s="27" t="str">
@@ -5588,7 +5661,7 @@
       <c r="R19" s="27" t="s">
         <v>609</v>
       </c>
-      <c r="S19" s="45" t="s">
+      <c r="S19" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T19" s="27" t="str">
@@ -5688,7 +5761,7 @@
       <c r="R20" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="S20" s="45" t="s">
+      <c r="S20" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T20" s="27" t="str">
@@ -5788,7 +5861,7 @@
       <c r="R21" s="27" t="s">
         <v>611</v>
       </c>
-      <c r="S21" s="45" t="s">
+      <c r="S21" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T21" s="27" t="str">
@@ -5888,7 +5961,7 @@
       <c r="R22" s="27" t="s">
         <v>612</v>
       </c>
-      <c r="S22" s="45" t="s">
+      <c r="S22" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T22" s="27" t="str">
@@ -5988,7 +6061,7 @@
       <c r="R23" s="27" t="s">
         <v>613</v>
       </c>
-      <c r="S23" s="45" t="s">
+      <c r="S23" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T23" s="27" t="str">
@@ -6088,7 +6161,7 @@
       <c r="R24" s="27" t="s">
         <v>614</v>
       </c>
-      <c r="S24" s="45" t="s">
+      <c r="S24" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T24" s="27" t="str">
@@ -6188,7 +6261,7 @@
       <c r="R25" s="27" t="s">
         <v>615</v>
       </c>
-      <c r="S25" s="45" t="s">
+      <c r="S25" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T25" s="27" t="str">
@@ -6288,7 +6361,7 @@
       <c r="R26" s="27" t="s">
         <v>616</v>
       </c>
-      <c r="S26" s="45" t="s">
+      <c r="S26" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T26" s="27" t="str">
@@ -6388,7 +6461,7 @@
       <c r="R27" s="27" t="s">
         <v>617</v>
       </c>
-      <c r="S27" s="45" t="s">
+      <c r="S27" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T27" s="27" t="str">
@@ -6488,7 +6561,7 @@
       <c r="R28" s="27" t="s">
         <v>618</v>
       </c>
-      <c r="S28" s="45" t="s">
+      <c r="S28" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T28" s="27" t="str">
@@ -6588,7 +6661,7 @@
       <c r="R29" s="27" t="s">
         <v>619</v>
       </c>
-      <c r="S29" s="45" t="s">
+      <c r="S29" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T29" s="27" t="str">
@@ -6688,7 +6761,7 @@
       <c r="R30" s="27" t="s">
         <v>620</v>
       </c>
-      <c r="S30" s="45" t="s">
+      <c r="S30" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T30" s="27" t="str">
@@ -6788,7 +6861,7 @@
       <c r="R31" s="27" t="s">
         <v>621</v>
       </c>
-      <c r="S31" s="45" t="s">
+      <c r="S31" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T31" s="27" t="str">
@@ -6888,7 +6961,7 @@
       <c r="R32" s="27" t="s">
         <v>622</v>
       </c>
-      <c r="S32" s="45" t="s">
+      <c r="S32" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T32" s="27" t="str">
@@ -6988,7 +7061,7 @@
       <c r="R33" s="27" t="s">
         <v>623</v>
       </c>
-      <c r="S33" s="45" t="s">
+      <c r="S33" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T33" s="27" t="str">
@@ -7088,7 +7161,7 @@
       <c r="R34" s="27" t="s">
         <v>624</v>
       </c>
-      <c r="S34" s="45" t="s">
+      <c r="S34" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T34" s="27" t="str">
@@ -7188,7 +7261,7 @@
       <c r="R35" s="27" t="s">
         <v>625</v>
       </c>
-      <c r="S35" s="45" t="s">
+      <c r="S35" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T35" s="27" t="str">
@@ -7288,7 +7361,7 @@
       <c r="R36" s="27" t="s">
         <v>626</v>
       </c>
-      <c r="S36" s="45" t="s">
+      <c r="S36" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T36" s="27" t="str">
@@ -7388,7 +7461,7 @@
       <c r="R37" s="27" t="s">
         <v>627</v>
       </c>
-      <c r="S37" s="45" t="s">
+      <c r="S37" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T37" s="27" t="str">
@@ -7488,7 +7561,7 @@
       <c r="R38" s="27" t="s">
         <v>628</v>
       </c>
-      <c r="S38" s="45" t="s">
+      <c r="S38" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T38" s="27" t="str">
@@ -7588,7 +7661,7 @@
       <c r="R39" s="27" t="s">
         <v>629</v>
       </c>
-      <c r="S39" s="45" t="s">
+      <c r="S39" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T39" s="27" t="str">
@@ -7688,7 +7761,7 @@
       <c r="R40" s="27" t="s">
         <v>630</v>
       </c>
-      <c r="S40" s="45" t="s">
+      <c r="S40" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T40" s="27" t="str">
@@ -7788,7 +7861,7 @@
       <c r="R41" s="27" t="s">
         <v>631</v>
       </c>
-      <c r="S41" s="45" t="s">
+      <c r="S41" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T41" s="27" t="str">
@@ -7888,7 +7961,7 @@
       <c r="R42" s="27" t="s">
         <v>632</v>
       </c>
-      <c r="S42" s="45" t="s">
+      <c r="S42" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T42" s="27" t="str">
@@ -7988,7 +8061,7 @@
       <c r="R43" s="27" t="s">
         <v>633</v>
       </c>
-      <c r="S43" s="45" t="s">
+      <c r="S43" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T43" s="27" t="str">
@@ -8088,7 +8161,7 @@
       <c r="R44" s="27" t="s">
         <v>634</v>
       </c>
-      <c r="S44" s="45" t="s">
+      <c r="S44" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T44" s="27" t="str">
@@ -8188,7 +8261,7 @@
       <c r="R45" s="27" t="s">
         <v>635</v>
       </c>
-      <c r="S45" s="45" t="s">
+      <c r="S45" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T45" s="27" t="str">
@@ -8288,7 +8361,7 @@
       <c r="R46" s="27" t="s">
         <v>636</v>
       </c>
-      <c r="S46" s="45" t="s">
+      <c r="S46" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T46" s="27" t="str">
@@ -8388,7 +8461,7 @@
       <c r="R47" s="27" t="s">
         <v>637</v>
       </c>
-      <c r="S47" s="45" t="s">
+      <c r="S47" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T47" s="27" t="str">
@@ -8488,7 +8561,7 @@
       <c r="R48" s="27" t="s">
         <v>638</v>
       </c>
-      <c r="S48" s="45" t="s">
+      <c r="S48" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T48" s="27" t="str">
@@ -8588,7 +8661,7 @@
       <c r="R49" s="27" t="s">
         <v>639</v>
       </c>
-      <c r="S49" s="45" t="s">
+      <c r="S49" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T49" s="27" t="str">
@@ -8688,7 +8761,7 @@
       <c r="R50" s="27" t="s">
         <v>640</v>
       </c>
-      <c r="S50" s="45" t="s">
+      <c r="S50" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T50" s="27" t="str">
@@ -8788,7 +8861,7 @@
       <c r="R51" s="27" t="s">
         <v>641</v>
       </c>
-      <c r="S51" s="45" t="s">
+      <c r="S51" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T51" s="27" t="str">
@@ -8888,7 +8961,7 @@
       <c r="R52" s="27" t="s">
         <v>642</v>
       </c>
-      <c r="S52" s="45" t="s">
+      <c r="S52" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T52" s="27" t="str">
@@ -8988,7 +9061,7 @@
       <c r="R53" s="27" t="s">
         <v>643</v>
       </c>
-      <c r="S53" s="45" t="s">
+      <c r="S53" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T53" s="27" t="str">
@@ -9088,7 +9161,7 @@
       <c r="R54" s="27" t="s">
         <v>644</v>
       </c>
-      <c r="S54" s="45" t="s">
+      <c r="S54" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T54" s="27" t="str">
@@ -9188,7 +9261,7 @@
       <c r="R55" s="27" t="s">
         <v>645</v>
       </c>
-      <c r="S55" s="45" t="s">
+      <c r="S55" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T55" s="27" t="str">
@@ -9288,7 +9361,7 @@
       <c r="R56" s="27" t="s">
         <v>604</v>
       </c>
-      <c r="S56" s="45" t="s">
+      <c r="S56" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T56" s="27" t="str">
@@ -9388,7 +9461,7 @@
       <c r="R57" s="27" t="s">
         <v>646</v>
       </c>
-      <c r="S57" s="45" t="s">
+      <c r="S57" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T57" s="27" t="str">
@@ -9488,7 +9561,7 @@
       <c r="R58" s="27" t="s">
         <v>647</v>
       </c>
-      <c r="S58" s="45" t="s">
+      <c r="S58" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T58" s="27" t="str">
@@ -9588,7 +9661,7 @@
       <c r="R59" s="27" t="s">
         <v>648</v>
       </c>
-      <c r="S59" s="45" t="s">
+      <c r="S59" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T59" s="27" t="str">
@@ -9688,7 +9761,7 @@
       <c r="R60" s="27" t="s">
         <v>649</v>
       </c>
-      <c r="S60" s="45" t="s">
+      <c r="S60" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T60" s="27" t="str">
@@ -9788,7 +9861,7 @@
       <c r="R61" s="27" t="s">
         <v>650</v>
       </c>
-      <c r="S61" s="45" t="s">
+      <c r="S61" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T61" s="27" t="str">
@@ -9888,7 +9961,7 @@
       <c r="R62" s="27" t="s">
         <v>651</v>
       </c>
-      <c r="S62" s="45" t="s">
+      <c r="S62" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T62" s="27" t="str">
@@ -9988,7 +10061,7 @@
       <c r="R63" s="27" t="s">
         <v>651</v>
       </c>
-      <c r="S63" s="45" t="s">
+      <c r="S63" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T63" s="27" t="str">
@@ -10088,7 +10161,7 @@
       <c r="R64" s="27" t="s">
         <v>652</v>
       </c>
-      <c r="S64" s="45" t="s">
+      <c r="S64" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T64" s="27" t="str">
@@ -10188,7 +10261,7 @@
       <c r="R65" s="27" t="s">
         <v>652</v>
       </c>
-      <c r="S65" s="45" t="s">
+      <c r="S65" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T65" s="27" t="str">
@@ -10288,7 +10361,7 @@
       <c r="R66" s="27" t="s">
         <v>653</v>
       </c>
-      <c r="S66" s="45" t="s">
+      <c r="S66" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T66" s="27" t="str">
@@ -10307,7 +10380,7 @@
         <v>43</v>
       </c>
       <c r="X66" s="43" t="str">
-        <f t="shared" ref="X66:X120" si="30">CONCATENATE("Key-CIRCU-",A66)</f>
+        <f t="shared" ref="X66:X125" si="30">CONCATENATE("Key-CIRCU-",A66)</f>
         <v>Key-CIRCU-66</v>
       </c>
       <c r="Y66" s="27" t="s">
@@ -10388,7 +10461,7 @@
       <c r="R67" s="27" t="s">
         <v>654</v>
       </c>
-      <c r="S67" s="45" t="s">
+      <c r="S67" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T67" s="27" t="str">
@@ -10488,7 +10561,7 @@
       <c r="R68" s="27" t="s">
         <v>652</v>
       </c>
-      <c r="S68" s="45" t="s">
+      <c r="S68" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T68" s="27" t="str">
@@ -10588,7 +10661,7 @@
       <c r="R69" s="27" t="s">
         <v>652</v>
       </c>
-      <c r="S69" s="45" t="s">
+      <c r="S69" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T69" s="27" t="str">
@@ -10688,7 +10761,7 @@
       <c r="R70" s="27" t="s">
         <v>655</v>
       </c>
-      <c r="S70" s="45" t="s">
+      <c r="S70" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T70" s="27" t="str">
@@ -10788,7 +10861,7 @@
       <c r="R71" s="27" t="s">
         <v>656</v>
       </c>
-      <c r="S71" s="45" t="s">
+      <c r="S71" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T71" s="27" t="str">
@@ -10888,7 +10961,7 @@
       <c r="R72" s="27" t="s">
         <v>657</v>
       </c>
-      <c r="S72" s="45" t="s">
+      <c r="S72" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T72" s="27" t="str">
@@ -10988,7 +11061,7 @@
       <c r="R73" s="27" t="s">
         <v>658</v>
       </c>
-      <c r="S73" s="45" t="s">
+      <c r="S73" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T73" s="27" t="str">
@@ -11088,7 +11161,7 @@
       <c r="R74" s="27" t="s">
         <v>659</v>
       </c>
-      <c r="S74" s="45" t="s">
+      <c r="S74" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T74" s="27" t="str">
@@ -11188,7 +11261,7 @@
       <c r="R75" s="27" t="s">
         <v>660</v>
       </c>
-      <c r="S75" s="45" t="s">
+      <c r="S75" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T75" s="27" t="str">
@@ -11288,7 +11361,7 @@
       <c r="R76" s="27" t="s">
         <v>657</v>
       </c>
-      <c r="S76" s="45" t="s">
+      <c r="S76" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T76" s="27" t="str">
@@ -11388,7 +11461,7 @@
       <c r="R77" s="27" t="s">
         <v>658</v>
       </c>
-      <c r="S77" s="45" t="s">
+      <c r="S77" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T77" s="27" t="str">
@@ -11488,7 +11561,7 @@
       <c r="R78" s="27" t="s">
         <v>659</v>
       </c>
-      <c r="S78" s="45" t="s">
+      <c r="S78" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T78" s="27" t="str">
@@ -11588,7 +11661,7 @@
       <c r="R79" s="27" t="s">
         <v>660</v>
       </c>
-      <c r="S79" s="45" t="s">
+      <c r="S79" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T79" s="27" t="str">
@@ -11688,7 +11761,7 @@
       <c r="R80" s="27" t="s">
         <v>657</v>
       </c>
-      <c r="S80" s="45" t="s">
+      <c r="S80" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T80" s="27" t="str">
@@ -11788,7 +11861,7 @@
       <c r="R81" s="27" t="s">
         <v>658</v>
       </c>
-      <c r="S81" s="45" t="s">
+      <c r="S81" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T81" s="27" t="str">
@@ -11888,7 +11961,7 @@
       <c r="R82" s="27" t="s">
         <v>659</v>
       </c>
-      <c r="S82" s="45" t="s">
+      <c r="S82" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T82" s="27" t="str">
@@ -11988,7 +12061,7 @@
       <c r="R83" s="27" t="s">
         <v>660</v>
       </c>
-      <c r="S83" s="45" t="s">
+      <c r="S83" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T83" s="27" t="str">
@@ -12088,7 +12161,7 @@
       <c r="R84" s="27" t="s">
         <v>661</v>
       </c>
-      <c r="S84" s="45" t="s">
+      <c r="S84" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T84" s="27" t="str">
@@ -12188,7 +12261,7 @@
       <c r="R85" s="27" t="s">
         <v>662</v>
       </c>
-      <c r="S85" s="45" t="s">
+      <c r="S85" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T85" s="27" t="str">
@@ -12288,7 +12361,7 @@
       <c r="R86" s="27" t="s">
         <v>652</v>
       </c>
-      <c r="S86" s="45" t="s">
+      <c r="S86" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T86" s="27" t="str">
@@ -12388,7 +12461,7 @@
       <c r="R87" s="27" t="s">
         <v>663</v>
       </c>
-      <c r="S87" s="45" t="s">
+      <c r="S87" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T87" s="27" t="str">
@@ -12488,7 +12561,7 @@
       <c r="R88" s="27" t="s">
         <v>664</v>
       </c>
-      <c r="S88" s="45" t="s">
+      <c r="S88" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T88" s="27" t="str">
@@ -12588,7 +12661,7 @@
       <c r="R89" s="27" t="s">
         <v>665</v>
       </c>
-      <c r="S89" s="45" t="s">
+      <c r="S89" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T89" s="27" t="str">
@@ -12688,7 +12761,7 @@
       <c r="R90" s="27" t="s">
         <v>666</v>
       </c>
-      <c r="S90" s="45" t="s">
+      <c r="S90" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T90" s="27" t="str">
@@ -12788,7 +12861,7 @@
       <c r="R91" s="27" t="s">
         <v>667</v>
       </c>
-      <c r="S91" s="45" t="s">
+      <c r="S91" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T91" s="27" t="str">
@@ -12888,7 +12961,7 @@
       <c r="R92" s="27" t="s">
         <v>668</v>
       </c>
-      <c r="S92" s="45" t="s">
+      <c r="S92" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T92" s="27" t="str">
@@ -12988,7 +13061,7 @@
       <c r="R93" s="27" t="s">
         <v>656</v>
       </c>
-      <c r="S93" s="45" t="s">
+      <c r="S93" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T93" s="27" t="str">
@@ -13088,7 +13161,7 @@
       <c r="R94" s="27" t="s">
         <v>653</v>
       </c>
-      <c r="S94" s="45" t="s">
+      <c r="S94" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T94" s="27" t="str">
@@ -13188,7 +13261,7 @@
       <c r="R95" s="27" t="s">
         <v>669</v>
       </c>
-      <c r="S95" s="45" t="s">
+      <c r="S95" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T95" s="27" t="str">
@@ -13288,7 +13361,7 @@
       <c r="R96" s="27" t="s">
         <v>670</v>
       </c>
-      <c r="S96" s="45" t="s">
+      <c r="S96" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T96" s="27" t="str">
@@ -13388,7 +13461,7 @@
       <c r="R97" s="27" t="s">
         <v>671</v>
       </c>
-      <c r="S97" s="45" t="s">
+      <c r="S97" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T97" s="27" t="str">
@@ -13488,7 +13561,7 @@
       <c r="R98" s="27" t="s">
         <v>672</v>
       </c>
-      <c r="S98" s="45" t="s">
+      <c r="S98" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T98" s="27" t="str">
@@ -13588,7 +13661,7 @@
       <c r="R99" s="27" t="s">
         <v>673</v>
       </c>
-      <c r="S99" s="45" t="s">
+      <c r="S99" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T99" s="27" t="str">
@@ -13688,7 +13761,7 @@
       <c r="R100" s="27" t="s">
         <v>674</v>
       </c>
-      <c r="S100" s="45" t="s">
+      <c r="S100" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T100" s="27" t="str">
@@ -13788,7 +13861,7 @@
       <c r="R101" s="27" t="s">
         <v>675</v>
       </c>
-      <c r="S101" s="45" t="s">
+      <c r="S101" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T101" s="27" t="str">
@@ -13888,7 +13961,7 @@
       <c r="R102" s="27" t="s">
         <v>676</v>
       </c>
-      <c r="S102" s="45" t="s">
+      <c r="S102" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T102" s="27" t="str">
@@ -13988,7 +14061,7 @@
       <c r="R103" s="27" t="s">
         <v>677</v>
       </c>
-      <c r="S103" s="45" t="s">
+      <c r="S103" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T103" s="27" t="str">
@@ -14088,7 +14161,7 @@
       <c r="R104" s="27" t="s">
         <v>678</v>
       </c>
-      <c r="S104" s="45" t="s">
+      <c r="S104" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T104" s="27" t="str">
@@ -14188,7 +14261,7 @@
       <c r="R105" s="27" t="s">
         <v>679</v>
       </c>
-      <c r="S105" s="45" t="s">
+      <c r="S105" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T105" s="27" t="str">
@@ -14288,7 +14361,7 @@
       <c r="R106" s="27" t="s">
         <v>680</v>
       </c>
-      <c r="S106" s="45" t="s">
+      <c r="S106" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T106" s="27" t="str">
@@ -14388,7 +14461,7 @@
       <c r="R107" s="27" t="s">
         <v>681</v>
       </c>
-      <c r="S107" s="45" t="s">
+      <c r="S107" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T107" s="27" t="str">
@@ -14488,7 +14561,7 @@
       <c r="R108" s="27" t="s">
         <v>682</v>
       </c>
-      <c r="S108" s="45" t="s">
+      <c r="S108" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T108" s="27" t="str">
@@ -14588,7 +14661,7 @@
       <c r="R109" s="27" t="s">
         <v>683</v>
       </c>
-      <c r="S109" s="45" t="s">
+      <c r="S109" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T109" s="27" t="str">
@@ -14688,7 +14761,7 @@
       <c r="R110" s="27" t="s">
         <v>684</v>
       </c>
-      <c r="S110" s="45" t="s">
+      <c r="S110" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T110" s="27" t="str">
@@ -14788,7 +14861,7 @@
       <c r="R111" s="27" t="s">
         <v>685</v>
       </c>
-      <c r="S111" s="45" t="s">
+      <c r="S111" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T111" s="27" t="str">
@@ -14888,7 +14961,7 @@
       <c r="R112" s="27" t="s">
         <v>686</v>
       </c>
-      <c r="S112" s="45" t="s">
+      <c r="S112" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T112" s="27" t="str">
@@ -14988,7 +15061,7 @@
       <c r="R113" s="27" t="s">
         <v>687</v>
       </c>
-      <c r="S113" s="45" t="s">
+      <c r="S113" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T113" s="27" t="str">
@@ -15089,7 +15162,7 @@
       <c r="R114" s="27" t="s">
         <v>688</v>
       </c>
-      <c r="S114" s="45" t="s">
+      <c r="S114" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T114" s="45" t="str">
@@ -15190,7 +15263,7 @@
       <c r="R115" s="27" t="s">
         <v>689</v>
       </c>
-      <c r="S115" s="45" t="s">
+      <c r="S115" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T115" s="45" t="str">
@@ -15291,7 +15364,7 @@
       <c r="R116" s="27" t="s">
         <v>690</v>
       </c>
-      <c r="S116" s="45" t="s">
+      <c r="S116" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T116" s="45" t="str">
@@ -15392,7 +15465,7 @@
       <c r="R117" s="27" t="s">
         <v>691</v>
       </c>
-      <c r="S117" s="45" t="s">
+      <c r="S117" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T117" s="45" t="str">
@@ -15493,7 +15566,7 @@
       <c r="R118" s="27" t="s">
         <v>692</v>
       </c>
-      <c r="S118" s="45" t="s">
+      <c r="S118" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T118" s="45" t="str">
@@ -15594,7 +15667,7 @@
       <c r="R119" s="27" t="s">
         <v>693</v>
       </c>
-      <c r="S119" s="45" t="s">
+      <c r="S119" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T119" s="45" t="str">
@@ -15695,7 +15768,7 @@
       <c r="R120" s="27" t="s">
         <v>694</v>
       </c>
-      <c r="S120" s="45" t="s">
+      <c r="S120" s="69" t="s">
         <v>9</v>
       </c>
       <c r="T120" s="45" t="str">
@@ -15736,85 +15809,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:30" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="41">
         <v>121</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>523</v>
+        <v>722</v>
       </c>
       <c r="C121" s="44" t="s">
+        <v>723</v>
+      </c>
+      <c r="D121" s="44" t="s">
+        <v>724</v>
+      </c>
+      <c r="E121" s="44" t="s">
+        <v>725</v>
+      </c>
+      <c r="F121" s="44" t="s">
         <v>701</v>
       </c>
-      <c r="D121" s="44" t="s">
+      <c r="G121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K121" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L121" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="M121" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="N121" s="32" t="s">
+        <v>726</v>
+      </c>
+      <c r="O121" s="32" t="s">
+        <v>727</v>
+      </c>
+      <c r="P121" s="27" t="s">
+        <v>702</v>
+      </c>
+      <c r="Q121" s="27" t="s">
         <v>703</v>
       </c>
-      <c r="E121" s="44" t="s">
-        <v>702</v>
-      </c>
-      <c r="F121" s="44" t="s">
+      <c r="R121" s="27" t="s">
         <v>704</v>
       </c>
-      <c r="G121" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="H121" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I121" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="J121" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="K121" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="L121" s="32" t="str">
-        <f t="shared" ref="L121:O125" si="41">SUBSTITUTE(CONCATENATE("", C121), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M121" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N121" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O121" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P121" s="27" t="s">
-        <v>705</v>
-      </c>
-      <c r="Q121" s="27" t="s">
-        <v>706</v>
-      </c>
-      <c r="R121" s="27" t="s">
-        <v>707</v>
-      </c>
-      <c r="S121" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T121" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>De API</v>
-      </c>
-      <c r="U121" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>Macros</v>
-      </c>
-      <c r="V121" s="45" t="str">
-        <f t="shared" si="40"/>
-        <v>Métodos</v>
+      <c r="S121" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="T121" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="U121" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="V121" s="45" t="s">
+        <v>726</v>
       </c>
       <c r="W121" s="27" t="s">
         <v>43</v>
       </c>
       <c r="X121" s="43" t="str">
-        <f t="shared" ref="X121:X125" si="42">CONCATENATE("Key-CIRCU-",A121)</f>
+        <f t="shared" si="30"/>
         <v>Key-CIRCU-121</v>
       </c>
       <c r="Y121" s="68" t="s">
@@ -15836,85 +15902,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:30" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="41">
         <v>122</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>523</v>
+        <v>722</v>
       </c>
       <c r="C122" s="44" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="D122" s="44" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="E122" s="44" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="F122" s="44" t="s">
+        <v>705</v>
+      </c>
+      <c r="G122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K122" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L122" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="M122" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="N122" s="32" t="s">
+        <v>726</v>
+      </c>
+      <c r="O122" s="32" t="s">
+        <v>730</v>
+      </c>
+      <c r="P122" s="27" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q122" s="27" t="s">
+        <v>707</v>
+      </c>
+      <c r="R122" s="27" t="s">
         <v>708</v>
       </c>
-      <c r="G122" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="H122" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I122" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="J122" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="K122" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="L122" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M122" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N122" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O122" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P122" s="27" t="s">
-        <v>709</v>
-      </c>
-      <c r="Q122" s="27" t="s">
-        <v>710</v>
-      </c>
-      <c r="R122" s="27" t="s">
-        <v>711</v>
-      </c>
-      <c r="S122" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T122" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>De API</v>
-      </c>
-      <c r="U122" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>Macros</v>
-      </c>
-      <c r="V122" s="45" t="str">
-        <f t="shared" si="40"/>
-        <v>Métodos</v>
+      <c r="S122" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="T122" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="U122" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="V122" s="45" t="s">
+        <v>726</v>
       </c>
       <c r="W122" s="27" t="s">
         <v>43</v>
       </c>
       <c r="X122" s="43" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="30"/>
         <v>Key-CIRCU-122</v>
       </c>
       <c r="Y122" s="68" t="s">
@@ -15936,85 +15995,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:30" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="41">
         <v>123</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>523</v>
+        <v>722</v>
       </c>
       <c r="C123" s="44" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="D123" s="44" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="E123" s="44" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="F123" s="44" t="s">
+        <v>709</v>
+      </c>
+      <c r="G123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K123" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L123" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="M123" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="N123" s="32" t="s">
+        <v>726</v>
+      </c>
+      <c r="O123" s="32" t="s">
+        <v>731</v>
+      </c>
+      <c r="P123" s="27" t="s">
+        <v>710</v>
+      </c>
+      <c r="Q123" s="27" t="s">
+        <v>711</v>
+      </c>
+      <c r="R123" s="27" t="s">
         <v>712</v>
       </c>
-      <c r="G123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="H123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="J123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="K123" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="L123" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M123" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N123" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O123" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P123" s="27" t="s">
-        <v>713</v>
-      </c>
-      <c r="Q123" s="27" t="s">
-        <v>714</v>
-      </c>
-      <c r="R123" s="27" t="s">
-        <v>715</v>
-      </c>
-      <c r="S123" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T123" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>De API</v>
-      </c>
-      <c r="U123" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>Macros</v>
-      </c>
-      <c r="V123" s="45" t="str">
-        <f t="shared" si="40"/>
-        <v>Métodos</v>
+      <c r="S123" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="T123" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="U123" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="V123" s="45" t="s">
+        <v>726</v>
       </c>
       <c r="W123" s="27" t="s">
         <v>43</v>
       </c>
       <c r="X123" s="43" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="30"/>
         <v>Key-CIRCU-123</v>
       </c>
       <c r="Y123" s="68" t="s">
@@ -16036,85 +16088,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:30" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="41">
         <v>124</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>523</v>
+        <v>722</v>
       </c>
       <c r="C124" s="44" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="D124" s="44" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="E124" s="44" t="s">
-        <v>702</v>
+        <v>725</v>
       </c>
       <c r="F124" s="44" t="s">
+        <v>713</v>
+      </c>
+      <c r="G124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K124" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L124" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="M124" s="32" t="s">
+        <v>724</v>
+      </c>
+      <c r="N124" s="32" t="s">
+        <v>726</v>
+      </c>
+      <c r="O124" s="32" t="s">
+        <v>732</v>
+      </c>
+      <c r="P124" s="27" t="s">
+        <v>714</v>
+      </c>
+      <c r="Q124" s="27" t="s">
+        <v>715</v>
+      </c>
+      <c r="R124" s="27" t="s">
         <v>716</v>
       </c>
-      <c r="G124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="H124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="J124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="K124" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="L124" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M124" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N124" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O124" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P124" s="27" t="s">
-        <v>717</v>
-      </c>
-      <c r="Q124" s="27" t="s">
-        <v>718</v>
-      </c>
-      <c r="R124" s="27" t="s">
-        <v>719</v>
-      </c>
-      <c r="S124" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T124" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>De API</v>
-      </c>
-      <c r="U124" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>Macros</v>
-      </c>
-      <c r="V124" s="45" t="str">
-        <f t="shared" si="40"/>
-        <v>Métodos</v>
+      <c r="S124" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="T124" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="U124" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="V124" s="45" t="s">
+        <v>726</v>
       </c>
       <c r="W124" s="27" t="s">
         <v>43</v>
       </c>
       <c r="X124" s="43" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="30"/>
         <v>Key-CIRCU-124</v>
       </c>
       <c r="Y124" s="68" t="s">
@@ -16136,85 +16181,78 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:30" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:30" s="70" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="41">
         <v>125</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>523</v>
+        <v>722</v>
       </c>
       <c r="C125" s="44" t="s">
-        <v>701</v>
+        <v>723</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>703</v>
+        <v>733</v>
       </c>
       <c r="E125" s="44" t="s">
+        <v>734</v>
+      </c>
+      <c r="F125" s="44" t="s">
+        <v>717</v>
+      </c>
+      <c r="G125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="I125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="K125" s="67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L125" s="32" t="s">
+        <v>723</v>
+      </c>
+      <c r="M125" s="32" t="s">
+        <v>733</v>
+      </c>
+      <c r="N125" s="32" t="s">
+        <v>735</v>
+      </c>
+      <c r="O125" s="32" t="s">
+        <v>736</v>
+      </c>
+      <c r="P125" s="27" t="s">
+        <v>718</v>
+      </c>
+      <c r="Q125" s="27" t="s">
+        <v>719</v>
+      </c>
+      <c r="R125" s="27" t="s">
         <v>720</v>
       </c>
-      <c r="F125" s="44" t="s">
-        <v>721</v>
-      </c>
-      <c r="G125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="H125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="I125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="J125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="K125" s="67" t="s">
-        <v>9</v>
-      </c>
-      <c r="L125" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M125" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N125" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O125" s="32" t="str">
-        <f t="shared" si="41"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P125" s="27" t="s">
-        <v>722</v>
-      </c>
-      <c r="Q125" s="27" t="s">
-        <v>723</v>
-      </c>
-      <c r="R125" s="27" t="s">
-        <v>724</v>
-      </c>
-      <c r="S125" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="T125" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>De API</v>
-      </c>
-      <c r="U125" s="27" t="str">
-        <f t="shared" si="40"/>
-        <v>Macros</v>
-      </c>
-      <c r="V125" s="45" t="str">
-        <f t="shared" si="40"/>
-        <v>Códigos Visuais</v>
+      <c r="S125" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="T125" s="27" t="s">
+        <v>728</v>
+      </c>
+      <c r="U125" s="27" t="s">
+        <v>737</v>
+      </c>
+      <c r="V125" s="45" t="s">
+        <v>735</v>
       </c>
       <c r="W125" s="27" t="s">
         <v>43</v>
       </c>
       <c r="X125" s="43" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="30"/>
         <v>Key-CIRCU-125</v>
       </c>
       <c r="Y125" s="68" t="s">
@@ -16240,87 +16278,80 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AC120">
     <sortCondition ref="E1:E120"/>
   </sortState>
-  <conditionalFormatting sqref="B121:B125">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B2:E2 P2:Q4 W2:W4">
-    <cfRule type="cellIs" dxfId="23" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:E3 D4:E4">
-    <cfRule type="cellIs" dxfId="22" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="63" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:D47 E11:E53">
-    <cfRule type="cellIs" dxfId="21" priority="90" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="93" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D6:E10">
-    <cfRule type="cellIs" dxfId="20" priority="58" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="61" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D68:E116">
-    <cfRule type="cellIs" dxfId="19" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E62:E67 D65:D67">
-    <cfRule type="cellIs" dxfId="18" priority="63" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="66" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E125:F125">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F114:F116">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117:F120 F1:F113 F126:F1048576">
-    <cfRule type="duplicateValues" dxfId="15" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F121:F124">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L117:Q120 T117:V120">
-    <cfRule type="cellIs" dxfId="13" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="35" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P7:Q8 AA7:AA8">
-    <cfRule type="cellIs" dxfId="12" priority="138" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="141" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R120">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA117">
-    <cfRule type="cellIs" dxfId="10" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="27" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA119:AA120">
-    <cfRule type="cellIs" dxfId="9" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1">
-    <cfRule type="cellIs" dxfId="8" priority="137" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="140" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:XFD4 A2:A125 AA3:AA4 AC3:AC4 B3:B113 C4:C113 AE7:XFD8 P15:Q113 AA15:AA113 AE15:XFD113 D48:E64 B114:C116 B117:E120 AE117:XFD120 W6:W125">
-    <cfRule type="cellIs" dxfId="7" priority="31" operator="equal">
+  <conditionalFormatting sqref="AE2:XFD4 AA3:AA4 AC3:AC4 B3:B113 C4:C113 AE7:XFD8 P15:Q113 AA15:AA113 AE15:XFD113 D48:E64 B114:C116 B117:E120 AE117:XFD120 A2:A125 W6:W125">
+    <cfRule type="cellIs" dxfId="0" priority="34" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F121:F125">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16534,7 +16565,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16609,22 +16640,22 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="4" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
